--- a/EEFUL_資金計画_シナリオ別月次.xlsx
+++ b/EEFUL_資金計画_シナリオ別月次.xlsx
@@ -2867,22 +2867,22 @@
         <v>11</v>
       </c>
       <c r="C65" s="13" t="n">
-        <v>0.168</v>
+        <v>0.232</v>
       </c>
       <c r="D65" s="10" t="n">
-        <v>3012</v>
+        <v>3207</v>
       </c>
       <c r="E65" s="10" t="n">
-        <v>3025</v>
+        <v>3245</v>
       </c>
       <c r="F65" s="10" t="n">
-        <v>3516</v>
+        <v>3663</v>
       </c>
       <c r="G65" s="10" t="n">
-        <v>420</v>
+        <v>451</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>541</v>
+        <v>561</v>
       </c>
       <c r="I65" s="10" t="n">
         <v>612</v>
@@ -2901,22 +2901,22 @@
         <v>9</v>
       </c>
       <c r="C66" s="13" t="n">
-        <v>0.28</v>
+        <v>0.334</v>
       </c>
       <c r="D66" s="10" t="n">
-        <v>3166</v>
+        <v>3361</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>3060</v>
+        <v>3270</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>3908</v>
+        <v>4200</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>458</v>
+        <v>476</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>696</v>
+        <v>739</v>
       </c>
       <c r="I66" s="10" t="n">
         <v>754</v>
@@ -2969,25 +2969,25 @@
         <v>14</v>
       </c>
       <c r="C68" s="13" t="n">
-        <v>0.551</v>
+        <v>0.619</v>
       </c>
       <c r="D68" s="10" t="n">
-        <v>3849</v>
+        <v>4041</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>3754</v>
+        <v>3910</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>4758</v>
+        <v>4907</v>
       </c>
       <c r="G68" s="10" t="n">
-        <v>597</v>
+        <v>623</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>838</v>
+        <v>867</v>
       </c>
       <c r="I68" s="10" t="n">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="J68" s="10" t="n">
         <v>7686</v>
@@ -3003,25 +3003,25 @@
         <v>22</v>
       </c>
       <c r="C69" s="13" t="n">
-        <v>0.644</v>
+        <v>0.716</v>
       </c>
       <c r="D69" s="10" t="n">
-        <v>4084</v>
+        <v>4279</v>
       </c>
       <c r="E69" s="10" t="n">
-        <v>3992</v>
+        <v>4177</v>
       </c>
       <c r="F69" s="10" t="n">
-        <v>4999</v>
+        <v>5192</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>775</v>
+        <v>806</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>1047</v>
+        <v>1078</v>
       </c>
       <c r="I69" s="10" t="n">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="J69" s="10" t="n">
         <v>9210</v>
@@ -3030,7 +3030,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>期限を2028/6に延ばした場合（戦略F）：到達確率 84%、必要資金P50 763</t>
+          <t>期限を2028/6に延ばした場合（戦略F）：到達確率 89%、必要資金P50 793</t>
         </is>
       </c>
     </row>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>LOI口頭合意（9/12）・基本合意9月中</t>
+          <t>DD（LOI 9/5・口頭合意9/12）</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">

--- a/EEFUL_資金計画_シナリオ別月次.xlsx
+++ b/EEFUL_資金計画_シナリオ別月次.xlsx
@@ -2833,22 +2833,22 @@
         <v>11</v>
       </c>
       <c r="C64" s="13" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.013</v>
       </c>
       <c r="D64" s="10" t="n">
-        <v>2561</v>
+        <v>2598</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>2576</v>
+        <v>2613</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>2968</v>
+        <v>2993</v>
       </c>
       <c r="G64" s="10" t="n">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="I64" s="10" t="n">
         <v>633</v>
@@ -2867,22 +2867,22 @@
         <v>11</v>
       </c>
       <c r="C65" s="13" t="n">
-        <v>0.232</v>
+        <v>0.291</v>
       </c>
       <c r="D65" s="10" t="n">
-        <v>3207</v>
+        <v>3361</v>
       </c>
       <c r="E65" s="10" t="n">
-        <v>3245</v>
+        <v>3370</v>
       </c>
       <c r="F65" s="10" t="n">
-        <v>3663</v>
+        <v>3770</v>
       </c>
       <c r="G65" s="10" t="n">
-        <v>451</v>
+        <v>473</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>561</v>
+        <v>586</v>
       </c>
       <c r="I65" s="10" t="n">
         <v>612</v>
@@ -2901,22 +2901,22 @@
         <v>9</v>
       </c>
       <c r="C66" s="13" t="n">
-        <v>0.334</v>
+        <v>0.373</v>
       </c>
       <c r="D66" s="10" t="n">
-        <v>3361</v>
+        <v>3517</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>3270</v>
+        <v>3320</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>4200</v>
+        <v>4307</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>476</v>
+        <v>520</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="I66" s="10" t="n">
         <v>754</v>
@@ -2935,25 +2935,25 @@
         <v>10</v>
       </c>
       <c r="C67" s="13" t="n">
-        <v>0.159</v>
+        <v>0.163</v>
       </c>
       <c r="D67" s="10" t="n">
-        <v>2886</v>
+        <v>2923</v>
       </c>
       <c r="E67" s="10" t="n">
-        <v>2772</v>
+        <v>2841</v>
       </c>
       <c r="F67" s="10" t="n">
-        <v>3462</v>
+        <v>3498</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="I67" s="10" t="n">
-        <v>663</v>
+        <v>672</v>
       </c>
       <c r="J67" s="10" t="n">
         <v>5280</v>
@@ -2969,25 +2969,25 @@
         <v>14</v>
       </c>
       <c r="C68" s="13" t="n">
-        <v>0.619</v>
+        <v>0.674</v>
       </c>
       <c r="D68" s="10" t="n">
-        <v>4041</v>
+        <v>4194</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>3910</v>
+        <v>4051</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>4907</v>
+        <v>5050</v>
       </c>
       <c r="G68" s="10" t="n">
-        <v>623</v>
+        <v>653</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>867</v>
+        <v>892</v>
       </c>
       <c r="I68" s="10" t="n">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="J68" s="10" t="n">
         <v>7686</v>
@@ -3003,25 +3003,25 @@
         <v>22</v>
       </c>
       <c r="C69" s="13" t="n">
-        <v>0.716</v>
+        <v>0.774</v>
       </c>
       <c r="D69" s="10" t="n">
-        <v>4279</v>
+        <v>4433</v>
       </c>
       <c r="E69" s="10" t="n">
-        <v>4177</v>
+        <v>4325</v>
       </c>
       <c r="F69" s="10" t="n">
-        <v>5192</v>
+        <v>5304</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>806</v>
+        <v>831</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>1078</v>
+        <v>1103</v>
       </c>
       <c r="I69" s="10" t="n">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="J69" s="10" t="n">
         <v>9210</v>
@@ -3030,7 +3030,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>期限を2028/6に延ばした場合（戦略F）：到達確率 89%、必要資金P50 793</t>
+          <t>期限を2028/6に延ばした場合（戦略F）：到達確率 91%、必要資金P50 812</t>
         </is>
       </c>
     </row>

--- a/EEFUL_資金計画_シナリオ別月次.xlsx
+++ b/EEFUL_資金計画_シナリオ別月次.xlsx
@@ -16,8 +16,7 @@
     <sheet name="S3" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="S4" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="S5" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="S6" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="月次実績2026" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="月次実績2026" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -256,7 +255,7 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <v>S1 基本（確定4件）</v>
+            <v>S1 基本（確定5件）</v>
           </tx>
           <spPr>
             <a:ln>
@@ -273,12 +272,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'サマリー'!$D$23:$S$23</f>
+              <f>'サマリー'!$D$22:$S$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'サマリー'!$D$24:$S$24</f>
+              <f>'サマリー'!$D$23:$S$23</f>
             </numRef>
           </val>
         </ser>
@@ -303,12 +302,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'サマリー'!$D$23:$S$23</f>
+              <f>'サマリー'!$D$22:$S$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'サマリー'!$D$25:$S$25</f>
+              <f>'サマリー'!$D$24:$S$24</f>
             </numRef>
           </val>
         </ser>
@@ -333,12 +332,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'サマリー'!$D$23:$S$23</f>
+              <f>'サマリー'!$D$22:$S$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'サマリー'!$D$26:$S$26</f>
+              <f>'サマリー'!$D$25:$S$25</f>
             </numRef>
           </val>
         </ser>
@@ -363,12 +362,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'サマリー'!$D$23:$S$23</f>
+              <f>'サマリー'!$D$22:$S$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'サマリー'!$D$27:$S$27</f>
+              <f>'サマリー'!$D$26:$S$26</f>
             </numRef>
           </val>
         </ser>
@@ -393,48 +392,18 @@
           </marker>
           <cat>
             <numRef>
-              <f>'サマリー'!$D$23:$S$23</f>
+              <f>'サマリー'!$D$22:$S$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'サマリー'!$D$28:$S$28</f>
+              <f>'サマリー'!$D$27:$S$27</f>
             </numRef>
           </val>
         </ser>
         <ser>
           <idx val="5"/>
           <order val="5"/>
-          <tx>
-            <v>S6 全件＋シルバーメディカル</v>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'サマリー'!$D$23:$S$23</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'サマリー'!$D$29:$S$29</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="6"/>
-          <order val="6"/>
           <tx>
             <v>安全水準</v>
           </tx>
@@ -453,12 +422,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'サマリー'!$D$23:$S$23</f>
+              <f>'サマリー'!$D$22:$S$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'サマリー'!$D$30:$S$30</f>
+              <f>'サマリー'!$D$28:$S$28</f>
             </numRef>
           </val>
         </ser>
@@ -573,7 +542,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>41</row>
+      <row>38</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="10080000" cy="3240000"/>
@@ -883,7 +852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S70"/>
+  <dimension ref="A1:S67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1003,7 +972,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>S1 基本（確定4件）</t>
+          <t>S1 基本（確定5件）</t>
         </is>
       </c>
       <c r="B5" s="5" t="str">
@@ -1012,16 +981,16 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>メディプロ、ヒューマンアイ、クレッシェンド</t>
+          <t>メディプロ、ヒューマンアイ、シルバーメディカル、クレッシェンド</t>
         </is>
       </c>
       <c r="D5" s="7">
         <f>S1!$B$39</f>
-        <v>133.6</v>
+        <v>253.7</v>
       </c>
       <c r="E5" s="7">
         <f>S1!$B$40</f>
-        <v>144.7</v>
+        <v>24.6</v>
       </c>
       <c r="F5" s="8" t="str">
         <f>S1!$B$41</f>
@@ -1029,11 +998,11 @@
       </c>
       <c r="G5" s="8" t="str">
         <f>S1!$B$42</f>
-        <v>—</v>
+        <v>2026/12</v>
       </c>
       <c r="H5" s="7">
         <f>S1!$B$43</f>
-        <v>0</v>
+        <v>75.4</v>
       </c>
       <c r="I5" s="7">
         <f>S1!$B$44</f>
@@ -1041,31 +1010,31 @@
       </c>
       <c r="J5" s="7">
         <f>S1!$B$45</f>
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="K5" s="7">
         <f>S1!$B$46</f>
-        <v>0</v>
+        <v>30.4</v>
       </c>
       <c r="L5" s="7">
         <f>S1!$B$47</f>
-        <v>144.7</v>
+        <v>24.6</v>
       </c>
       <c r="M5" s="9">
         <f>S1!$B$48</f>
-        <v>1658</v>
+        <v>2435</v>
       </c>
       <c r="N5" s="9">
         <f>S1!$B$49</f>
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="O5" s="9">
         <f>S1!$B$50</f>
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="P5" s="7">
         <f>S1!$B$51</f>
-        <v>44.85</v>
+        <v>127.85</v>
       </c>
     </row>
     <row r="6">
@@ -1080,16 +1049,16 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>メディプロ、ヒューマンアイ、クレッシェンド、ワイズケア</t>
+          <t>メディプロ、ヒューマンアイ、シルバーメディカル、クレッシェンド、ワイズケア</t>
         </is>
       </c>
       <c r="D6" s="7">
         <f>S2!$B$39</f>
-        <v>269.6</v>
+        <v>389.7</v>
       </c>
       <c r="E6" s="7">
         <f>S2!$B$40</f>
-        <v>8.7</v>
+        <v>-111.4</v>
       </c>
       <c r="F6" s="8" t="str">
         <f>S2!$B$41</f>
@@ -1101,39 +1070,39 @@
       </c>
       <c r="H6" s="7">
         <f>S2!$B$43</f>
-        <v>91.3</v>
+        <v>211.4</v>
       </c>
       <c r="I6" s="7">
         <f>S2!$B$44</f>
-        <v>0.3</v>
+        <v>6.4</v>
       </c>
       <c r="J6" s="7">
         <f>S2!$B$45</f>
-        <v>24.3</v>
+        <v>144.4</v>
       </c>
       <c r="K6" s="7">
         <f>S2!$B$46</f>
-        <v>46.3</v>
+        <v>166.4</v>
       </c>
       <c r="L6" s="7">
         <f>S2!$B$47</f>
-        <v>8.7</v>
+        <v>-111.4</v>
       </c>
       <c r="M6" s="9">
         <f>S2!$B$48</f>
-        <v>2143</v>
+        <v>2920</v>
       </c>
       <c r="N6" s="9">
         <f>S2!$B$49</f>
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="O6" s="9">
         <f>S2!$B$50</f>
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="P6" s="7">
         <f>S2!$B$51</f>
-        <v>44.85</v>
+        <v>127.85</v>
       </c>
     </row>
     <row r="7">
@@ -1148,16 +1117,16 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>メディプロ、ヒューマンアイ、クレッシェンド、エーステイスト</t>
+          <t>メディプロ、ヒューマンアイ、シルバーメディカル、クレッシェンド、エーステイスト</t>
         </is>
       </c>
       <c r="D7" s="7">
         <f>S3!$B$39</f>
-        <v>208.1</v>
+        <v>328.2</v>
       </c>
       <c r="E7" s="7">
         <f>S3!$B$40</f>
-        <v>70.2</v>
+        <v>-49.9</v>
       </c>
       <c r="F7" s="8" t="str">
         <f>S3!$B$41</f>
@@ -1165,11 +1134,11 @@
       </c>
       <c r="G7" s="8" t="str">
         <f>S3!$B$42</f>
-        <v>2027/7</v>
+        <v>2026/12</v>
       </c>
       <c r="H7" s="7">
         <f>S3!$B$43</f>
-        <v>29.8</v>
+        <v>149.9</v>
       </c>
       <c r="I7" s="7">
         <f>S3!$B$44</f>
@@ -1177,31 +1146,31 @@
       </c>
       <c r="J7" s="7">
         <f>S3!$B$45</f>
-        <v>0</v>
+        <v>82.9</v>
       </c>
       <c r="K7" s="7">
         <f>S3!$B$46</f>
-        <v>0</v>
+        <v>104.9</v>
       </c>
       <c r="L7" s="7">
         <f>S3!$B$47</f>
-        <v>70.2</v>
+        <v>-49.9</v>
       </c>
       <c r="M7" s="9">
         <f>S3!$B$48</f>
-        <v>2108</v>
+        <v>2885</v>
       </c>
       <c r="N7" s="9">
         <f>S3!$B$49</f>
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="O7" s="9">
         <f>S3!$B$50</f>
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="P7" s="7">
         <f>S3!$B$51</f>
-        <v>105.25</v>
+        <v>188.25</v>
       </c>
     </row>
     <row r="8">
@@ -1216,16 +1185,16 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>メディプロ、ヒューマンアイ、クレッシェンド、ワイズケア、エーステイスト</t>
+          <t>メディプロ、ヒューマンアイ、シルバーメディカル、クレッシェンド、ワイズケア、エーステイスト</t>
         </is>
       </c>
       <c r="D8" s="7">
         <f>S4!$B$39</f>
-        <v>344.1</v>
+        <v>464.2</v>
       </c>
       <c r="E8" s="7">
         <f>S4!$B$40</f>
-        <v>-65.8</v>
+        <v>-185.9</v>
       </c>
       <c r="F8" s="8" t="str">
         <f>S4!$B$41</f>
@@ -1237,39 +1206,39 @@
       </c>
       <c r="H8" s="7">
         <f>S4!$B$43</f>
-        <v>165.8</v>
+        <v>285.9</v>
       </c>
       <c r="I8" s="7">
         <f>S4!$B$44</f>
-        <v>5.05</v>
+        <v>11.15</v>
       </c>
       <c r="J8" s="7">
         <f>S4!$B$45</f>
-        <v>98.8</v>
+        <v>218.9</v>
       </c>
       <c r="K8" s="7">
         <f>S4!$B$46</f>
-        <v>120.8</v>
+        <v>240.9</v>
       </c>
       <c r="L8" s="7">
         <f>S4!$B$47</f>
-        <v>-65.8</v>
+        <v>-185.9</v>
       </c>
       <c r="M8" s="9">
         <f>S4!$B$48</f>
-        <v>2593</v>
+        <v>3370</v>
       </c>
       <c r="N8" s="9">
         <f>S4!$B$49</f>
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="O8" s="9">
         <f>S4!$B$50</f>
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="P8" s="7">
         <f>S4!$B$51</f>
-        <v>105.25</v>
+        <v>188.25</v>
       </c>
     </row>
     <row r="9">
@@ -1284,16 +1253,16 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>メディプロ、ヒューマンアイ、クレッシェンド、ワイズケア、エーステイスト、日本経営センター、セレサ</t>
+          <t>メディプロ、ヒューマンアイ、クレッシェンド、ワイズケア、エーステイスト、日本経営センター、セレサ、シルバーメディカル</t>
         </is>
       </c>
       <c r="D9" s="7">
         <f>S5!$B$39</f>
-        <v>494.2</v>
+        <v>614.3</v>
       </c>
       <c r="E9" s="7">
         <f>S5!$B$40</f>
-        <v>-215.9</v>
+        <v>-336.0</v>
       </c>
       <c r="F9" s="8" t="str">
         <f>S5!$B$41</f>
@@ -1305,106 +1274,38 @@
       </c>
       <c r="H9" s="7">
         <f>S5!$B$43</f>
-        <v>315.9</v>
+        <v>436.0</v>
       </c>
       <c r="I9" s="7">
         <f>S5!$B$44</f>
-        <v>5.05</v>
+        <v>11.15</v>
       </c>
       <c r="J9" s="7">
         <f>S5!$B$45</f>
-        <v>191.3</v>
+        <v>311.4</v>
       </c>
       <c r="K9" s="7">
         <f>S5!$B$46</f>
-        <v>270.9</v>
+        <v>391.0</v>
       </c>
       <c r="L9" s="7">
         <f>S5!$B$47</f>
-        <v>-215.9</v>
+        <v>-336.0</v>
       </c>
       <c r="M9" s="9">
         <f>S5!$B$48</f>
-        <v>3111</v>
+        <v>3888</v>
       </c>
       <c r="N9" s="9">
         <f>S5!$B$49</f>
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="O9" s="9">
         <f>S5!$B$50</f>
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="P9" s="7">
         <f>S5!$B$51</f>
-        <v>138.15</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>S6 全件＋シルバーメディカル</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="str">
-        <f>S6!$B$3</f>
-        <v>最小化</v>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>メディプロ、ヒューマンアイ、クレッシェンド、ワイズケア、エーステイスト、日本経営センター、セレサ、シルバーメディカル</t>
-        </is>
-      </c>
-      <c r="D10" s="7">
-        <f>S6!$B$39</f>
-        <v>614.3</v>
-      </c>
-      <c r="E10" s="7">
-        <f>S6!$B$40</f>
-        <v>-336.0</v>
-      </c>
-      <c r="F10" s="8" t="str">
-        <f>S6!$B$41</f>
-        <v>2027/12</v>
-      </c>
-      <c r="G10" s="8" t="str">
-        <f>S6!$B$42</f>
-        <v>2026/11</v>
-      </c>
-      <c r="H10" s="7">
-        <f>S6!$B$43</f>
-        <v>436.0</v>
-      </c>
-      <c r="I10" s="7">
-        <f>S6!$B$44</f>
-        <v>11.15</v>
-      </c>
-      <c r="J10" s="7">
-        <f>S6!$B$45</f>
-        <v>311.4</v>
-      </c>
-      <c r="K10" s="7">
-        <f>S6!$B$46</f>
-        <v>391.0</v>
-      </c>
-      <c r="L10" s="7">
-        <f>S6!$B$47</f>
-        <v>-336.0</v>
-      </c>
-      <c r="M10" s="9">
-        <f>S6!$B$48</f>
-        <v>3888</v>
-      </c>
-      <c r="N10" s="9">
-        <f>S6!$B$49</f>
-        <v>161</v>
-      </c>
-      <c r="O10" s="9">
-        <f>S6!$B$50</f>
-        <v>271</v>
-      </c>
-      <c r="P10" s="7">
-        <f>S6!$B$51</f>
         <v>221.15</v>
       </c>
     </row>
@@ -1460,32 +1361,32 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>S1 基本（確定4件）</t>
+          <t>S1 基本（確定5件）</t>
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>189.6</v>
+        <v>367.7</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>11</v>
+        <v>189</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>133.6</v>
+        <v>253.7</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26/12</t>
         </is>
       </c>
       <c r="G15" s="10" t="n">
-        <v>1658</v>
+        <v>2435</v>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>104 / 124</t>
+          <t>83 / 140</t>
         </is>
       </c>
     </row>
@@ -1496,16 +1397,16 @@
         </is>
       </c>
       <c r="B16" s="10" t="n">
-        <v>455.6</v>
+        <v>633.7</v>
       </c>
       <c r="C16" s="10" t="n">
-        <v>277</v>
+        <v>455</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>269.6</v>
+        <v>389.7</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>91</v>
+        <v>211</v>
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
@@ -1513,11 +1414,11 @@
         </is>
       </c>
       <c r="G16" s="10" t="n">
-        <v>2143</v>
+        <v>2920</v>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>142 / 190</t>
+          <t>121 / 206</t>
         </is>
       </c>
     </row>
@@ -1528,28 +1429,28 @@
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>264.2</v>
+        <v>442.2</v>
       </c>
       <c r="C17" s="10" t="n">
-        <v>86</v>
+        <v>264</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>208.2</v>
+        <v>328.2</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>27/7</t>
+          <t>26/12</t>
         </is>
       </c>
       <c r="G17" s="10" t="n">
-        <v>2108</v>
+        <v>2885</v>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>124 / 149</t>
+          <t>103 / 165</t>
         </is>
       </c>
     </row>
@@ -1560,16 +1461,16 @@
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>530.2</v>
+        <v>708.2</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>352</v>
+        <v>530</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>344.2</v>
+        <v>464.2</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>166</v>
+        <v>286</v>
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
@@ -1577,11 +1478,11 @@
         </is>
       </c>
       <c r="G18" s="10" t="n">
-        <v>2593</v>
+        <v>3370</v>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>162 / 215</t>
+          <t>141 / 231</t>
         </is>
       </c>
     </row>
@@ -1592,16 +1493,16 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>701.9</v>
+        <v>879.9</v>
       </c>
       <c r="C19" s="10" t="n">
-        <v>524</v>
+        <v>702</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>494.3</v>
+        <v>614.3</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>316</v>
+        <v>436</v>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
@@ -1609,1428 +1510,1254 @@
         </is>
       </c>
       <c r="G19" s="10" t="n">
-        <v>3111</v>
+        <v>3888</v>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>182 / 255</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>S6 全件＋シルバーメディカル</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="n">
-        <v>880</v>
-      </c>
-      <c r="C20" s="10" t="n">
-        <v>702</v>
-      </c>
-      <c r="D20" s="10" t="n">
-        <v>614.4</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>436</v>
-      </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>26/11</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="n">
-        <v>3888</v>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
           <t>161 / 271</t>
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>期末現預金の月次推移（シナリオ別・各シートのモードに連動）</t>
+        </is>
+      </c>
+    </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>期末現預金の月次推移（シナリオ別・各シートのモードに連動）</t>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>シナリオ</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="inlineStr"/>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>2026/9</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>2026/10</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>2026/11</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>2026/12</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>2027/1</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>2027/2</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>2027/3</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>2027/4</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>2027/5</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>2027/6</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>2027/7</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>2027/8</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>2027/9</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t>2027/10</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>2027/11</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr">
+        <is>
+          <t>2027/12</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>シナリオ</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr"/>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>2026/9</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>2026/10</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>2026/11</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>2026/12</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>2027/1</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>2027/2</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>2027/3</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>2027/4</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>2027/5</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>2027/6</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>2027/7</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>2027/8</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t>2027/9</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="inlineStr">
-        <is>
-          <t>2027/10</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t>2027/11</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="inlineStr">
-        <is>
-          <t>2027/12</t>
-        </is>
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>S1 基本（確定5件）</t>
+        </is>
+      </c>
+      <c r="D23" s="12">
+        <f>S1!C31</f>
+        <v>329.3</v>
+      </c>
+      <c r="E23" s="12">
+        <f>S1!D31</f>
+        <v>304.1</v>
+      </c>
+      <c r="F23" s="12">
+        <f>S1!E31</f>
+        <v>229.6</v>
+      </c>
+      <c r="G23" s="12">
+        <f>S1!F31</f>
+        <v>96.6</v>
+      </c>
+      <c r="H23" s="12">
+        <f>S1!G31</f>
+        <v>91.6</v>
+      </c>
+      <c r="I23" s="12">
+        <f>S1!H31</f>
+        <v>86.6</v>
+      </c>
+      <c r="J23" s="12">
+        <f>S1!I31</f>
+        <v>69.6</v>
+      </c>
+      <c r="K23" s="12">
+        <f>S1!J31</f>
+        <v>64.6</v>
+      </c>
+      <c r="L23" s="12">
+        <f>S1!K31</f>
+        <v>59.6</v>
+      </c>
+      <c r="M23" s="12">
+        <f>S1!L31</f>
+        <v>54.6</v>
+      </c>
+      <c r="N23" s="12">
+        <f>S1!M31</f>
+        <v>49.6</v>
+      </c>
+      <c r="O23" s="12">
+        <f>S1!N31</f>
+        <v>44.6</v>
+      </c>
+      <c r="P23" s="12">
+        <f>S1!O31</f>
+        <v>39.6</v>
+      </c>
+      <c r="Q23" s="12">
+        <f>S1!P31</f>
+        <v>34.6</v>
+      </c>
+      <c r="R23" s="12">
+        <f>S1!Q31</f>
+        <v>29.6</v>
+      </c>
+      <c r="S23" s="12">
+        <f>S1!R31</f>
+        <v>24.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>S1 基本（確定4件）</t>
+          <t>S2 基本＋ワイズケア</t>
         </is>
       </c>
       <c r="D24" s="12">
-        <f>S1!C31</f>
+        <f>S2!C31</f>
         <v>329.3</v>
       </c>
       <c r="E24" s="12">
-        <f>S1!D31</f>
-        <v>305.2</v>
+        <f>S2!D31</f>
+        <v>295.4</v>
       </c>
       <c r="F24" s="12">
-        <f>S1!E31</f>
-        <v>235.7</v>
+        <f>S2!E31</f>
+        <v>93.6</v>
       </c>
       <c r="G24" s="12">
-        <f>S1!F31</f>
-        <v>216.7</v>
+        <f>S2!F31</f>
+        <v>-39.4</v>
       </c>
       <c r="H24" s="12">
-        <f>S1!G31</f>
-        <v>211.7</v>
+        <f>S2!G31</f>
+        <v>-44.4</v>
       </c>
       <c r="I24" s="12">
-        <f>S1!H31</f>
-        <v>206.7</v>
+        <f>S2!H31</f>
+        <v>-49.4</v>
       </c>
       <c r="J24" s="12">
-        <f>S1!I31</f>
-        <v>189.7</v>
+        <f>S2!I31</f>
+        <v>-66.4</v>
       </c>
       <c r="K24" s="12">
-        <f>S1!J31</f>
-        <v>184.7</v>
+        <f>S2!J31</f>
+        <v>-71.4</v>
       </c>
       <c r="L24" s="12">
-        <f>S1!K31</f>
-        <v>179.7</v>
+        <f>S2!K31</f>
+        <v>-76.4</v>
       </c>
       <c r="M24" s="12">
-        <f>S1!L31</f>
-        <v>174.7</v>
+        <f>S2!L31</f>
+        <v>-81.4</v>
       </c>
       <c r="N24" s="12">
-        <f>S1!M31</f>
-        <v>169.7</v>
+        <f>S2!M31</f>
+        <v>-86.4</v>
       </c>
       <c r="O24" s="12">
-        <f>S1!N31</f>
-        <v>164.7</v>
+        <f>S2!N31</f>
+        <v>-91.4</v>
       </c>
       <c r="P24" s="12">
-        <f>S1!O31</f>
-        <v>159.7</v>
+        <f>S2!O31</f>
+        <v>-96.4</v>
       </c>
       <c r="Q24" s="12">
-        <f>S1!P31</f>
-        <v>154.7</v>
+        <f>S2!P31</f>
+        <v>-101.4</v>
       </c>
       <c r="R24" s="12">
-        <f>S1!Q31</f>
-        <v>149.7</v>
+        <f>S2!Q31</f>
+        <v>-106.4</v>
       </c>
       <c r="S24" s="12">
-        <f>S1!R31</f>
-        <v>144.7</v>
+        <f>S2!R31</f>
+        <v>-111.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>S2 基本＋ワイズケア</t>
+          <t>S3 基本＋エーステイスト</t>
         </is>
       </c>
       <c r="D25" s="12">
-        <f>S2!C31</f>
+        <f>S3!C31</f>
         <v>329.3</v>
       </c>
       <c r="E25" s="12">
-        <f>S2!D31</f>
-        <v>296.5</v>
+        <f>S3!D31</f>
+        <v>301.35</v>
       </c>
       <c r="F25" s="12">
-        <f>S2!E31</f>
-        <v>99.7</v>
+        <f>S3!E31</f>
+        <v>224.85</v>
       </c>
       <c r="G25" s="12">
-        <f>S2!F31</f>
-        <v>80.7</v>
+        <f>S3!F31</f>
+        <v>22.1</v>
       </c>
       <c r="H25" s="12">
-        <f>S2!G31</f>
-        <v>75.7</v>
+        <f>S3!G31</f>
+        <v>17.1</v>
       </c>
       <c r="I25" s="12">
-        <f>S2!H31</f>
-        <v>70.7</v>
+        <f>S3!H31</f>
+        <v>12.1</v>
       </c>
       <c r="J25" s="12">
-        <f>S2!I31</f>
-        <v>53.7</v>
+        <f>S3!I31</f>
+        <v>-4.9</v>
       </c>
       <c r="K25" s="12">
-        <f>S2!J31</f>
-        <v>48.7</v>
+        <f>S3!J31</f>
+        <v>-9.9</v>
       </c>
       <c r="L25" s="12">
-        <f>S2!K31</f>
-        <v>43.7</v>
+        <f>S3!K31</f>
+        <v>-14.9</v>
       </c>
       <c r="M25" s="12">
-        <f>S2!L31</f>
-        <v>38.7</v>
+        <f>S3!L31</f>
+        <v>-19.9</v>
       </c>
       <c r="N25" s="12">
-        <f>S2!M31</f>
-        <v>33.7</v>
+        <f>S3!M31</f>
+        <v>-24.9</v>
       </c>
       <c r="O25" s="12">
-        <f>S2!N31</f>
-        <v>28.7</v>
+        <f>S3!N31</f>
+        <v>-29.9</v>
       </c>
       <c r="P25" s="12">
-        <f>S2!O31</f>
-        <v>23.7</v>
+        <f>S3!O31</f>
+        <v>-34.9</v>
       </c>
       <c r="Q25" s="12">
-        <f>S2!P31</f>
-        <v>18.7</v>
+        <f>S3!P31</f>
+        <v>-39.9</v>
       </c>
       <c r="R25" s="12">
-        <f>S2!Q31</f>
-        <v>13.7</v>
+        <f>S3!Q31</f>
+        <v>-44.9</v>
       </c>
       <c r="S25" s="12">
-        <f>S2!R31</f>
-        <v>8.7</v>
+        <f>S3!R31</f>
+        <v>-49.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>S3 基本＋エーステイスト</t>
+          <t>S4 基本＋ワイズ＋エース</t>
         </is>
       </c>
       <c r="D26" s="12">
-        <f>S3!C31</f>
+        <f>S4!C31</f>
         <v>329.3</v>
       </c>
       <c r="E26" s="12">
-        <f>S3!D31</f>
-        <v>302.45</v>
+        <f>S4!D31</f>
+        <v>292.65</v>
       </c>
       <c r="F26" s="12">
-        <f>S3!E31</f>
-        <v>230.95</v>
+        <f>S4!E31</f>
+        <v>88.85</v>
       </c>
       <c r="G26" s="12">
-        <f>S3!F31</f>
-        <v>142.2</v>
+        <f>S4!F31</f>
+        <v>-113.9</v>
       </c>
       <c r="H26" s="12">
-        <f>S3!G31</f>
-        <v>137.2</v>
+        <f>S4!G31</f>
+        <v>-118.9</v>
       </c>
       <c r="I26" s="12">
-        <f>S3!H31</f>
-        <v>132.2</v>
+        <f>S4!H31</f>
+        <v>-123.9</v>
       </c>
       <c r="J26" s="12">
-        <f>S3!I31</f>
-        <v>115.2</v>
+        <f>S4!I31</f>
+        <v>-140.9</v>
       </c>
       <c r="K26" s="12">
-        <f>S3!J31</f>
-        <v>110.2</v>
+        <f>S4!J31</f>
+        <v>-145.9</v>
       </c>
       <c r="L26" s="12">
-        <f>S3!K31</f>
-        <v>105.2</v>
+        <f>S4!K31</f>
+        <v>-150.9</v>
       </c>
       <c r="M26" s="12">
-        <f>S3!L31</f>
-        <v>100.2</v>
+        <f>S4!L31</f>
+        <v>-155.9</v>
       </c>
       <c r="N26" s="12">
-        <f>S3!M31</f>
-        <v>95.2</v>
+        <f>S4!M31</f>
+        <v>-160.9</v>
       </c>
       <c r="O26" s="12">
-        <f>S3!N31</f>
-        <v>90.2</v>
+        <f>S4!N31</f>
+        <v>-165.9</v>
       </c>
       <c r="P26" s="12">
-        <f>S3!O31</f>
-        <v>85.2</v>
+        <f>S4!O31</f>
+        <v>-170.9</v>
       </c>
       <c r="Q26" s="12">
-        <f>S3!P31</f>
-        <v>80.2</v>
+        <f>S4!P31</f>
+        <v>-175.9</v>
       </c>
       <c r="R26" s="12">
-        <f>S3!Q31</f>
-        <v>75.2</v>
+        <f>S4!Q31</f>
+        <v>-180.9</v>
       </c>
       <c r="S26" s="12">
-        <f>S3!R31</f>
-        <v>70.2</v>
+        <f>S4!R31</f>
+        <v>-185.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>S4 基本＋ワイズ＋エース</t>
+          <t>S5 全件（＋日本経営C＋セレサ）</t>
         </is>
       </c>
       <c r="D27" s="12">
-        <f>S4!C31</f>
+        <f>S5!C31</f>
         <v>329.3</v>
       </c>
       <c r="E27" s="12">
-        <f>S4!D31</f>
-        <v>293.75</v>
+        <f>S5!D31</f>
+        <v>292.65</v>
       </c>
       <c r="F27" s="12">
-        <f>S4!E31</f>
-        <v>94.95</v>
+        <f>S5!E31</f>
+        <v>88.85</v>
       </c>
       <c r="G27" s="12">
-        <f>S4!F31</f>
-        <v>6.2</v>
+        <f>S5!F31</f>
+        <v>-118.65</v>
       </c>
       <c r="H27" s="12">
-        <f>S4!G31</f>
-        <v>1.2</v>
+        <f>S5!G31</f>
+        <v>-211.4</v>
       </c>
       <c r="I27" s="12">
-        <f>S4!H31</f>
-        <v>-3.8</v>
+        <f>S5!H31</f>
+        <v>-218.5</v>
       </c>
       <c r="J27" s="12">
-        <f>S4!I31</f>
-        <v>-20.8</v>
+        <f>S5!I31</f>
+        <v>-291.0</v>
       </c>
       <c r="K27" s="12">
-        <f>S4!J31</f>
-        <v>-25.8</v>
+        <f>S5!J31</f>
+        <v>-296.0</v>
       </c>
       <c r="L27" s="12">
-        <f>S4!K31</f>
-        <v>-30.8</v>
+        <f>S5!K31</f>
+        <v>-301.0</v>
       </c>
       <c r="M27" s="12">
-        <f>S4!L31</f>
-        <v>-35.8</v>
+        <f>S5!L31</f>
+        <v>-306.0</v>
       </c>
       <c r="N27" s="12">
-        <f>S4!M31</f>
-        <v>-40.8</v>
+        <f>S5!M31</f>
+        <v>-311.0</v>
       </c>
       <c r="O27" s="12">
-        <f>S4!N31</f>
-        <v>-45.8</v>
+        <f>S5!N31</f>
+        <v>-316.0</v>
       </c>
       <c r="P27" s="12">
-        <f>S4!O31</f>
-        <v>-50.8</v>
+        <f>S5!O31</f>
+        <v>-321.0</v>
       </c>
       <c r="Q27" s="12">
-        <f>S4!P31</f>
-        <v>-55.8</v>
+        <f>S5!P31</f>
+        <v>-326.0</v>
       </c>
       <c r="R27" s="12">
-        <f>S4!Q31</f>
-        <v>-60.8</v>
+        <f>S5!Q31</f>
+        <v>-331.0</v>
       </c>
       <c r="S27" s="12">
-        <f>S4!R31</f>
-        <v>-65.8</v>
+        <f>S5!R31</f>
+        <v>-336.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>S5 全件（＋日本経営C＋セレサ）</t>
+          <t>安全水準</t>
         </is>
       </c>
       <c r="D28" s="12">
-        <f>S5!C31</f>
-        <v>329.3</v>
-      </c>
-      <c r="E28" s="12">
-        <f>S5!D31</f>
-        <v>293.75</v>
-      </c>
-      <c r="F28" s="12">
-        <f>S5!E31</f>
-        <v>94.95</v>
-      </c>
-      <c r="G28" s="12">
-        <f>S5!F31</f>
-        <v>1.45</v>
-      </c>
-      <c r="H28" s="12">
-        <f>S5!G31</f>
-        <v>-91.3</v>
-      </c>
-      <c r="I28" s="12">
-        <f>S5!H31</f>
-        <v>-98.4</v>
-      </c>
-      <c r="J28" s="12">
-        <f>S5!I31</f>
-        <v>-170.9</v>
-      </c>
-      <c r="K28" s="12">
-        <f>S5!J31</f>
-        <v>-175.9</v>
-      </c>
-      <c r="L28" s="12">
-        <f>S5!K31</f>
-        <v>-180.9</v>
-      </c>
-      <c r="M28" s="12">
-        <f>S5!L31</f>
-        <v>-185.9</v>
-      </c>
-      <c r="N28" s="12">
-        <f>S5!M31</f>
-        <v>-190.9</v>
-      </c>
-      <c r="O28" s="12">
-        <f>S5!N31</f>
-        <v>-195.9</v>
-      </c>
-      <c r="P28" s="12">
-        <f>S5!O31</f>
-        <v>-200.9</v>
-      </c>
-      <c r="Q28" s="12">
-        <f>S5!P31</f>
-        <v>-205.9</v>
-      </c>
-      <c r="R28" s="12">
-        <f>S5!Q31</f>
-        <v>-210.9</v>
-      </c>
-      <c r="S28" s="12">
-        <f>S5!R31</f>
-        <v>-215.9</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>S6 全件＋シルバーメディカル</t>
-        </is>
-      </c>
-      <c r="D29" s="12">
-        <f>S6!C31</f>
-        <v>329.3</v>
-      </c>
-      <c r="E29" s="12">
-        <f>S6!D31</f>
-        <v>292.65</v>
-      </c>
-      <c r="F29" s="12">
-        <f>S6!E31</f>
-        <v>88.85</v>
-      </c>
-      <c r="G29" s="12">
-        <f>S6!F31</f>
-        <v>-118.65</v>
-      </c>
-      <c r="H29" s="12">
-        <f>S6!G31</f>
-        <v>-211.4</v>
-      </c>
-      <c r="I29" s="12">
-        <f>S6!H31</f>
-        <v>-218.5</v>
-      </c>
-      <c r="J29" s="12">
-        <f>S6!I31</f>
-        <v>-291.0</v>
-      </c>
-      <c r="K29" s="12">
-        <f>S6!J31</f>
-        <v>-296.0</v>
-      </c>
-      <c r="L29" s="12">
-        <f>S6!K31</f>
-        <v>-301.0</v>
-      </c>
-      <c r="M29" s="12">
-        <f>S6!L31</f>
-        <v>-306.0</v>
-      </c>
-      <c r="N29" s="12">
-        <f>S6!M31</f>
-        <v>-311.0</v>
-      </c>
-      <c r="O29" s="12">
-        <f>S6!N31</f>
-        <v>-316.0</v>
-      </c>
-      <c r="P29" s="12">
-        <f>S6!O31</f>
-        <v>-321.0</v>
-      </c>
-      <c r="Q29" s="12">
-        <f>S6!P31</f>
-        <v>-326.0</v>
-      </c>
-      <c r="R29" s="12">
-        <f>S6!Q31</f>
-        <v>-331.0</v>
-      </c>
-      <c r="S29" s="12">
-        <f>S6!R31</f>
-        <v>-336.0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>安全水準</t>
-        </is>
-      </c>
-      <c r="D30" s="12">
         <f>前提!$B$4</f>
         <v>100.0</v>
       </c>
-      <c r="E30" s="12">
+      <c r="E28" s="12">
         <f>前提!$B$4</f>
         <v>100.0</v>
       </c>
-      <c r="F30" s="12">
+      <c r="F28" s="12">
         <f>前提!$B$4</f>
         <v>100.0</v>
       </c>
-      <c r="G30" s="12">
+      <c r="G28" s="12">
         <f>前提!$B$4</f>
         <v>100.0</v>
       </c>
-      <c r="H30" s="12">
+      <c r="H28" s="12">
         <f>前提!$B$4</f>
         <v>100.0</v>
       </c>
-      <c r="I30" s="12">
+      <c r="I28" s="12">
         <f>前提!$B$4</f>
         <v>100.0</v>
       </c>
-      <c r="J30" s="12">
+      <c r="J28" s="12">
         <f>前提!$B$4</f>
         <v>100.0</v>
       </c>
-      <c r="K30" s="12">
+      <c r="K28" s="12">
         <f>前提!$B$4</f>
         <v>100.0</v>
       </c>
-      <c r="L30" s="12">
+      <c r="L28" s="12">
         <f>前提!$B$4</f>
         <v>100.0</v>
       </c>
-      <c r="M30" s="12">
+      <c r="M28" s="12">
         <f>前提!$B$4</f>
         <v>100.0</v>
       </c>
-      <c r="N30" s="12">
+      <c r="N28" s="12">
         <f>前提!$B$4</f>
         <v>100.0</v>
       </c>
-      <c r="O30" s="12">
+      <c r="O28" s="12">
         <f>前提!$B$4</f>
         <v>100.0</v>
       </c>
-      <c r="P30" s="12">
+      <c r="P28" s="12">
         <f>前提!$B$4</f>
         <v>100.0</v>
       </c>
-      <c r="Q30" s="12">
+      <c r="Q28" s="12">
         <f>前提!$B$4</f>
         <v>100.0</v>
       </c>
-      <c r="R30" s="12">
+      <c r="R28" s="12">
         <f>前提!$B$4</f>
         <v>100.0</v>
       </c>
-      <c r="S30" s="12">
+      <c r="S28" s="12">
         <f>前提!$B$4</f>
         <v>100.0</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>必要調達額（累計不足額）の月次推移</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>シナリオ</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr"/>
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>2026/9</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>2026/10</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>2026/11</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>2026/12</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>2027/1</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>2027/2</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>2027/3</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>2027/4</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>2027/5</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>2027/6</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>2027/7</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>2027/8</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>2027/9</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>2027/10</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>2027/11</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t>2027/12</t>
+        </is>
+      </c>
+    </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>必要調達額（累計不足額）の月次推移</t>
-        </is>
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>S1 基本（確定5件）</t>
+        </is>
+      </c>
+      <c r="D32" s="12">
+        <f>S1!C33</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="12">
+        <f>S1!D33</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="12">
+        <f>S1!E33</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="12">
+        <f>S1!F33</f>
+        <v>3.4</v>
+      </c>
+      <c r="H32" s="12">
+        <f>S1!G33</f>
+        <v>8.4</v>
+      </c>
+      <c r="I32" s="12">
+        <f>S1!H33</f>
+        <v>13.4</v>
+      </c>
+      <c r="J32" s="12">
+        <f>S1!I33</f>
+        <v>30.4</v>
+      </c>
+      <c r="K32" s="12">
+        <f>S1!J33</f>
+        <v>35.4</v>
+      </c>
+      <c r="L32" s="12">
+        <f>S1!K33</f>
+        <v>40.4</v>
+      </c>
+      <c r="M32" s="12">
+        <f>S1!L33</f>
+        <v>45.4</v>
+      </c>
+      <c r="N32" s="12">
+        <f>S1!M33</f>
+        <v>50.4</v>
+      </c>
+      <c r="O32" s="12">
+        <f>S1!N33</f>
+        <v>55.4</v>
+      </c>
+      <c r="P32" s="12">
+        <f>S1!O33</f>
+        <v>60.4</v>
+      </c>
+      <c r="Q32" s="12">
+        <f>S1!P33</f>
+        <v>65.4</v>
+      </c>
+      <c r="R32" s="12">
+        <f>S1!Q33</f>
+        <v>70.4</v>
+      </c>
+      <c r="S32" s="12">
+        <f>S1!R33</f>
+        <v>75.4</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>シナリオ</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr"/>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>2026/9</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>2026/10</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>2026/11</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>2026/12</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>2027/1</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>2027/2</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>2027/3</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>2027/4</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t>2027/5</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>2027/6</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t>2027/7</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>2027/8</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t>2027/9</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t>2027/10</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t>2027/11</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t>2027/12</t>
-        </is>
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>S2 基本＋ワイズケア</t>
+        </is>
+      </c>
+      <c r="D33" s="12">
+        <f>S2!C33</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="12">
+        <f>S2!D33</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="12">
+        <f>S2!E33</f>
+        <v>6.4</v>
+      </c>
+      <c r="G33" s="12">
+        <f>S2!F33</f>
+        <v>139.4</v>
+      </c>
+      <c r="H33" s="12">
+        <f>S2!G33</f>
+        <v>144.4</v>
+      </c>
+      <c r="I33" s="12">
+        <f>S2!H33</f>
+        <v>149.4</v>
+      </c>
+      <c r="J33" s="12">
+        <f>S2!I33</f>
+        <v>166.4</v>
+      </c>
+      <c r="K33" s="12">
+        <f>S2!J33</f>
+        <v>171.4</v>
+      </c>
+      <c r="L33" s="12">
+        <f>S2!K33</f>
+        <v>176.4</v>
+      </c>
+      <c r="M33" s="12">
+        <f>S2!L33</f>
+        <v>181.4</v>
+      </c>
+      <c r="N33" s="12">
+        <f>S2!M33</f>
+        <v>186.4</v>
+      </c>
+      <c r="O33" s="12">
+        <f>S2!N33</f>
+        <v>191.4</v>
+      </c>
+      <c r="P33" s="12">
+        <f>S2!O33</f>
+        <v>196.4</v>
+      </c>
+      <c r="Q33" s="12">
+        <f>S2!P33</f>
+        <v>201.4</v>
+      </c>
+      <c r="R33" s="12">
+        <f>S2!Q33</f>
+        <v>206.4</v>
+      </c>
+      <c r="S33" s="12">
+        <f>S2!R33</f>
+        <v>211.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>S1 基本（確定4件）</t>
+          <t>S3 基本＋エーステイスト</t>
         </is>
       </c>
       <c r="D34" s="12">
-        <f>S1!C33</f>
+        <f>S3!C33</f>
         <v>0</v>
       </c>
       <c r="E34" s="12">
-        <f>S1!D33</f>
+        <f>S3!D33</f>
         <v>0</v>
       </c>
       <c r="F34" s="12">
-        <f>S1!E33</f>
+        <f>S3!E33</f>
         <v>0</v>
       </c>
       <c r="G34" s="12">
-        <f>S1!F33</f>
-        <v>0</v>
+        <f>S3!F33</f>
+        <v>77.9</v>
       </c>
       <c r="H34" s="12">
-        <f>S1!G33</f>
-        <v>0</v>
+        <f>S3!G33</f>
+        <v>82.9</v>
       </c>
       <c r="I34" s="12">
-        <f>S1!H33</f>
-        <v>0</v>
+        <f>S3!H33</f>
+        <v>87.9</v>
       </c>
       <c r="J34" s="12">
-        <f>S1!I33</f>
-        <v>0</v>
+        <f>S3!I33</f>
+        <v>104.9</v>
       </c>
       <c r="K34" s="12">
-        <f>S1!J33</f>
-        <v>0</v>
+        <f>S3!J33</f>
+        <v>109.9</v>
       </c>
       <c r="L34" s="12">
-        <f>S1!K33</f>
-        <v>0</v>
+        <f>S3!K33</f>
+        <v>114.9</v>
       </c>
       <c r="M34" s="12">
-        <f>S1!L33</f>
-        <v>0</v>
+        <f>S3!L33</f>
+        <v>119.9</v>
       </c>
       <c r="N34" s="12">
-        <f>S1!M33</f>
-        <v>0</v>
+        <f>S3!M33</f>
+        <v>124.9</v>
       </c>
       <c r="O34" s="12">
-        <f>S1!N33</f>
-        <v>0</v>
+        <f>S3!N33</f>
+        <v>129.9</v>
       </c>
       <c r="P34" s="12">
-        <f>S1!O33</f>
-        <v>0</v>
+        <f>S3!O33</f>
+        <v>134.9</v>
       </c>
       <c r="Q34" s="12">
-        <f>S1!P33</f>
-        <v>0</v>
+        <f>S3!P33</f>
+        <v>139.9</v>
       </c>
       <c r="R34" s="12">
-        <f>S1!Q33</f>
-        <v>0</v>
+        <f>S3!Q33</f>
+        <v>144.9</v>
       </c>
       <c r="S34" s="12">
-        <f>S1!R33</f>
-        <v>0</v>
+        <f>S3!R33</f>
+        <v>149.9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>S2 基本＋ワイズケア</t>
+          <t>S4 基本＋ワイズ＋エース</t>
         </is>
       </c>
       <c r="D35" s="12">
-        <f>S2!C33</f>
+        <f>S4!C33</f>
         <v>0</v>
       </c>
       <c r="E35" s="12">
-        <f>S2!D33</f>
+        <f>S4!D33</f>
         <v>0</v>
       </c>
       <c r="F35" s="12">
-        <f>S2!E33</f>
-        <v>0.3</v>
+        <f>S4!E33</f>
+        <v>11.15</v>
       </c>
       <c r="G35" s="12">
-        <f>S2!F33</f>
-        <v>19.3</v>
+        <f>S4!F33</f>
+        <v>213.9</v>
       </c>
       <c r="H35" s="12">
-        <f>S2!G33</f>
-        <v>24.3</v>
+        <f>S4!G33</f>
+        <v>218.9</v>
       </c>
       <c r="I35" s="12">
-        <f>S2!H33</f>
-        <v>29.3</v>
+        <f>S4!H33</f>
+        <v>223.9</v>
       </c>
       <c r="J35" s="12">
-        <f>S2!I33</f>
-        <v>46.3</v>
+        <f>S4!I33</f>
+        <v>240.9</v>
       </c>
       <c r="K35" s="12">
-        <f>S2!J33</f>
-        <v>51.3</v>
+        <f>S4!J33</f>
+        <v>245.9</v>
       </c>
       <c r="L35" s="12">
-        <f>S2!K33</f>
-        <v>56.3</v>
+        <f>S4!K33</f>
+        <v>250.9</v>
       </c>
       <c r="M35" s="12">
-        <f>S2!L33</f>
-        <v>61.3</v>
+        <f>S4!L33</f>
+        <v>255.9</v>
       </c>
       <c r="N35" s="12">
-        <f>S2!M33</f>
-        <v>66.3</v>
+        <f>S4!M33</f>
+        <v>260.9</v>
       </c>
       <c r="O35" s="12">
-        <f>S2!N33</f>
-        <v>71.3</v>
+        <f>S4!N33</f>
+        <v>265.9</v>
       </c>
       <c r="P35" s="12">
-        <f>S2!O33</f>
-        <v>76.3</v>
+        <f>S4!O33</f>
+        <v>270.9</v>
       </c>
       <c r="Q35" s="12">
-        <f>S2!P33</f>
-        <v>81.3</v>
+        <f>S4!P33</f>
+        <v>275.9</v>
       </c>
       <c r="R35" s="12">
-        <f>S2!Q33</f>
-        <v>86.3</v>
+        <f>S4!Q33</f>
+        <v>280.9</v>
       </c>
       <c r="S35" s="12">
-        <f>S2!R33</f>
-        <v>91.3</v>
+        <f>S4!R33</f>
+        <v>285.9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>S3 基本＋エーステイスト</t>
+          <t>S5 全件（＋日本経営C＋セレサ）</t>
         </is>
       </c>
       <c r="D36" s="12">
-        <f>S3!C33</f>
+        <f>S5!C33</f>
         <v>0</v>
       </c>
       <c r="E36" s="12">
-        <f>S3!D33</f>
+        <f>S5!D33</f>
         <v>0</v>
       </c>
       <c r="F36" s="12">
-        <f>S3!E33</f>
-        <v>0</v>
+        <f>S5!E33</f>
+        <v>11.15</v>
       </c>
       <c r="G36" s="12">
-        <f>S3!F33</f>
-        <v>0</v>
+        <f>S5!F33</f>
+        <v>218.65</v>
       </c>
       <c r="H36" s="12">
-        <f>S3!G33</f>
-        <v>0</v>
+        <f>S5!G33</f>
+        <v>311.4</v>
       </c>
       <c r="I36" s="12">
-        <f>S3!H33</f>
-        <v>0</v>
+        <f>S5!H33</f>
+        <v>318.5</v>
       </c>
       <c r="J36" s="12">
-        <f>S3!I33</f>
-        <v>0</v>
+        <f>S5!I33</f>
+        <v>391.0</v>
       </c>
       <c r="K36" s="12">
-        <f>S3!J33</f>
-        <v>0</v>
+        <f>S5!J33</f>
+        <v>396.0</v>
       </c>
       <c r="L36" s="12">
-        <f>S3!K33</f>
-        <v>0</v>
+        <f>S5!K33</f>
+        <v>401.0</v>
       </c>
       <c r="M36" s="12">
-        <f>S3!L33</f>
-        <v>0</v>
+        <f>S5!L33</f>
+        <v>406.0</v>
       </c>
       <c r="N36" s="12">
-        <f>S3!M33</f>
-        <v>4.8</v>
+        <f>S5!M33</f>
+        <v>411.0</v>
       </c>
       <c r="O36" s="12">
-        <f>S3!N33</f>
-        <v>9.8</v>
+        <f>S5!N33</f>
+        <v>416.0</v>
       </c>
       <c r="P36" s="12">
-        <f>S3!O33</f>
-        <v>14.8</v>
+        <f>S5!O33</f>
+        <v>421.0</v>
       </c>
       <c r="Q36" s="12">
-        <f>S3!P33</f>
-        <v>19.8</v>
+        <f>S5!P33</f>
+        <v>426.0</v>
       </c>
       <c r="R36" s="12">
-        <f>S3!Q33</f>
-        <v>24.8</v>
+        <f>S5!Q33</f>
+        <v>431.0</v>
       </c>
       <c r="S36" s="12">
-        <f>S3!R33</f>
-        <v>29.8</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>S4 基本＋ワイズ＋エース</t>
-        </is>
-      </c>
-      <c r="D37" s="12">
-        <f>S4!C33</f>
-        <v>0</v>
-      </c>
-      <c r="E37" s="12">
-        <f>S4!D33</f>
-        <v>0</v>
-      </c>
-      <c r="F37" s="12">
-        <f>S4!E33</f>
-        <v>5.05</v>
-      </c>
-      <c r="G37" s="12">
-        <f>S4!F33</f>
-        <v>93.8</v>
-      </c>
-      <c r="H37" s="12">
-        <f>S4!G33</f>
-        <v>98.8</v>
-      </c>
-      <c r="I37" s="12">
-        <f>S4!H33</f>
-        <v>103.8</v>
-      </c>
-      <c r="J37" s="12">
-        <f>S4!I33</f>
-        <v>120.8</v>
-      </c>
-      <c r="K37" s="12">
-        <f>S4!J33</f>
-        <v>125.8</v>
-      </c>
-      <c r="L37" s="12">
-        <f>S4!K33</f>
-        <v>130.8</v>
-      </c>
-      <c r="M37" s="12">
-        <f>S4!L33</f>
-        <v>135.8</v>
-      </c>
-      <c r="N37" s="12">
-        <f>S4!M33</f>
-        <v>140.8</v>
-      </c>
-      <c r="O37" s="12">
-        <f>S4!N33</f>
-        <v>145.8</v>
-      </c>
-      <c r="P37" s="12">
-        <f>S4!O33</f>
-        <v>150.8</v>
-      </c>
-      <c r="Q37" s="12">
-        <f>S4!P33</f>
-        <v>155.8</v>
-      </c>
-      <c r="R37" s="12">
-        <f>S4!Q33</f>
-        <v>160.8</v>
-      </c>
-      <c r="S37" s="12">
-        <f>S4!R33</f>
-        <v>165.8</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>S5 全件（＋日本経営C＋セレサ）</t>
-        </is>
-      </c>
-      <c r="D38" s="12">
-        <f>S5!C33</f>
-        <v>0</v>
-      </c>
-      <c r="E38" s="12">
-        <f>S5!D33</f>
-        <v>0</v>
-      </c>
-      <c r="F38" s="12">
-        <f>S5!E33</f>
-        <v>5.05</v>
-      </c>
-      <c r="G38" s="12">
-        <f>S5!F33</f>
-        <v>98.55</v>
-      </c>
-      <c r="H38" s="12">
-        <f>S5!G33</f>
-        <v>191.3</v>
-      </c>
-      <c r="I38" s="12">
-        <f>S5!H33</f>
-        <v>198.4</v>
-      </c>
-      <c r="J38" s="12">
-        <f>S5!I33</f>
-        <v>270.9</v>
-      </c>
-      <c r="K38" s="12">
-        <f>S5!J33</f>
-        <v>275.9</v>
-      </c>
-      <c r="L38" s="12">
-        <f>S5!K33</f>
-        <v>280.9</v>
-      </c>
-      <c r="M38" s="12">
-        <f>S5!L33</f>
-        <v>285.9</v>
-      </c>
-      <c r="N38" s="12">
-        <f>S5!M33</f>
-        <v>290.9</v>
-      </c>
-      <c r="O38" s="12">
-        <f>S5!N33</f>
-        <v>295.9</v>
-      </c>
-      <c r="P38" s="12">
-        <f>S5!O33</f>
-        <v>300.9</v>
-      </c>
-      <c r="Q38" s="12">
-        <f>S5!P33</f>
-        <v>305.9</v>
-      </c>
-      <c r="R38" s="12">
-        <f>S5!Q33</f>
-        <v>310.9</v>
-      </c>
-      <c r="S38" s="12">
         <f>S5!R33</f>
-        <v>315.9</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>S6 全件＋シルバーメディカル</t>
-        </is>
-      </c>
-      <c r="D39" s="12">
-        <f>S6!C33</f>
-        <v>0</v>
-      </c>
-      <c r="E39" s="12">
-        <f>S6!D33</f>
-        <v>0</v>
-      </c>
-      <c r="F39" s="12">
-        <f>S6!E33</f>
-        <v>11.15</v>
-      </c>
-      <c r="G39" s="12">
-        <f>S6!F33</f>
-        <v>218.65</v>
-      </c>
-      <c r="H39" s="12">
-        <f>S6!G33</f>
-        <v>311.4</v>
-      </c>
-      <c r="I39" s="12">
-        <f>S6!H33</f>
-        <v>318.5</v>
-      </c>
-      <c r="J39" s="12">
-        <f>S6!I33</f>
-        <v>391.0</v>
-      </c>
-      <c r="K39" s="12">
-        <f>S6!J33</f>
-        <v>396.0</v>
-      </c>
-      <c r="L39" s="12">
-        <f>S6!K33</f>
-        <v>401.0</v>
-      </c>
-      <c r="M39" s="12">
-        <f>S6!L33</f>
-        <v>406.0</v>
-      </c>
-      <c r="N39" s="12">
-        <f>S6!M33</f>
-        <v>411.0</v>
-      </c>
-      <c r="O39" s="12">
-        <f>S6!N33</f>
-        <v>416.0</v>
-      </c>
-      <c r="P39" s="12">
-        <f>S6!O33</f>
-        <v>421.0</v>
-      </c>
-      <c r="Q39" s="12">
-        <f>S6!P33</f>
-        <v>426.0</v>
-      </c>
-      <c r="R39" s="12">
-        <f>S6!Q33</f>
-        <v>431.0</v>
-      </c>
-      <c r="S39" s="12">
-        <f>S6!R33</f>
         <v>436.0</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>売上36億円への道筋 — 戦略別モンテカルロ結果（2万回・手出し最小化ベース・値貼付。詳細はHTML資料 第8章）</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>戦略</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>追う案件数</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>36億円到達確率（2027/12）</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>期待売上（年換算）</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>売上P50</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>売上P80</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>必要資金P50</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>必要資金P80</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>到達時の必要資金（中央値）</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>全件成約時の売上</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>A 確定5件＋中型積み上げ（大型なし）</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C61" s="13" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="D61" s="10" t="n">
+        <v>3370</v>
+      </c>
+      <c r="E61" s="10" t="n">
+        <v>3372</v>
+      </c>
+      <c r="F61" s="10" t="n">
+        <v>3768</v>
+      </c>
+      <c r="G61" s="10" t="n">
+        <v>475</v>
+      </c>
+      <c r="H61" s="10" t="n">
+        <v>587</v>
+      </c>
+      <c r="I61" s="10" t="n">
+        <v>612</v>
+      </c>
+      <c r="J61" s="10" t="n">
+        <v>4600</v>
+      </c>
+    </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>売上36億円への道筋 — 戦略別モンテカルロ結果（2万回・手出し最小化ベース・値貼付。詳細はHTML資料 第8章）</t>
-        </is>
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>B 中型＋ライブアシスト</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C62" s="13" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="D62" s="10" t="n">
+        <v>3521</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>3510</v>
+      </c>
+      <c r="F62" s="10" t="n">
+        <v>3929</v>
+      </c>
+      <c r="G62" s="10" t="n">
+        <v>526</v>
+      </c>
+      <c r="H62" s="10" t="n">
+        <v>648</v>
+      </c>
+      <c r="I62" s="10" t="n">
+        <v>640</v>
+      </c>
+      <c r="J62" s="10" t="n">
+        <v>4999</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>戦略</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>追う案件数</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>36億円到達確率（2027/12）</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>期待売上（年換算）</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>売上P50</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>売上P80</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>必要資金P50</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>必要資金P80</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>到達時の必要資金（中央値）</t>
-        </is>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>全件成約時の売上</t>
-        </is>
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>C 中型＋プラスディー</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C63" s="13" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="D63" s="10" t="n">
+        <v>3506</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>3320</v>
+      </c>
+      <c r="F63" s="10" t="n">
+        <v>4307</v>
+      </c>
+      <c r="G63" s="10" t="n">
+        <v>520</v>
+      </c>
+      <c r="H63" s="10" t="n">
+        <v>754</v>
+      </c>
+      <c r="I63" s="10" t="n">
+        <v>754</v>
+      </c>
+      <c r="J63" s="10" t="n">
+        <v>5225</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>A 中型積み上げ（大型なし）</t>
+          <t>D 中型＋ヒナ資本提携＋ライブアシスト</t>
         </is>
       </c>
       <c r="B64" s="11" t="n">
         <v>11</v>
       </c>
       <c r="C64" s="13" t="n">
-        <v>0.013</v>
+        <v>0.498</v>
       </c>
       <c r="D64" s="10" t="n">
-        <v>2598</v>
+        <v>3693</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>2613</v>
+        <v>3599</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>2993</v>
+        <v>4253</v>
       </c>
       <c r="G64" s="10" t="n">
-        <v>356</v>
+        <v>544</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>470</v>
+        <v>687</v>
       </c>
       <c r="I64" s="10" t="n">
-        <v>633</v>
+        <v>665</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>3823</v>
+        <v>6057</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>B 中型＋シルバーメディカル</t>
+          <t>F 中型＋プラスディー＋ヒナ＋ライブアシスト</t>
         </is>
       </c>
       <c r="B65" s="11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C65" s="13" t="n">
-        <v>0.291</v>
+        <v>0.677</v>
       </c>
       <c r="D65" s="10" t="n">
-        <v>3361</v>
+        <v>4194</v>
       </c>
       <c r="E65" s="10" t="n">
-        <v>3370</v>
+        <v>4056</v>
       </c>
       <c r="F65" s="10" t="n">
-        <v>3770</v>
+        <v>5043</v>
       </c>
       <c r="G65" s="10" t="n">
-        <v>473</v>
+        <v>653</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>586</v>
+        <v>890</v>
       </c>
       <c r="I65" s="10" t="n">
-        <v>612</v>
+        <v>763</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>4530</v>
+        <v>7686</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>C 中型＋大型2件（シルバー＋プラスディー）</t>
+          <t>E 全方位（LOI以上＋本格検討すべて）</t>
         </is>
       </c>
       <c r="B66" s="11" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C66" s="13" t="n">
-        <v>0.373</v>
+        <v>0.78</v>
       </c>
       <c r="D66" s="10" t="n">
-        <v>3517</v>
+        <v>4434</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>3320</v>
+        <v>4340</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>4307</v>
+        <v>5291</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>520</v>
+        <v>837</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>754</v>
+        <v>1099</v>
       </c>
       <c r="I66" s="10" t="n">
-        <v>754</v>
+        <v>920</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>5225</v>
+        <v>9210</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>D 中型＋ヒナ資本提携＋ライブアシスト</t>
-        </is>
-      </c>
-      <c r="B67" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C67" s="13" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="D67" s="10" t="n">
-        <v>2923</v>
-      </c>
-      <c r="E67" s="10" t="n">
-        <v>2841</v>
-      </c>
-      <c r="F67" s="10" t="n">
-        <v>3498</v>
-      </c>
-      <c r="G67" s="10" t="n">
-        <v>426</v>
-      </c>
-      <c r="H67" s="10" t="n">
-        <v>567</v>
-      </c>
-      <c r="I67" s="10" t="n">
-        <v>672</v>
-      </c>
-      <c r="J67" s="10" t="n">
-        <v>5280</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>F 中型＋大型3件（シルバー＋プラスディー＋ヒナ）＋ライブアシスト</t>
-        </is>
-      </c>
-      <c r="B68" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="C68" s="13" t="n">
-        <v>0.674</v>
-      </c>
-      <c r="D68" s="10" t="n">
-        <v>4194</v>
-      </c>
-      <c r="E68" s="10" t="n">
-        <v>4051</v>
-      </c>
-      <c r="F68" s="10" t="n">
-        <v>5050</v>
-      </c>
-      <c r="G68" s="10" t="n">
-        <v>653</v>
-      </c>
-      <c r="H68" s="10" t="n">
-        <v>892</v>
-      </c>
-      <c r="I68" s="10" t="n">
-        <v>763</v>
-      </c>
-      <c r="J68" s="10" t="n">
-        <v>7686</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>E 全方位（LOI以上＋本格検討すべて）</t>
-        </is>
-      </c>
-      <c r="B69" s="11" t="n">
-        <v>22</v>
-      </c>
-      <c r="C69" s="13" t="n">
-        <v>0.774</v>
-      </c>
-      <c r="D69" s="10" t="n">
-        <v>4433</v>
-      </c>
-      <c r="E69" s="10" t="n">
-        <v>4325</v>
-      </c>
-      <c r="F69" s="10" t="n">
-        <v>5304</v>
-      </c>
-      <c r="G69" s="10" t="n">
-        <v>831</v>
-      </c>
-      <c r="H69" s="10" t="n">
-        <v>1103</v>
-      </c>
-      <c r="I69" s="10" t="n">
-        <v>918</v>
-      </c>
-      <c r="J69" s="10" t="n">
-        <v>9210</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>期限を2028/6に延ばした場合（戦略F）：到達確率 91%、必要資金P50 812</t>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>期限を2028/6に延ばした場合（戦略F）：到達確率 91%、必要資金P50 814</t>
         </is>
       </c>
     </row>
@@ -3041,1681 +2768,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:S51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
-    <col width="9" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>S6 全件＋シルバーメディカル — HD単体 月次キャッシュ推移（百万円）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>実行フラグ（1＝実行、0＝見送り）とモード（現行／最小化）を変えると全体が再計算されます。青字＝入力値</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>モード</t>
-        </is>
-      </c>
-      <c r="B3" s="22" t="inlineStr">
-        <is>
-          <t>最小化</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>← 「現行」または「最小化」</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>案件</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>実行フラグ</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>HT100%化</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>メディプロ</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>ヒューマンアイ</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>クレッシェンド</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>ワイズケア</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>エーステイスト</t>
-        </is>
-      </c>
-      <c r="B11" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>日本経営センター</t>
-        </is>
-      </c>
-      <c r="B12" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>セレサ</t>
-        </is>
-      </c>
-      <c r="B13" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>シルバーメディカル</t>
-        </is>
-      </c>
-      <c r="B14" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr"/>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>2026/9</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>2026/10</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>2026/11</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>2026/12</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>2027/1</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>2027/2</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>2027/3</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>2027/4</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>2027/5</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>2027/6</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>2027/7</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>2027/8</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>2027/9</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t>2027/10</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t>2027/11</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
-        <is>
-          <t>2027/12</t>
-        </is>
-      </c>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>期首現預金</t>
-        </is>
-      </c>
-      <c r="C18" s="20">
-        <f>前提!$B$3</f>
-        <v>366.3</v>
-      </c>
-      <c r="D18" s="20">
-        <f>C31</f>
-        <v>329.3</v>
-      </c>
-      <c r="E18" s="20">
-        <f>D31</f>
-        <v>292.65</v>
-      </c>
-      <c r="F18" s="20">
-        <f>E31</f>
-        <v>88.85</v>
-      </c>
-      <c r="G18" s="20">
-        <f>F31</f>
-        <v>-118.65</v>
-      </c>
-      <c r="H18" s="20">
-        <f>G31</f>
-        <v>-211.4</v>
-      </c>
-      <c r="I18" s="20">
-        <f>H31</f>
-        <v>-218.5</v>
-      </c>
-      <c r="J18" s="20">
-        <f>I31</f>
-        <v>-291.0</v>
-      </c>
-      <c r="K18" s="20">
-        <f>J31</f>
-        <v>-296.0</v>
-      </c>
-      <c r="L18" s="20">
-        <f>K31</f>
-        <v>-301.0</v>
-      </c>
-      <c r="M18" s="20">
-        <f>L31</f>
-        <v>-306.0</v>
-      </c>
-      <c r="N18" s="20">
-        <f>M31</f>
-        <v>-311.0</v>
-      </c>
-      <c r="O18" s="20">
-        <f>N31</f>
-        <v>-316.0</v>
-      </c>
-      <c r="P18" s="20">
-        <f>O31</f>
-        <v>-321.0</v>
-      </c>
-      <c r="Q18" s="20">
-        <f>P31</f>
-        <v>-326.0</v>
-      </c>
-      <c r="R18" s="20">
-        <f>Q31</f>
-        <v>-331.0</v>
-      </c>
-      <c r="S18" s="20" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>HD運営費</t>
-        </is>
-      </c>
-      <c r="C19" s="23">
-        <f>前提!D$11</f>
-        <v>-7</v>
-      </c>
-      <c r="D19" s="23">
-        <f>前提!E$11</f>
-        <v>-7</v>
-      </c>
-      <c r="E19" s="23">
-        <f>前提!F$11</f>
-        <v>-7</v>
-      </c>
-      <c r="F19" s="23">
-        <f>前提!G$11</f>
-        <v>-7</v>
-      </c>
-      <c r="G19" s="23">
-        <f>前提!H$11</f>
-        <v>-5</v>
-      </c>
-      <c r="H19" s="23">
-        <f>前提!I$11</f>
-        <v>-5</v>
-      </c>
-      <c r="I19" s="23">
-        <f>前提!J$11</f>
-        <v>-5</v>
-      </c>
-      <c r="J19" s="23">
-        <f>前提!K$11</f>
-        <v>-5</v>
-      </c>
-      <c r="K19" s="23">
-        <f>前提!L$11</f>
-        <v>-5</v>
-      </c>
-      <c r="L19" s="23">
-        <f>前提!M$11</f>
-        <v>-5</v>
-      </c>
-      <c r="M19" s="23">
-        <f>前提!N$11</f>
-        <v>-5</v>
-      </c>
-      <c r="N19" s="23">
-        <f>前提!O$11</f>
-        <v>-5</v>
-      </c>
-      <c r="O19" s="23">
-        <f>前提!P$11</f>
-        <v>-5</v>
-      </c>
-      <c r="P19" s="23">
-        <f>前提!Q$11</f>
-        <v>-5</v>
-      </c>
-      <c r="Q19" s="23">
-        <f>前提!R$11</f>
-        <v>-5</v>
-      </c>
-      <c r="R19" s="23">
-        <f>前提!S$11</f>
-        <v>-5</v>
-      </c>
-      <c r="S19" s="23">
-        <f>SUM(C19:R19)</f>
-        <v>-88</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>案件支出（マイナスは対象会社借入等による軽減）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　HT100%化</t>
-        </is>
-      </c>
-      <c r="C21" s="23">
-        <f>-$B$6*(SUMIFS(前提!$D$12:$D$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$D$12:$D$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,$B$3))</f>
-        <v>-30.0</v>
-      </c>
-      <c r="D21" s="23">
-        <f>-$B$6*(SUMIFS(前提!$E$12:$E$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$E$12:$E$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="23">
-        <f>-$B$6*(SUMIFS(前提!$F$12:$F$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$F$12:$F$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="23">
-        <f>-$B$6*(SUMIFS(前提!$G$12:$G$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$G$12:$G$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="G21" s="23">
-        <f>-$B$6*(SUMIFS(前提!$H$12:$H$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$H$12:$H$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="H21" s="23">
-        <f>-$B$6*(SUMIFS(前提!$I$12:$I$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$I$12:$I$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="I21" s="23">
-        <f>-$B$6*(SUMIFS(前提!$J$12:$J$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$J$12:$J$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="J21" s="23">
-        <f>-$B$6*(SUMIFS(前提!$K$12:$K$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$K$12:$K$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="K21" s="23">
-        <f>-$B$6*(SUMIFS(前提!$L$12:$L$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$L$12:$L$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="L21" s="23">
-        <f>-$B$6*(SUMIFS(前提!$M$12:$M$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$M$12:$M$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="M21" s="23">
-        <f>-$B$6*(SUMIFS(前提!$N$12:$N$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$N$12:$N$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="N21" s="23">
-        <f>-$B$6*(SUMIFS(前提!$O$12:$O$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$O$12:$O$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="O21" s="23">
-        <f>-$B$6*(SUMIFS(前提!$P$12:$P$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$P$12:$P$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="P21" s="23">
-        <f>-$B$6*(SUMIFS(前提!$Q$12:$Q$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$Q$12:$Q$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="23">
-        <f>-$B$6*(SUMIFS(前提!$R$12:$R$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$R$12:$R$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="R21" s="23">
-        <f>-$B$6*(SUMIFS(前提!$S$12:$S$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$S$12:$S$51,前提!$A$12:$A$51,TRIM($A21),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="S21" s="23">
-        <f>SUM(C21:R21)</f>
-        <v>-30.0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　メディプロ</t>
-        </is>
-      </c>
-      <c r="C22" s="23">
-        <f>-$B$7*(SUMIFS(前提!$D$12:$D$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$D$12:$D$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="D22" s="23">
-        <f>-$B$7*(SUMIFS(前提!$E$12:$E$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$E$12:$E$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,$B$3))</f>
-        <v>-1.5</v>
-      </c>
-      <c r="E22" s="23">
-        <f>-$B$7*(SUMIFS(前提!$F$12:$F$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$F$12:$F$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,$B$3))</f>
-        <v>-30.5</v>
-      </c>
-      <c r="F22" s="23">
-        <f>-$B$7*(SUMIFS(前提!$G$12:$G$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$G$12:$G$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="G22" s="23">
-        <f>-$B$7*(SUMIFS(前提!$H$12:$H$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$H$12:$H$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="H22" s="23">
-        <f>-$B$7*(SUMIFS(前提!$I$12:$I$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$I$12:$I$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="I22" s="23">
-        <f>-$B$7*(SUMIFS(前提!$J$12:$J$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$J$12:$J$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="23">
-        <f>-$B$7*(SUMIFS(前提!$K$12:$K$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$K$12:$K$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="K22" s="23">
-        <f>-$B$7*(SUMIFS(前提!$L$12:$L$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$L$12:$L$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="L22" s="23">
-        <f>-$B$7*(SUMIFS(前提!$M$12:$M$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$M$12:$M$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="M22" s="23">
-        <f>-$B$7*(SUMIFS(前提!$N$12:$N$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$N$12:$N$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="N22" s="23">
-        <f>-$B$7*(SUMIFS(前提!$O$12:$O$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$O$12:$O$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="O22" s="23">
-        <f>-$B$7*(SUMIFS(前提!$P$12:$P$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$P$12:$P$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="P22" s="23">
-        <f>-$B$7*(SUMIFS(前提!$Q$12:$Q$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$Q$12:$Q$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="23">
-        <f>-$B$7*(SUMIFS(前提!$R$12:$R$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$R$12:$R$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="R22" s="23">
-        <f>-$B$7*(SUMIFS(前提!$S$12:$S$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$S$12:$S$51,前提!$A$12:$A$51,TRIM($A22),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="S22" s="23">
-        <f>SUM(C22:R22)</f>
-        <v>-32.0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　ヒューマンアイ</t>
-        </is>
-      </c>
-      <c r="C23" s="23">
-        <f>-$B$8*(SUMIFS(前提!$D$12:$D$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$D$12:$D$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="D23" s="23">
-        <f>-$B$8*(SUMIFS(前提!$E$12:$E$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$E$12:$E$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,$B$3))</f>
-        <v>-12.5</v>
-      </c>
-      <c r="E23" s="23">
-        <f>-$B$8*(SUMIFS(前提!$F$12:$F$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$F$12:$F$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="F23" s="23">
-        <f>-$B$8*(SUMIFS(前提!$G$12:$G$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$G$12:$G$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,$B$3))</f>
-        <v>-12.0</v>
-      </c>
-      <c r="G23" s="23">
-        <f>-$B$8*(SUMIFS(前提!$H$12:$H$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$H$12:$H$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="H23" s="23">
-        <f>-$B$8*(SUMIFS(前提!$I$12:$I$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$I$12:$I$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="I23" s="23">
-        <f>-$B$8*(SUMIFS(前提!$J$12:$J$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$J$12:$J$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,$B$3))</f>
-        <v>-12.0</v>
-      </c>
-      <c r="J23" s="23">
-        <f>-$B$8*(SUMIFS(前提!$K$12:$K$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$K$12:$K$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="K23" s="23">
-        <f>-$B$8*(SUMIFS(前提!$L$12:$L$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$L$12:$L$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="L23" s="23">
-        <f>-$B$8*(SUMIFS(前提!$M$12:$M$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$M$12:$M$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="M23" s="23">
-        <f>-$B$8*(SUMIFS(前提!$N$12:$N$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$N$12:$N$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="N23" s="23">
-        <f>-$B$8*(SUMIFS(前提!$O$12:$O$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$O$12:$O$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="O23" s="23">
-        <f>-$B$8*(SUMIFS(前提!$P$12:$P$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$P$12:$P$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="P23" s="23">
-        <f>-$B$8*(SUMIFS(前提!$Q$12:$Q$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$Q$12:$Q$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="23">
-        <f>-$B$8*(SUMIFS(前提!$R$12:$R$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$R$12:$R$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="R23" s="23">
-        <f>-$B$8*(SUMIFS(前提!$S$12:$S$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$S$12:$S$51,前提!$A$12:$A$51,TRIM($A23),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="S23" s="23">
-        <f>SUM(C23:R23)</f>
-        <v>-36.5</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　クレッシェンド</t>
-        </is>
-      </c>
-      <c r="C24" s="23">
-        <f>-$B$9*(SUMIFS(前提!$D$12:$D$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$D$12:$D$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="D24" s="23">
-        <f>-$B$9*(SUMIFS(前提!$E$12:$E$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$E$12:$E$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,$B$3))</f>
-        <v>-3.1</v>
-      </c>
-      <c r="E24" s="23">
-        <f>-$B$9*(SUMIFS(前提!$F$12:$F$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$F$12:$F$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,$B$3))</f>
-        <v>-32.0</v>
-      </c>
-      <c r="F24" s="23">
-        <f>-$B$9*(SUMIFS(前提!$G$12:$G$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$G$12:$G$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="G24" s="23">
-        <f>-$B$9*(SUMIFS(前提!$H$12:$H$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$H$12:$H$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="H24" s="23">
-        <f>-$B$9*(SUMIFS(前提!$I$12:$I$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$I$12:$I$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="I24" s="23">
-        <f>-$B$9*(SUMIFS(前提!$J$12:$J$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$J$12:$J$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="J24" s="23">
-        <f>-$B$9*(SUMIFS(前提!$K$12:$K$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$K$12:$K$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="K24" s="23">
-        <f>-$B$9*(SUMIFS(前提!$L$12:$L$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$L$12:$L$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="L24" s="23">
-        <f>-$B$9*(SUMIFS(前提!$M$12:$M$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$M$12:$M$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="M24" s="23">
-        <f>-$B$9*(SUMIFS(前提!$N$12:$N$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$N$12:$N$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="N24" s="23">
-        <f>-$B$9*(SUMIFS(前提!$O$12:$O$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$O$12:$O$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="O24" s="23">
-        <f>-$B$9*(SUMIFS(前提!$P$12:$P$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$P$12:$P$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="P24" s="23">
-        <f>-$B$9*(SUMIFS(前提!$Q$12:$Q$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$Q$12:$Q$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="23">
-        <f>-$B$9*(SUMIFS(前提!$R$12:$R$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$R$12:$R$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="R24" s="23">
-        <f>-$B$9*(SUMIFS(前提!$S$12:$S$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$S$12:$S$51,前提!$A$12:$A$51,TRIM($A24),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="S24" s="23">
-        <f>SUM(C24:R24)</f>
-        <v>-35.1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　ワイズケア</t>
-        </is>
-      </c>
-      <c r="C25" s="23">
-        <f>-$B$10*(SUMIFS(前提!$D$12:$D$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$D$12:$D$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="23">
-        <f>-$B$10*(SUMIFS(前提!$E$12:$E$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$E$12:$E$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,$B$3))</f>
-        <v>-8.7</v>
-      </c>
-      <c r="E25" s="23">
-        <f>-$B$10*(SUMIFS(前提!$F$12:$F$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$F$12:$F$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,$B$3))</f>
-        <v>-127.3</v>
-      </c>
-      <c r="F25" s="23">
-        <f>-$B$10*(SUMIFS(前提!$G$12:$G$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$G$12:$G$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="23">
-        <f>-$B$10*(SUMIFS(前提!$H$12:$H$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$H$12:$H$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="23">
-        <f>-$B$10*(SUMIFS(前提!$I$12:$I$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$I$12:$I$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="I25" s="23">
-        <f>-$B$10*(SUMIFS(前提!$J$12:$J$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$J$12:$J$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="J25" s="23">
-        <f>-$B$10*(SUMIFS(前提!$K$12:$K$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$K$12:$K$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="K25" s="23">
-        <f>-$B$10*(SUMIFS(前提!$L$12:$L$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$L$12:$L$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="L25" s="23">
-        <f>-$B$10*(SUMIFS(前提!$M$12:$M$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$M$12:$M$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="M25" s="23">
-        <f>-$B$10*(SUMIFS(前提!$N$12:$N$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$N$12:$N$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="N25" s="23">
-        <f>-$B$10*(SUMIFS(前提!$O$12:$O$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$O$12:$O$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="O25" s="23">
-        <f>-$B$10*(SUMIFS(前提!$P$12:$P$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$P$12:$P$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="P25" s="23">
-        <f>-$B$10*(SUMIFS(前提!$Q$12:$Q$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$Q$12:$Q$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="23">
-        <f>-$B$10*(SUMIFS(前提!$R$12:$R$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$R$12:$R$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="R25" s="23">
-        <f>-$B$10*(SUMIFS(前提!$S$12:$S$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$S$12:$S$51,前提!$A$12:$A$51,TRIM($A25),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="S25" s="23">
-        <f>SUM(C25:R25)</f>
-        <v>-136.0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　エーステイスト</t>
-        </is>
-      </c>
-      <c r="C26" s="23">
-        <f>-$B$11*(SUMIFS(前提!$D$12:$D$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$D$12:$D$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="D26" s="23">
-        <f>-$B$11*(SUMIFS(前提!$E$12:$E$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$E$12:$E$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,$B$3))</f>
-        <v>-2.75</v>
-      </c>
-      <c r="E26" s="23">
-        <f>-$B$11*(SUMIFS(前提!$F$12:$F$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$F$12:$F$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,$B$3))</f>
-        <v>-2.0</v>
-      </c>
-      <c r="F26" s="23">
-        <f>-$B$11*(SUMIFS(前提!$G$12:$G$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$G$12:$G$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,$B$3))</f>
-        <v>-69.75</v>
-      </c>
-      <c r="G26" s="23">
-        <f>-$B$11*(SUMIFS(前提!$H$12:$H$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$H$12:$H$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="23">
-        <f>-$B$11*(SUMIFS(前提!$I$12:$I$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$I$12:$I$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="I26" s="23">
-        <f>-$B$11*(SUMIFS(前提!$J$12:$J$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$J$12:$J$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="J26" s="23">
-        <f>-$B$11*(SUMIFS(前提!$K$12:$K$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$K$12:$K$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="K26" s="23">
-        <f>-$B$11*(SUMIFS(前提!$L$12:$L$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$L$12:$L$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="L26" s="23">
-        <f>-$B$11*(SUMIFS(前提!$M$12:$M$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$M$12:$M$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="M26" s="23">
-        <f>-$B$11*(SUMIFS(前提!$N$12:$N$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$N$12:$N$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="N26" s="23">
-        <f>-$B$11*(SUMIFS(前提!$O$12:$O$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$O$12:$O$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="O26" s="23">
-        <f>-$B$11*(SUMIFS(前提!$P$12:$P$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$P$12:$P$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="P26" s="23">
-        <f>-$B$11*(SUMIFS(前提!$Q$12:$Q$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$Q$12:$Q$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="23">
-        <f>-$B$11*(SUMIFS(前提!$R$12:$R$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$R$12:$R$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="R26" s="23">
-        <f>-$B$11*(SUMIFS(前提!$S$12:$S$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$S$12:$S$51,前提!$A$12:$A$51,TRIM($A26),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="S26" s="23">
-        <f>SUM(C26:R26)</f>
-        <v>-74.5</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　日本経営センター</t>
-        </is>
-      </c>
-      <c r="C27" s="23">
-        <f>-$B$12*(SUMIFS(前提!$D$12:$D$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$D$12:$D$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="D27" s="23">
-        <f>-$B$12*(SUMIFS(前提!$E$12:$E$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$E$12:$E$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="E27" s="23">
-        <f>-$B$12*(SUMIFS(前提!$F$12:$F$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$F$12:$F$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="F27" s="23">
-        <f>-$B$12*(SUMIFS(前提!$G$12:$G$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$G$12:$G$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,$B$3))</f>
-        <v>-4.75</v>
-      </c>
-      <c r="G27" s="23">
-        <f>-$B$12*(SUMIFS(前提!$H$12:$H$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$H$12:$H$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,$B$3))</f>
-        <v>-87.75</v>
-      </c>
-      <c r="H27" s="23">
-        <f>-$B$12*(SUMIFS(前提!$I$12:$I$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$I$12:$I$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="I27" s="23">
-        <f>-$B$12*(SUMIFS(前提!$J$12:$J$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$J$12:$J$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="J27" s="23">
-        <f>-$B$12*(SUMIFS(前提!$K$12:$K$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$K$12:$K$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="K27" s="23">
-        <f>-$B$12*(SUMIFS(前提!$L$12:$L$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$L$12:$L$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="L27" s="23">
-        <f>-$B$12*(SUMIFS(前提!$M$12:$M$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$M$12:$M$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="M27" s="23">
-        <f>-$B$12*(SUMIFS(前提!$N$12:$N$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$N$12:$N$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="N27" s="23">
-        <f>-$B$12*(SUMIFS(前提!$O$12:$O$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$O$12:$O$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="O27" s="23">
-        <f>-$B$12*(SUMIFS(前提!$P$12:$P$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$P$12:$P$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="P27" s="23">
-        <f>-$B$12*(SUMIFS(前提!$Q$12:$Q$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$Q$12:$Q$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="Q27" s="23">
-        <f>-$B$12*(SUMIFS(前提!$R$12:$R$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$R$12:$R$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="R27" s="23">
-        <f>-$B$12*(SUMIFS(前提!$S$12:$S$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$S$12:$S$51,前提!$A$12:$A$51,TRIM($A27),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="S27" s="23">
-        <f>SUM(C27:R27)</f>
-        <v>-92.5</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　セレサ</t>
-        </is>
-      </c>
-      <c r="C28" s="23">
-        <f>-$B$13*(SUMIFS(前提!$D$12:$D$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$D$12:$D$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="D28" s="23">
-        <f>-$B$13*(SUMIFS(前提!$E$12:$E$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$E$12:$E$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="23">
-        <f>-$B$13*(SUMIFS(前提!$F$12:$F$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$F$12:$F$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="F28" s="23">
-        <f>-$B$13*(SUMIFS(前提!$G$12:$G$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$G$12:$G$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="G28" s="23">
-        <f>-$B$13*(SUMIFS(前提!$H$12:$H$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$H$12:$H$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="H28" s="23">
-        <f>-$B$13*(SUMIFS(前提!$I$12:$I$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$I$12:$I$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,$B$3))</f>
-        <v>-2.1</v>
-      </c>
-      <c r="I28" s="23">
-        <f>-$B$13*(SUMIFS(前提!$J$12:$J$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$J$12:$J$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,$B$3))</f>
-        <v>-55.5</v>
-      </c>
-      <c r="J28" s="23">
-        <f>-$B$13*(SUMIFS(前提!$K$12:$K$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$K$12:$K$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="K28" s="23">
-        <f>-$B$13*(SUMIFS(前提!$L$12:$L$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$L$12:$L$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="L28" s="23">
-        <f>-$B$13*(SUMIFS(前提!$M$12:$M$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$M$12:$M$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="M28" s="23">
-        <f>-$B$13*(SUMIFS(前提!$N$12:$N$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$N$12:$N$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="N28" s="23">
-        <f>-$B$13*(SUMIFS(前提!$O$12:$O$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$O$12:$O$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="O28" s="23">
-        <f>-$B$13*(SUMIFS(前提!$P$12:$P$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$P$12:$P$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="P28" s="23">
-        <f>-$B$13*(SUMIFS(前提!$Q$12:$Q$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$Q$12:$Q$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="Q28" s="23">
-        <f>-$B$13*(SUMIFS(前提!$R$12:$R$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$R$12:$R$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="R28" s="23">
-        <f>-$B$13*(SUMIFS(前提!$S$12:$S$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$S$12:$S$51,前提!$A$12:$A$51,TRIM($A28),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="S28" s="23">
-        <f>SUM(C28:R28)</f>
-        <v>-57.6</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　シルバーメディカル</t>
-        </is>
-      </c>
-      <c r="C29" s="23">
-        <f>-$B$14*(SUMIFS(前提!$D$12:$D$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$D$12:$D$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="D29" s="23">
-        <f>-$B$14*(SUMIFS(前提!$E$12:$E$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$E$12:$E$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>-1.1</v>
-      </c>
-      <c r="E29" s="23">
-        <f>-$B$14*(SUMIFS(前提!$F$12:$F$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$F$12:$F$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>-5.0</v>
-      </c>
-      <c r="F29" s="23">
-        <f>-$B$14*(SUMIFS(前提!$G$12:$G$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$G$12:$G$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>-114.0</v>
-      </c>
-      <c r="G29" s="23">
-        <f>-$B$14*(SUMIFS(前提!$H$12:$H$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$H$12:$H$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="H29" s="23">
-        <f>-$B$14*(SUMIFS(前提!$I$12:$I$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$I$12:$I$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="I29" s="23">
-        <f>-$B$14*(SUMIFS(前提!$J$12:$J$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$J$12:$J$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="J29" s="23">
-        <f>-$B$14*(SUMIFS(前提!$K$12:$K$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$K$12:$K$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="K29" s="23">
-        <f>-$B$14*(SUMIFS(前提!$L$12:$L$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$L$12:$L$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="L29" s="23">
-        <f>-$B$14*(SUMIFS(前提!$M$12:$M$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$M$12:$M$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="M29" s="23">
-        <f>-$B$14*(SUMIFS(前提!$N$12:$N$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$N$12:$N$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="N29" s="23">
-        <f>-$B$14*(SUMIFS(前提!$O$12:$O$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$O$12:$O$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="O29" s="23">
-        <f>-$B$14*(SUMIFS(前提!$P$12:$P$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$P$12:$P$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="P29" s="23">
-        <f>-$B$14*(SUMIFS(前提!$Q$12:$Q$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$Q$12:$Q$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="23">
-        <f>-$B$14*(SUMIFS(前提!$R$12:$R$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$R$12:$R$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="R29" s="23">
-        <f>-$B$14*(SUMIFS(前提!$S$12:$S$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$S$12:$S$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>0</v>
-      </c>
-      <c r="S29" s="23">
-        <f>SUM(C29:R29)</f>
-        <v>-120.1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>案件支出 合計</t>
-        </is>
-      </c>
-      <c r="C30" s="20">
-        <f>SUM(C21:C29)</f>
-        <v>-30.0</v>
-      </c>
-      <c r="D30" s="20">
-        <f>SUM(D21:D29)</f>
-        <v>-29.65</v>
-      </c>
-      <c r="E30" s="20">
-        <f>SUM(E21:E29)</f>
-        <v>-196.8</v>
-      </c>
-      <c r="F30" s="20">
-        <f>SUM(F21:F29)</f>
-        <v>-200.5</v>
-      </c>
-      <c r="G30" s="20">
-        <f>SUM(G21:G29)</f>
-        <v>-87.75</v>
-      </c>
-      <c r="H30" s="20">
-        <f>SUM(H21:H29)</f>
-        <v>-2.1</v>
-      </c>
-      <c r="I30" s="20">
-        <f>SUM(I21:I29)</f>
-        <v>-67.5</v>
-      </c>
-      <c r="J30" s="20">
-        <f>SUM(J21:J29)</f>
-        <v>0</v>
-      </c>
-      <c r="K30" s="20">
-        <f>SUM(K21:K29)</f>
-        <v>0</v>
-      </c>
-      <c r="L30" s="20">
-        <f>SUM(L21:L29)</f>
-        <v>0</v>
-      </c>
-      <c r="M30" s="20">
-        <f>SUM(M21:M29)</f>
-        <v>0</v>
-      </c>
-      <c r="N30" s="20">
-        <f>SUM(N21:N29)</f>
-        <v>0</v>
-      </c>
-      <c r="O30" s="20">
-        <f>SUM(O21:O29)</f>
-        <v>0</v>
-      </c>
-      <c r="P30" s="20">
-        <f>SUM(P21:P29)</f>
-        <v>0</v>
-      </c>
-      <c r="Q30" s="20">
-        <f>SUM(Q21:Q29)</f>
-        <v>0</v>
-      </c>
-      <c r="R30" s="20">
-        <f>SUM(R21:R29)</f>
-        <v>0</v>
-      </c>
-      <c r="S30" s="20">
-        <f>SUM(C30:R30)</f>
-        <v>-614.3</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>期末現預金</t>
-        </is>
-      </c>
-      <c r="C31" s="21">
-        <f>C18+C19+C30</f>
-        <v>329.3</v>
-      </c>
-      <c r="D31" s="21">
-        <f>D18+D19+D30</f>
-        <v>292.65</v>
-      </c>
-      <c r="E31" s="21">
-        <f>E18+E19+E30</f>
-        <v>88.85</v>
-      </c>
-      <c r="F31" s="21">
-        <f>F18+F19+F30</f>
-        <v>-118.65</v>
-      </c>
-      <c r="G31" s="21">
-        <f>G18+G19+G30</f>
-        <v>-211.4</v>
-      </c>
-      <c r="H31" s="21">
-        <f>H18+H19+H30</f>
-        <v>-218.5</v>
-      </c>
-      <c r="I31" s="21">
-        <f>I18+I19+I30</f>
-        <v>-291.0</v>
-      </c>
-      <c r="J31" s="21">
-        <f>J18+J19+J30</f>
-        <v>-296.0</v>
-      </c>
-      <c r="K31" s="21">
-        <f>K18+K19+K30</f>
-        <v>-301.0</v>
-      </c>
-      <c r="L31" s="21">
-        <f>L18+L19+L30</f>
-        <v>-306.0</v>
-      </c>
-      <c r="M31" s="21">
-        <f>M18+M19+M30</f>
-        <v>-311.0</v>
-      </c>
-      <c r="N31" s="21">
-        <f>N18+N19+N30</f>
-        <v>-316.0</v>
-      </c>
-      <c r="O31" s="21">
-        <f>O18+O19+O30</f>
-        <v>-321.0</v>
-      </c>
-      <c r="P31" s="21">
-        <f>P18+P19+P30</f>
-        <v>-326.0</v>
-      </c>
-      <c r="Q31" s="21">
-        <f>Q18+Q19+Q30</f>
-        <v>-331.0</v>
-      </c>
-      <c r="R31" s="21">
-        <f>R18+R19+R30</f>
-        <v>-336.0</v>
-      </c>
-      <c r="S31" s="21" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>安全水準との差</t>
-        </is>
-      </c>
-      <c r="C32" s="23">
-        <f>C31-前提!$B$4</f>
-        <v>229.3</v>
-      </c>
-      <c r="D32" s="23">
-        <f>D31-前提!$B$4</f>
-        <v>192.65</v>
-      </c>
-      <c r="E32" s="23">
-        <f>E31-前提!$B$4</f>
-        <v>-11.15</v>
-      </c>
-      <c r="F32" s="23">
-        <f>F31-前提!$B$4</f>
-        <v>-218.65</v>
-      </c>
-      <c r="G32" s="23">
-        <f>G31-前提!$B$4</f>
-        <v>-311.4</v>
-      </c>
-      <c r="H32" s="23">
-        <f>H31-前提!$B$4</f>
-        <v>-318.5</v>
-      </c>
-      <c r="I32" s="23">
-        <f>I31-前提!$B$4</f>
-        <v>-391.0</v>
-      </c>
-      <c r="J32" s="23">
-        <f>J31-前提!$B$4</f>
-        <v>-396.0</v>
-      </c>
-      <c r="K32" s="23">
-        <f>K31-前提!$B$4</f>
-        <v>-401.0</v>
-      </c>
-      <c r="L32" s="23">
-        <f>L31-前提!$B$4</f>
-        <v>-406.0</v>
-      </c>
-      <c r="M32" s="23">
-        <f>M31-前提!$B$4</f>
-        <v>-411.0</v>
-      </c>
-      <c r="N32" s="23">
-        <f>N31-前提!$B$4</f>
-        <v>-416.0</v>
-      </c>
-      <c r="O32" s="23">
-        <f>O31-前提!$B$4</f>
-        <v>-421.0</v>
-      </c>
-      <c r="P32" s="23">
-        <f>P31-前提!$B$4</f>
-        <v>-426.0</v>
-      </c>
-      <c r="Q32" s="23">
-        <f>Q31-前提!$B$4</f>
-        <v>-431.0</v>
-      </c>
-      <c r="R32" s="23">
-        <f>R31-前提!$B$4</f>
-        <v>-436.0</v>
-      </c>
-      <c r="S32" s="23" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>必要調達額（安全水準を維持するための不足額）</t>
-        </is>
-      </c>
-      <c r="C33" s="24">
-        <f>MAX(0,前提!$B$4-C31)</f>
-        <v>0</v>
-      </c>
-      <c r="D33" s="24">
-        <f>MAX(0,前提!$B$4-D31)</f>
-        <v>0</v>
-      </c>
-      <c r="E33" s="24">
-        <f>MAX(0,前提!$B$4-E31)</f>
-        <v>11.15</v>
-      </c>
-      <c r="F33" s="24">
-        <f>MAX(0,前提!$B$4-F31)</f>
-        <v>218.65</v>
-      </c>
-      <c r="G33" s="24">
-        <f>MAX(0,前提!$B$4-G31)</f>
-        <v>311.4</v>
-      </c>
-      <c r="H33" s="24">
-        <f>MAX(0,前提!$B$4-H31)</f>
-        <v>318.5</v>
-      </c>
-      <c r="I33" s="24">
-        <f>MAX(0,前提!$B$4-I31)</f>
-        <v>391.0</v>
-      </c>
-      <c r="J33" s="24">
-        <f>MAX(0,前提!$B$4-J31)</f>
-        <v>396.0</v>
-      </c>
-      <c r="K33" s="24">
-        <f>MAX(0,前提!$B$4-K31)</f>
-        <v>401.0</v>
-      </c>
-      <c r="L33" s="24">
-        <f>MAX(0,前提!$B$4-L31)</f>
-        <v>406.0</v>
-      </c>
-      <c r="M33" s="24">
-        <f>MAX(0,前提!$B$4-M31)</f>
-        <v>411.0</v>
-      </c>
-      <c r="N33" s="24">
-        <f>MAX(0,前提!$B$4-N31)</f>
-        <v>416.0</v>
-      </c>
-      <c r="O33" s="24">
-        <f>MAX(0,前提!$B$4-O31)</f>
-        <v>421.0</v>
-      </c>
-      <c r="P33" s="24">
-        <f>MAX(0,前提!$B$4-P31)</f>
-        <v>426.0</v>
-      </c>
-      <c r="Q33" s="24">
-        <f>MAX(0,前提!$B$4-Q31)</f>
-        <v>431.0</v>
-      </c>
-      <c r="R33" s="24">
-        <f>MAX(0,前提!$B$4-R31)</f>
-        <v>436.0</v>
-      </c>
-      <c r="S33" s="24" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>累計案件支出</t>
-        </is>
-      </c>
-      <c r="C34" s="23">
-        <f>-SUM($C30:C30)</f>
-        <v>30.0</v>
-      </c>
-      <c r="D34" s="23">
-        <f>-SUM($C30:D30)</f>
-        <v>59.65</v>
-      </c>
-      <c r="E34" s="23">
-        <f>-SUM($C30:E30)</f>
-        <v>256.45</v>
-      </c>
-      <c r="F34" s="23">
-        <f>-SUM($C30:F30)</f>
-        <v>456.95</v>
-      </c>
-      <c r="G34" s="23">
-        <f>-SUM($C30:G30)</f>
-        <v>544.7</v>
-      </c>
-      <c r="H34" s="23">
-        <f>-SUM($C30:H30)</f>
-        <v>546.8</v>
-      </c>
-      <c r="I34" s="23">
-        <f>-SUM($C30:I30)</f>
-        <v>614.3</v>
-      </c>
-      <c r="J34" s="23">
-        <f>-SUM($C30:J30)</f>
-        <v>614.3</v>
-      </c>
-      <c r="K34" s="23">
-        <f>-SUM($C30:K30)</f>
-        <v>614.3</v>
-      </c>
-      <c r="L34" s="23">
-        <f>-SUM($C30:L30)</f>
-        <v>614.3</v>
-      </c>
-      <c r="M34" s="23">
-        <f>-SUM($C30:M30)</f>
-        <v>614.3</v>
-      </c>
-      <c r="N34" s="23">
-        <f>-SUM($C30:N30)</f>
-        <v>614.3</v>
-      </c>
-      <c r="O34" s="23">
-        <f>-SUM($C30:O30)</f>
-        <v>614.3</v>
-      </c>
-      <c r="P34" s="23">
-        <f>-SUM($C30:P30)</f>
-        <v>614.3</v>
-      </c>
-      <c r="Q34" s="23">
-        <f>-SUM($C30:Q30)</f>
-        <v>614.3</v>
-      </c>
-      <c r="R34" s="23">
-        <f>-SUM($C30:R30)</f>
-        <v>614.3</v>
-      </c>
-      <c r="S34" s="23" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>安全水準割込み（1＝割込）</t>
-        </is>
-      </c>
-      <c r="C35" s="23">
-        <f>IF(C31&lt;前提!$B$4,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D35" s="23">
-        <f>IF(D31&lt;前提!$B$4,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E35" s="23">
-        <f>IF(E31&lt;前提!$B$4,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="F35" s="23">
-        <f>IF(F31&lt;前提!$B$4,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="G35" s="23">
-        <f>IF(G31&lt;前提!$B$4,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="H35" s="23">
-        <f>IF(H31&lt;前提!$B$4,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="I35" s="23">
-        <f>IF(I31&lt;前提!$B$4,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J35" s="23">
-        <f>IF(J31&lt;前提!$B$4,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="K35" s="23">
-        <f>IF(K31&lt;前提!$B$4,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="L35" s="23">
-        <f>IF(L31&lt;前提!$B$4,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="M35" s="23">
-        <f>IF(M31&lt;前提!$B$4,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="N35" s="23">
-        <f>IF(N31&lt;前提!$B$4,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="O35" s="23">
-        <f>IF(O31&lt;前提!$B$4,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="P35" s="23">
-        <f>IF(P31&lt;前提!$B$4,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="Q35" s="23">
-        <f>IF(Q31&lt;前提!$B$4,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="R35" s="23">
-        <f>IF(R31&lt;前提!$B$4,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="S35" s="23" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>サマリー指標</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>総支出（案件・16ヶ月）</t>
-        </is>
-      </c>
-      <c r="B39" s="20">
-        <f>-S30</f>
-        <v>614.3</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>最低残高</t>
-        </is>
-      </c>
-      <c r="B40" s="20">
-        <f>MIN(C31:R31)</f>
-        <v>-336.0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>最低残高の月</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="str">
-        <f>INDEX($C$17:$R$17,MATCH(B40,C31:R31,0))</f>
-        <v>2027/12</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>初めて安全水準を割る月</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="str">
-        <f>IFERROR(INDEX($C$17:$R$17,MATCH(1,C35:R35,0)),"—")</f>
-        <v>2026/11</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>必要調達額（2027/12まで）</t>
-        </is>
-      </c>
-      <c r="B43" s="20">
-        <f>MAX(C33:R33)</f>
-        <v>436.0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>2026/11までの不足</t>
-        </is>
-      </c>
-      <c r="B44" s="20">
-        <f>E33</f>
-        <v>11.15</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>2027/1までの不足</t>
-        </is>
-      </c>
-      <c r="B45" s="20">
-        <f>G33</f>
-        <v>311.4</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>2027/3までの不足</t>
-        </is>
-      </c>
-      <c r="B46" s="20">
-        <f>I33</f>
-        <v>391.0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>2027/12 期末現預金</t>
-        </is>
-      </c>
-      <c r="B47" s="20">
-        <f>R31</f>
-        <v>-336.0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>年換算売上（オーガニック＋実行案件）</t>
-        </is>
-      </c>
-      <c r="B48" s="25">
-        <f>前提!$B$5+SUMPRODUCT($B$6:$B$14,案件一覧!$D$4:$D$12)</f>
-        <v>3888</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>年換算 調整後EBITDA（現状）</t>
-        </is>
-      </c>
-      <c r="B49" s="25">
-        <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12)</f>
-        <v>161</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>年換算 調整後EBITDA（改善後）</t>
-        </is>
-      </c>
-      <c r="B50" s="25">
-        <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$F$4:$F$12)</f>
-        <v>271</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>承継・残置負債</t>
-        </is>
-      </c>
-      <c r="B51" s="20">
-        <f>SUMPRODUCT($B$6:$B$14,案件一覧!$G$4:$G$12)</f>
-        <v>221.15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10133,7 +8185,7 @@
     <row r="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>S1 基本（確定4件） — HD単体 月次キャッシュ推移（百万円）</t>
+          <t>S1 基本（確定5件） — HD単体 月次キャッシュ推移（百万円）</t>
         </is>
       </c>
     </row>
@@ -10260,7 +8312,7 @@
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -10372,59 +8424,59 @@
       </c>
       <c r="E18" s="20">
         <f>D31</f>
-        <v>305.2</v>
+        <v>304.1</v>
       </c>
       <c r="F18" s="20">
         <f>E31</f>
-        <v>235.7</v>
+        <v>229.6</v>
       </c>
       <c r="G18" s="20">
         <f>F31</f>
-        <v>216.7</v>
+        <v>96.6</v>
       </c>
       <c r="H18" s="20">
         <f>G31</f>
-        <v>211.7</v>
+        <v>91.6</v>
       </c>
       <c r="I18" s="20">
         <f>H31</f>
-        <v>206.7</v>
+        <v>86.6</v>
       </c>
       <c r="J18" s="20">
         <f>I31</f>
-        <v>189.7</v>
+        <v>69.6</v>
       </c>
       <c r="K18" s="20">
         <f>J31</f>
-        <v>184.7</v>
+        <v>64.6</v>
       </c>
       <c r="L18" s="20">
         <f>K31</f>
-        <v>179.7</v>
+        <v>59.6</v>
       </c>
       <c r="M18" s="20">
         <f>L31</f>
-        <v>174.7</v>
+        <v>54.6</v>
       </c>
       <c r="N18" s="20">
         <f>M31</f>
-        <v>169.7</v>
+        <v>49.6</v>
       </c>
       <c r="O18" s="20">
         <f>N31</f>
-        <v>164.7</v>
+        <v>44.6</v>
       </c>
       <c r="P18" s="20">
         <f>O31</f>
-        <v>159.7</v>
+        <v>39.6</v>
       </c>
       <c r="Q18" s="20">
         <f>P31</f>
-        <v>154.7</v>
+        <v>34.6</v>
       </c>
       <c r="R18" s="20">
         <f>Q31</f>
-        <v>149.7</v>
+        <v>29.6</v>
       </c>
       <c r="S18" s="20" t="n"/>
     </row>
@@ -11122,15 +9174,15 @@
       </c>
       <c r="D29" s="23">
         <f>-$B$14*(SUMIFS(前提!$E$12:$E$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$E$12:$E$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>0.0</v>
+        <v>-1.1</v>
       </c>
       <c r="E29" s="23">
         <f>-$B$14*(SUMIFS(前提!$F$12:$F$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$F$12:$F$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>0.0</v>
+        <v>-5.0</v>
       </c>
       <c r="F29" s="23">
         <f>-$B$14*(SUMIFS(前提!$G$12:$G$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$G$12:$G$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>0.0</v>
+        <v>-114.0</v>
       </c>
       <c r="G29" s="23">
         <f>-$B$14*(SUMIFS(前提!$H$12:$H$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$H$12:$H$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
@@ -11182,7 +9234,7 @@
       </c>
       <c r="S29" s="23">
         <f>SUM(C29:R29)</f>
-        <v>0.0</v>
+        <v>-120.1</v>
       </c>
     </row>
     <row r="30">
@@ -11197,15 +9249,15 @@
       </c>
       <c r="D30" s="20">
         <f>SUM(D21:D29)</f>
-        <v>-17.1</v>
+        <v>-18.2</v>
       </c>
       <c r="E30" s="20">
         <f>SUM(E21:E29)</f>
-        <v>-62.5</v>
+        <v>-67.5</v>
       </c>
       <c r="F30" s="20">
         <f>SUM(F21:F29)</f>
-        <v>-12.0</v>
+        <v>-126.0</v>
       </c>
       <c r="G30" s="20">
         <f>SUM(G21:G29)</f>
@@ -11257,7 +9309,7 @@
       </c>
       <c r="S30" s="20">
         <f>SUM(C30:R30)</f>
-        <v>-133.6</v>
+        <v>-253.7</v>
       </c>
     </row>
     <row r="31">
@@ -11272,63 +9324,63 @@
       </c>
       <c r="D31" s="21">
         <f>D18+D19+D30</f>
-        <v>305.2</v>
+        <v>304.1</v>
       </c>
       <c r="E31" s="21">
         <f>E18+E19+E30</f>
-        <v>235.7</v>
+        <v>229.6</v>
       </c>
       <c r="F31" s="21">
         <f>F18+F19+F30</f>
-        <v>216.7</v>
+        <v>96.6</v>
       </c>
       <c r="G31" s="21">
         <f>G18+G19+G30</f>
-        <v>211.7</v>
+        <v>91.6</v>
       </c>
       <c r="H31" s="21">
         <f>H18+H19+H30</f>
-        <v>206.7</v>
+        <v>86.6</v>
       </c>
       <c r="I31" s="21">
         <f>I18+I19+I30</f>
-        <v>189.7</v>
+        <v>69.6</v>
       </c>
       <c r="J31" s="21">
         <f>J18+J19+J30</f>
-        <v>184.7</v>
+        <v>64.6</v>
       </c>
       <c r="K31" s="21">
         <f>K18+K19+K30</f>
-        <v>179.7</v>
+        <v>59.6</v>
       </c>
       <c r="L31" s="21">
         <f>L18+L19+L30</f>
-        <v>174.7</v>
+        <v>54.6</v>
       </c>
       <c r="M31" s="21">
         <f>M18+M19+M30</f>
-        <v>169.7</v>
+        <v>49.6</v>
       </c>
       <c r="N31" s="21">
         <f>N18+N19+N30</f>
-        <v>164.7</v>
+        <v>44.6</v>
       </c>
       <c r="O31" s="21">
         <f>O18+O19+O30</f>
-        <v>159.7</v>
+        <v>39.6</v>
       </c>
       <c r="P31" s="21">
         <f>P18+P19+P30</f>
-        <v>154.7</v>
+        <v>34.6</v>
       </c>
       <c r="Q31" s="21">
         <f>Q18+Q19+Q30</f>
-        <v>149.7</v>
+        <v>29.6</v>
       </c>
       <c r="R31" s="21">
         <f>R18+R19+R30</f>
-        <v>144.7</v>
+        <v>24.6</v>
       </c>
       <c r="S31" s="21" t="n"/>
     </row>
@@ -11344,63 +9396,63 @@
       </c>
       <c r="D32" s="23">
         <f>D31-前提!$B$4</f>
-        <v>205.2</v>
+        <v>204.1</v>
       </c>
       <c r="E32" s="23">
         <f>E31-前提!$B$4</f>
-        <v>135.7</v>
+        <v>129.6</v>
       </c>
       <c r="F32" s="23">
         <f>F31-前提!$B$4</f>
-        <v>116.7</v>
+        <v>-3.4</v>
       </c>
       <c r="G32" s="23">
         <f>G31-前提!$B$4</f>
-        <v>111.7</v>
+        <v>-8.4</v>
       </c>
       <c r="H32" s="23">
         <f>H31-前提!$B$4</f>
-        <v>106.7</v>
+        <v>-13.4</v>
       </c>
       <c r="I32" s="23">
         <f>I31-前提!$B$4</f>
-        <v>89.7</v>
+        <v>-30.4</v>
       </c>
       <c r="J32" s="23">
         <f>J31-前提!$B$4</f>
-        <v>84.7</v>
+        <v>-35.4</v>
       </c>
       <c r="K32" s="23">
         <f>K31-前提!$B$4</f>
-        <v>79.7</v>
+        <v>-40.4</v>
       </c>
       <c r="L32" s="23">
         <f>L31-前提!$B$4</f>
-        <v>74.7</v>
+        <v>-45.4</v>
       </c>
       <c r="M32" s="23">
         <f>M31-前提!$B$4</f>
-        <v>69.7</v>
+        <v>-50.4</v>
       </c>
       <c r="N32" s="23">
         <f>N31-前提!$B$4</f>
-        <v>64.7</v>
+        <v>-55.4</v>
       </c>
       <c r="O32" s="23">
         <f>O31-前提!$B$4</f>
-        <v>59.7</v>
+        <v>-60.4</v>
       </c>
       <c r="P32" s="23">
         <f>P31-前提!$B$4</f>
-        <v>54.7</v>
+        <v>-65.4</v>
       </c>
       <c r="Q32" s="23">
         <f>Q31-前提!$B$4</f>
-        <v>49.7</v>
+        <v>-70.4</v>
       </c>
       <c r="R32" s="23">
         <f>R31-前提!$B$4</f>
-        <v>44.7</v>
+        <v>-75.4</v>
       </c>
       <c r="S32" s="23" t="n"/>
     </row>
@@ -11424,55 +9476,55 @@
       </c>
       <c r="F33" s="24">
         <f>MAX(0,前提!$B$4-F31)</f>
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="G33" s="24">
         <f>MAX(0,前提!$B$4-G31)</f>
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="H33" s="24">
         <f>MAX(0,前提!$B$4-H31)</f>
-        <v>0</v>
+        <v>13.4</v>
       </c>
       <c r="I33" s="24">
         <f>MAX(0,前提!$B$4-I31)</f>
-        <v>0</v>
+        <v>30.4</v>
       </c>
       <c r="J33" s="24">
         <f>MAX(0,前提!$B$4-J31)</f>
-        <v>0</v>
+        <v>35.4</v>
       </c>
       <c r="K33" s="24">
         <f>MAX(0,前提!$B$4-K31)</f>
-        <v>0</v>
+        <v>40.4</v>
       </c>
       <c r="L33" s="24">
         <f>MAX(0,前提!$B$4-L31)</f>
-        <v>0</v>
+        <v>45.4</v>
       </c>
       <c r="M33" s="24">
         <f>MAX(0,前提!$B$4-M31)</f>
-        <v>0</v>
+        <v>50.4</v>
       </c>
       <c r="N33" s="24">
         <f>MAX(0,前提!$B$4-N31)</f>
-        <v>0</v>
+        <v>55.4</v>
       </c>
       <c r="O33" s="24">
         <f>MAX(0,前提!$B$4-O31)</f>
-        <v>0</v>
+        <v>60.4</v>
       </c>
       <c r="P33" s="24">
         <f>MAX(0,前提!$B$4-P31)</f>
-        <v>0</v>
+        <v>65.4</v>
       </c>
       <c r="Q33" s="24">
         <f>MAX(0,前提!$B$4-Q31)</f>
-        <v>0</v>
+        <v>70.4</v>
       </c>
       <c r="R33" s="24">
         <f>MAX(0,前提!$B$4-R31)</f>
-        <v>0</v>
+        <v>75.4</v>
       </c>
       <c r="S33" s="24" t="n"/>
     </row>
@@ -11488,63 +9540,63 @@
       </c>
       <c r="D34" s="23">
         <f>-SUM($C30:D30)</f>
-        <v>47.1</v>
+        <v>48.2</v>
       </c>
       <c r="E34" s="23">
         <f>-SUM($C30:E30)</f>
-        <v>109.6</v>
+        <v>115.7</v>
       </c>
       <c r="F34" s="23">
         <f>-SUM($C30:F30)</f>
-        <v>121.6</v>
+        <v>241.7</v>
       </c>
       <c r="G34" s="23">
         <f>-SUM($C30:G30)</f>
-        <v>121.6</v>
+        <v>241.7</v>
       </c>
       <c r="H34" s="23">
         <f>-SUM($C30:H30)</f>
-        <v>121.6</v>
+        <v>241.7</v>
       </c>
       <c r="I34" s="23">
         <f>-SUM($C30:I30)</f>
-        <v>133.6</v>
+        <v>253.7</v>
       </c>
       <c r="J34" s="23">
         <f>-SUM($C30:J30)</f>
-        <v>133.6</v>
+        <v>253.7</v>
       </c>
       <c r="K34" s="23">
         <f>-SUM($C30:K30)</f>
-        <v>133.6</v>
+        <v>253.7</v>
       </c>
       <c r="L34" s="23">
         <f>-SUM($C30:L30)</f>
-        <v>133.6</v>
+        <v>253.7</v>
       </c>
       <c r="M34" s="23">
         <f>-SUM($C30:M30)</f>
-        <v>133.6</v>
+        <v>253.7</v>
       </c>
       <c r="N34" s="23">
         <f>-SUM($C30:N30)</f>
-        <v>133.6</v>
+        <v>253.7</v>
       </c>
       <c r="O34" s="23">
         <f>-SUM($C30:O30)</f>
-        <v>133.6</v>
+        <v>253.7</v>
       </c>
       <c r="P34" s="23">
         <f>-SUM($C30:P30)</f>
-        <v>133.6</v>
+        <v>253.7</v>
       </c>
       <c r="Q34" s="23">
         <f>-SUM($C30:Q30)</f>
-        <v>133.6</v>
+        <v>253.7</v>
       </c>
       <c r="R34" s="23">
         <f>-SUM($C30:R30)</f>
-        <v>133.6</v>
+        <v>253.7</v>
       </c>
       <c r="S34" s="23" t="n"/>
     </row>
@@ -11568,55 +9620,55 @@
       </c>
       <c r="F35" s="23">
         <f>IF(F31&lt;前提!$B$4,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" s="23">
         <f>IF(G31&lt;前提!$B$4,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" s="23">
         <f>IF(H31&lt;前提!$B$4,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" s="23">
         <f>IF(I31&lt;前提!$B$4,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="23">
         <f>IF(J31&lt;前提!$B$4,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" s="23">
         <f>IF(K31&lt;前提!$B$4,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="23">
         <f>IF(L31&lt;前提!$B$4,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="23">
         <f>IF(M31&lt;前提!$B$4,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" s="23">
         <f>IF(N31&lt;前提!$B$4,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" s="23">
         <f>IF(O31&lt;前提!$B$4,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P35" s="23">
         <f>IF(P31&lt;前提!$B$4,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q35" s="23">
         <f>IF(Q31&lt;前提!$B$4,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" s="23">
         <f>IF(R31&lt;前提!$B$4,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" s="23" t="n"/>
     </row>
@@ -11635,7 +9687,7 @@
       </c>
       <c r="B39" s="20">
         <f>-S30</f>
-        <v>133.6</v>
+        <v>253.7</v>
       </c>
     </row>
     <row r="40">
@@ -11646,7 +9698,7 @@
       </c>
       <c r="B40" s="20">
         <f>MIN(C31:R31)</f>
-        <v>144.7</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="41">
@@ -11668,7 +9720,7 @@
       </c>
       <c r="B42" s="4" t="str">
         <f>IFERROR(INDEX($C$17:$R$17,MATCH(1,C35:R35,0)),"—")</f>
-        <v>—</v>
+        <v>2026/12</v>
       </c>
     </row>
     <row r="43">
@@ -11679,7 +9731,7 @@
       </c>
       <c r="B43" s="20">
         <f>MAX(C33:R33)</f>
-        <v>0</v>
+        <v>75.4</v>
       </c>
     </row>
     <row r="44">
@@ -11701,7 +9753,7 @@
       </c>
       <c r="B45" s="20">
         <f>G33</f>
-        <v>0</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="46">
@@ -11712,7 +9764,7 @@
       </c>
       <c r="B46" s="20">
         <f>I33</f>
-        <v>0</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="47">
@@ -11723,7 +9775,7 @@
       </c>
       <c r="B47" s="20">
         <f>R31</f>
-        <v>144.7</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="48">
@@ -11734,7 +9786,7 @@
       </c>
       <c r="B48" s="25">
         <f>前提!$B$5+SUMPRODUCT($B$6:$B$14,案件一覧!$D$4:$D$12)</f>
-        <v>1658</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="49">
@@ -11745,7 +9797,7 @@
       </c>
       <c r="B49" s="25">
         <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12)</f>
-        <v>104</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50">
@@ -11756,7 +9808,7 @@
       </c>
       <c r="B50" s="25">
         <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$F$4:$F$12)</f>
-        <v>124</v>
+        <v>140</v>
       </c>
     </row>
     <row r="51">
@@ -11767,7 +9819,7 @@
       </c>
       <c r="B51" s="20">
         <f>SUMPRODUCT($B$6:$B$14,案件一覧!$G$4:$G$12)</f>
-        <v>44.85</v>
+        <v>127.85</v>
       </c>
     </row>
   </sheetData>
@@ -11935,7 +9987,7 @@
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -12047,59 +10099,59 @@
       </c>
       <c r="E18" s="20">
         <f>D31</f>
-        <v>296.5</v>
+        <v>295.4</v>
       </c>
       <c r="F18" s="20">
         <f>E31</f>
-        <v>99.7</v>
+        <v>93.6</v>
       </c>
       <c r="G18" s="20">
         <f>F31</f>
-        <v>80.7</v>
+        <v>-39.4</v>
       </c>
       <c r="H18" s="20">
         <f>G31</f>
-        <v>75.7</v>
+        <v>-44.4</v>
       </c>
       <c r="I18" s="20">
         <f>H31</f>
-        <v>70.7</v>
+        <v>-49.4</v>
       </c>
       <c r="J18" s="20">
         <f>I31</f>
-        <v>53.7</v>
+        <v>-66.4</v>
       </c>
       <c r="K18" s="20">
         <f>J31</f>
-        <v>48.7</v>
+        <v>-71.4</v>
       </c>
       <c r="L18" s="20">
         <f>K31</f>
-        <v>43.7</v>
+        <v>-76.4</v>
       </c>
       <c r="M18" s="20">
         <f>L31</f>
-        <v>38.7</v>
+        <v>-81.4</v>
       </c>
       <c r="N18" s="20">
         <f>M31</f>
-        <v>33.7</v>
+        <v>-86.4</v>
       </c>
       <c r="O18" s="20">
         <f>N31</f>
-        <v>28.7</v>
+        <v>-91.4</v>
       </c>
       <c r="P18" s="20">
         <f>O31</f>
-        <v>23.7</v>
+        <v>-96.4</v>
       </c>
       <c r="Q18" s="20">
         <f>P31</f>
-        <v>18.7</v>
+        <v>-101.4</v>
       </c>
       <c r="R18" s="20">
         <f>Q31</f>
-        <v>13.7</v>
+        <v>-106.4</v>
       </c>
       <c r="S18" s="20" t="n"/>
     </row>
@@ -12797,15 +10849,15 @@
       </c>
       <c r="D29" s="23">
         <f>-$B$14*(SUMIFS(前提!$E$12:$E$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$E$12:$E$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>0.0</v>
+        <v>-1.1</v>
       </c>
       <c r="E29" s="23">
         <f>-$B$14*(SUMIFS(前提!$F$12:$F$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$F$12:$F$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>0.0</v>
+        <v>-5.0</v>
       </c>
       <c r="F29" s="23">
         <f>-$B$14*(SUMIFS(前提!$G$12:$G$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$G$12:$G$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>0.0</v>
+        <v>-114.0</v>
       </c>
       <c r="G29" s="23">
         <f>-$B$14*(SUMIFS(前提!$H$12:$H$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$H$12:$H$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
@@ -12857,7 +10909,7 @@
       </c>
       <c r="S29" s="23">
         <f>SUM(C29:R29)</f>
-        <v>0.0</v>
+        <v>-120.1</v>
       </c>
     </row>
     <row r="30">
@@ -12872,15 +10924,15 @@
       </c>
       <c r="D30" s="20">
         <f>SUM(D21:D29)</f>
-        <v>-25.8</v>
+        <v>-26.9</v>
       </c>
       <c r="E30" s="20">
         <f>SUM(E21:E29)</f>
-        <v>-189.8</v>
+        <v>-194.8</v>
       </c>
       <c r="F30" s="20">
         <f>SUM(F21:F29)</f>
-        <v>-12.0</v>
+        <v>-126.0</v>
       </c>
       <c r="G30" s="20">
         <f>SUM(G21:G29)</f>
@@ -12932,7 +10984,7 @@
       </c>
       <c r="S30" s="20">
         <f>SUM(C30:R30)</f>
-        <v>-269.6</v>
+        <v>-389.7</v>
       </c>
     </row>
     <row r="31">
@@ -12947,63 +10999,63 @@
       </c>
       <c r="D31" s="21">
         <f>D18+D19+D30</f>
-        <v>296.5</v>
+        <v>295.4</v>
       </c>
       <c r="E31" s="21">
         <f>E18+E19+E30</f>
-        <v>99.7</v>
+        <v>93.6</v>
       </c>
       <c r="F31" s="21">
         <f>F18+F19+F30</f>
-        <v>80.7</v>
+        <v>-39.4</v>
       </c>
       <c r="G31" s="21">
         <f>G18+G19+G30</f>
-        <v>75.7</v>
+        <v>-44.4</v>
       </c>
       <c r="H31" s="21">
         <f>H18+H19+H30</f>
-        <v>70.7</v>
+        <v>-49.4</v>
       </c>
       <c r="I31" s="21">
         <f>I18+I19+I30</f>
-        <v>53.7</v>
+        <v>-66.4</v>
       </c>
       <c r="J31" s="21">
         <f>J18+J19+J30</f>
-        <v>48.7</v>
+        <v>-71.4</v>
       </c>
       <c r="K31" s="21">
         <f>K18+K19+K30</f>
-        <v>43.7</v>
+        <v>-76.4</v>
       </c>
       <c r="L31" s="21">
         <f>L18+L19+L30</f>
-        <v>38.7</v>
+        <v>-81.4</v>
       </c>
       <c r="M31" s="21">
         <f>M18+M19+M30</f>
-        <v>33.7</v>
+        <v>-86.4</v>
       </c>
       <c r="N31" s="21">
         <f>N18+N19+N30</f>
-        <v>28.7</v>
+        <v>-91.4</v>
       </c>
       <c r="O31" s="21">
         <f>O18+O19+O30</f>
-        <v>23.7</v>
+        <v>-96.4</v>
       </c>
       <c r="P31" s="21">
         <f>P18+P19+P30</f>
-        <v>18.7</v>
+        <v>-101.4</v>
       </c>
       <c r="Q31" s="21">
         <f>Q18+Q19+Q30</f>
-        <v>13.7</v>
+        <v>-106.4</v>
       </c>
       <c r="R31" s="21">
         <f>R18+R19+R30</f>
-        <v>8.7</v>
+        <v>-111.4</v>
       </c>
       <c r="S31" s="21" t="n"/>
     </row>
@@ -13019,63 +11071,63 @@
       </c>
       <c r="D32" s="23">
         <f>D31-前提!$B$4</f>
-        <v>196.5</v>
+        <v>195.4</v>
       </c>
       <c r="E32" s="23">
         <f>E31-前提!$B$4</f>
-        <v>-0.3</v>
+        <v>-6.4</v>
       </c>
       <c r="F32" s="23">
         <f>F31-前提!$B$4</f>
-        <v>-19.3</v>
+        <v>-139.4</v>
       </c>
       <c r="G32" s="23">
         <f>G31-前提!$B$4</f>
-        <v>-24.3</v>
+        <v>-144.4</v>
       </c>
       <c r="H32" s="23">
         <f>H31-前提!$B$4</f>
-        <v>-29.3</v>
+        <v>-149.4</v>
       </c>
       <c r="I32" s="23">
         <f>I31-前提!$B$4</f>
-        <v>-46.3</v>
+        <v>-166.4</v>
       </c>
       <c r="J32" s="23">
         <f>J31-前提!$B$4</f>
-        <v>-51.3</v>
+        <v>-171.4</v>
       </c>
       <c r="K32" s="23">
         <f>K31-前提!$B$4</f>
-        <v>-56.3</v>
+        <v>-176.4</v>
       </c>
       <c r="L32" s="23">
         <f>L31-前提!$B$4</f>
-        <v>-61.3</v>
+        <v>-181.4</v>
       </c>
       <c r="M32" s="23">
         <f>M31-前提!$B$4</f>
-        <v>-66.3</v>
+        <v>-186.4</v>
       </c>
       <c r="N32" s="23">
         <f>N31-前提!$B$4</f>
-        <v>-71.3</v>
+        <v>-191.4</v>
       </c>
       <c r="O32" s="23">
         <f>O31-前提!$B$4</f>
-        <v>-76.3</v>
+        <v>-196.4</v>
       </c>
       <c r="P32" s="23">
         <f>P31-前提!$B$4</f>
-        <v>-81.3</v>
+        <v>-201.4</v>
       </c>
       <c r="Q32" s="23">
         <f>Q31-前提!$B$4</f>
-        <v>-86.3</v>
+        <v>-206.4</v>
       </c>
       <c r="R32" s="23">
         <f>R31-前提!$B$4</f>
-        <v>-91.3</v>
+        <v>-211.4</v>
       </c>
       <c r="S32" s="23" t="n"/>
     </row>
@@ -13095,59 +11147,59 @@
       </c>
       <c r="E33" s="24">
         <f>MAX(0,前提!$B$4-E31)</f>
-        <v>0.3</v>
+        <v>6.4</v>
       </c>
       <c r="F33" s="24">
         <f>MAX(0,前提!$B$4-F31)</f>
-        <v>19.3</v>
+        <v>139.4</v>
       </c>
       <c r="G33" s="24">
         <f>MAX(0,前提!$B$4-G31)</f>
-        <v>24.3</v>
+        <v>144.4</v>
       </c>
       <c r="H33" s="24">
         <f>MAX(0,前提!$B$4-H31)</f>
-        <v>29.3</v>
+        <v>149.4</v>
       </c>
       <c r="I33" s="24">
         <f>MAX(0,前提!$B$4-I31)</f>
-        <v>46.3</v>
+        <v>166.4</v>
       </c>
       <c r="J33" s="24">
         <f>MAX(0,前提!$B$4-J31)</f>
-        <v>51.3</v>
+        <v>171.4</v>
       </c>
       <c r="K33" s="24">
         <f>MAX(0,前提!$B$4-K31)</f>
-        <v>56.3</v>
+        <v>176.4</v>
       </c>
       <c r="L33" s="24">
         <f>MAX(0,前提!$B$4-L31)</f>
-        <v>61.3</v>
+        <v>181.4</v>
       </c>
       <c r="M33" s="24">
         <f>MAX(0,前提!$B$4-M31)</f>
-        <v>66.3</v>
+        <v>186.4</v>
       </c>
       <c r="N33" s="24">
         <f>MAX(0,前提!$B$4-N31)</f>
-        <v>71.3</v>
+        <v>191.4</v>
       </c>
       <c r="O33" s="24">
         <f>MAX(0,前提!$B$4-O31)</f>
-        <v>76.3</v>
+        <v>196.4</v>
       </c>
       <c r="P33" s="24">
         <f>MAX(0,前提!$B$4-P31)</f>
-        <v>81.3</v>
+        <v>201.4</v>
       </c>
       <c r="Q33" s="24">
         <f>MAX(0,前提!$B$4-Q31)</f>
-        <v>86.3</v>
+        <v>206.4</v>
       </c>
       <c r="R33" s="24">
         <f>MAX(0,前提!$B$4-R31)</f>
-        <v>91.3</v>
+        <v>211.4</v>
       </c>
       <c r="S33" s="24" t="n"/>
     </row>
@@ -13163,63 +11215,63 @@
       </c>
       <c r="D34" s="23">
         <f>-SUM($C30:D30)</f>
-        <v>55.8</v>
+        <v>56.9</v>
       </c>
       <c r="E34" s="23">
         <f>-SUM($C30:E30)</f>
-        <v>245.6</v>
+        <v>251.7</v>
       </c>
       <c r="F34" s="23">
         <f>-SUM($C30:F30)</f>
-        <v>257.6</v>
+        <v>377.7</v>
       </c>
       <c r="G34" s="23">
         <f>-SUM($C30:G30)</f>
-        <v>257.6</v>
+        <v>377.7</v>
       </c>
       <c r="H34" s="23">
         <f>-SUM($C30:H30)</f>
-        <v>257.6</v>
+        <v>377.7</v>
       </c>
       <c r="I34" s="23">
         <f>-SUM($C30:I30)</f>
-        <v>269.6</v>
+        <v>389.7</v>
       </c>
       <c r="J34" s="23">
         <f>-SUM($C30:J30)</f>
-        <v>269.6</v>
+        <v>389.7</v>
       </c>
       <c r="K34" s="23">
         <f>-SUM($C30:K30)</f>
-        <v>269.6</v>
+        <v>389.7</v>
       </c>
       <c r="L34" s="23">
         <f>-SUM($C30:L30)</f>
-        <v>269.6</v>
+        <v>389.7</v>
       </c>
       <c r="M34" s="23">
         <f>-SUM($C30:M30)</f>
-        <v>269.6</v>
+        <v>389.7</v>
       </c>
       <c r="N34" s="23">
         <f>-SUM($C30:N30)</f>
-        <v>269.6</v>
+        <v>389.7</v>
       </c>
       <c r="O34" s="23">
         <f>-SUM($C30:O30)</f>
-        <v>269.6</v>
+        <v>389.7</v>
       </c>
       <c r="P34" s="23">
         <f>-SUM($C30:P30)</f>
-        <v>269.6</v>
+        <v>389.7</v>
       </c>
       <c r="Q34" s="23">
         <f>-SUM($C30:Q30)</f>
-        <v>269.6</v>
+        <v>389.7</v>
       </c>
       <c r="R34" s="23">
         <f>-SUM($C30:R30)</f>
-        <v>269.6</v>
+        <v>389.7</v>
       </c>
       <c r="S34" s="23" t="n"/>
     </row>
@@ -13310,7 +11362,7 @@
       </c>
       <c r="B39" s="20">
         <f>-S30</f>
-        <v>269.6</v>
+        <v>389.7</v>
       </c>
     </row>
     <row r="40">
@@ -13321,7 +11373,7 @@
       </c>
       <c r="B40" s="20">
         <f>MIN(C31:R31)</f>
-        <v>8.7</v>
+        <v>-111.4</v>
       </c>
     </row>
     <row r="41">
@@ -13354,7 +11406,7 @@
       </c>
       <c r="B43" s="20">
         <f>MAX(C33:R33)</f>
-        <v>91.3</v>
+        <v>211.4</v>
       </c>
     </row>
     <row r="44">
@@ -13365,7 +11417,7 @@
       </c>
       <c r="B44" s="20">
         <f>E33</f>
-        <v>0.3</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="45">
@@ -13376,7 +11428,7 @@
       </c>
       <c r="B45" s="20">
         <f>G33</f>
-        <v>24.3</v>
+        <v>144.4</v>
       </c>
     </row>
     <row r="46">
@@ -13387,7 +11439,7 @@
       </c>
       <c r="B46" s="20">
         <f>I33</f>
-        <v>46.3</v>
+        <v>166.4</v>
       </c>
     </row>
     <row r="47">
@@ -13398,7 +11450,7 @@
       </c>
       <c r="B47" s="20">
         <f>R31</f>
-        <v>8.7</v>
+        <v>-111.4</v>
       </c>
     </row>
     <row r="48">
@@ -13409,7 +11461,7 @@
       </c>
       <c r="B48" s="25">
         <f>前提!$B$5+SUMPRODUCT($B$6:$B$14,案件一覧!$D$4:$D$12)</f>
-        <v>2143</v>
+        <v>2920</v>
       </c>
     </row>
     <row r="49">
@@ -13420,7 +11472,7 @@
       </c>
       <c r="B49" s="25">
         <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12)</f>
-        <v>142</v>
+        <v>121</v>
       </c>
     </row>
     <row r="50">
@@ -13431,7 +11483,7 @@
       </c>
       <c r="B50" s="25">
         <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$F$4:$F$12)</f>
-        <v>190</v>
+        <v>206</v>
       </c>
     </row>
     <row r="51">
@@ -13442,7 +11494,7 @@
       </c>
       <c r="B51" s="20">
         <f>SUMPRODUCT($B$6:$B$14,案件一覧!$G$4:$G$12)</f>
-        <v>44.85</v>
+        <v>127.85</v>
       </c>
     </row>
   </sheetData>
@@ -13610,7 +11662,7 @@
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -13722,59 +11774,59 @@
       </c>
       <c r="E18" s="20">
         <f>D31</f>
-        <v>302.45</v>
+        <v>301.35</v>
       </c>
       <c r="F18" s="20">
         <f>E31</f>
-        <v>230.95</v>
+        <v>224.85</v>
       </c>
       <c r="G18" s="20">
         <f>F31</f>
-        <v>142.2</v>
+        <v>22.1</v>
       </c>
       <c r="H18" s="20">
         <f>G31</f>
-        <v>137.2</v>
+        <v>17.1</v>
       </c>
       <c r="I18" s="20">
         <f>H31</f>
-        <v>132.2</v>
+        <v>12.1</v>
       </c>
       <c r="J18" s="20">
         <f>I31</f>
-        <v>115.2</v>
+        <v>-4.9</v>
       </c>
       <c r="K18" s="20">
         <f>J31</f>
-        <v>110.2</v>
+        <v>-9.9</v>
       </c>
       <c r="L18" s="20">
         <f>K31</f>
-        <v>105.2</v>
+        <v>-14.9</v>
       </c>
       <c r="M18" s="20">
         <f>L31</f>
-        <v>100.2</v>
+        <v>-19.9</v>
       </c>
       <c r="N18" s="20">
         <f>M31</f>
-        <v>95.2</v>
+        <v>-24.9</v>
       </c>
       <c r="O18" s="20">
         <f>N31</f>
-        <v>90.2</v>
+        <v>-29.9</v>
       </c>
       <c r="P18" s="20">
         <f>O31</f>
-        <v>85.2</v>
+        <v>-34.9</v>
       </c>
       <c r="Q18" s="20">
         <f>P31</f>
-        <v>80.2</v>
+        <v>-39.9</v>
       </c>
       <c r="R18" s="20">
         <f>Q31</f>
-        <v>75.2</v>
+        <v>-44.9</v>
       </c>
       <c r="S18" s="20" t="n"/>
     </row>
@@ -14472,15 +12524,15 @@
       </c>
       <c r="D29" s="23">
         <f>-$B$14*(SUMIFS(前提!$E$12:$E$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$E$12:$E$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>0.0</v>
+        <v>-1.1</v>
       </c>
       <c r="E29" s="23">
         <f>-$B$14*(SUMIFS(前提!$F$12:$F$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$F$12:$F$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>0.0</v>
+        <v>-5.0</v>
       </c>
       <c r="F29" s="23">
         <f>-$B$14*(SUMIFS(前提!$G$12:$G$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$G$12:$G$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>0.0</v>
+        <v>-114.0</v>
       </c>
       <c r="G29" s="23">
         <f>-$B$14*(SUMIFS(前提!$H$12:$H$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$H$12:$H$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
@@ -14532,7 +12584,7 @@
       </c>
       <c r="S29" s="23">
         <f>SUM(C29:R29)</f>
-        <v>0.0</v>
+        <v>-120.1</v>
       </c>
     </row>
     <row r="30">
@@ -14547,15 +12599,15 @@
       </c>
       <c r="D30" s="20">
         <f>SUM(D21:D29)</f>
-        <v>-19.85</v>
+        <v>-20.95</v>
       </c>
       <c r="E30" s="20">
         <f>SUM(E21:E29)</f>
-        <v>-64.5</v>
+        <v>-69.5</v>
       </c>
       <c r="F30" s="20">
         <f>SUM(F21:F29)</f>
-        <v>-81.75</v>
+        <v>-195.75</v>
       </c>
       <c r="G30" s="20">
         <f>SUM(G21:G29)</f>
@@ -14607,7 +12659,7 @@
       </c>
       <c r="S30" s="20">
         <f>SUM(C30:R30)</f>
-        <v>-208.1</v>
+        <v>-328.2</v>
       </c>
     </row>
     <row r="31">
@@ -14622,63 +12674,63 @@
       </c>
       <c r="D31" s="21">
         <f>D18+D19+D30</f>
-        <v>302.45</v>
+        <v>301.35</v>
       </c>
       <c r="E31" s="21">
         <f>E18+E19+E30</f>
-        <v>230.95</v>
+        <v>224.85</v>
       </c>
       <c r="F31" s="21">
         <f>F18+F19+F30</f>
-        <v>142.2</v>
+        <v>22.1</v>
       </c>
       <c r="G31" s="21">
         <f>G18+G19+G30</f>
-        <v>137.2</v>
+        <v>17.1</v>
       </c>
       <c r="H31" s="21">
         <f>H18+H19+H30</f>
-        <v>132.2</v>
+        <v>12.1</v>
       </c>
       <c r="I31" s="21">
         <f>I18+I19+I30</f>
-        <v>115.2</v>
+        <v>-4.9</v>
       </c>
       <c r="J31" s="21">
         <f>J18+J19+J30</f>
-        <v>110.2</v>
+        <v>-9.9</v>
       </c>
       <c r="K31" s="21">
         <f>K18+K19+K30</f>
-        <v>105.2</v>
+        <v>-14.9</v>
       </c>
       <c r="L31" s="21">
         <f>L18+L19+L30</f>
-        <v>100.2</v>
+        <v>-19.9</v>
       </c>
       <c r="M31" s="21">
         <f>M18+M19+M30</f>
-        <v>95.2</v>
+        <v>-24.9</v>
       </c>
       <c r="N31" s="21">
         <f>N18+N19+N30</f>
-        <v>90.2</v>
+        <v>-29.9</v>
       </c>
       <c r="O31" s="21">
         <f>O18+O19+O30</f>
-        <v>85.2</v>
+        <v>-34.9</v>
       </c>
       <c r="P31" s="21">
         <f>P18+P19+P30</f>
-        <v>80.2</v>
+        <v>-39.9</v>
       </c>
       <c r="Q31" s="21">
         <f>Q18+Q19+Q30</f>
-        <v>75.2</v>
+        <v>-44.9</v>
       </c>
       <c r="R31" s="21">
         <f>R18+R19+R30</f>
-        <v>70.2</v>
+        <v>-49.9</v>
       </c>
       <c r="S31" s="21" t="n"/>
     </row>
@@ -14694,63 +12746,63 @@
       </c>
       <c r="D32" s="23">
         <f>D31-前提!$B$4</f>
-        <v>202.45</v>
+        <v>201.35</v>
       </c>
       <c r="E32" s="23">
         <f>E31-前提!$B$4</f>
-        <v>130.95</v>
+        <v>124.85</v>
       </c>
       <c r="F32" s="23">
         <f>F31-前提!$B$4</f>
-        <v>42.2</v>
+        <v>-77.9</v>
       </c>
       <c r="G32" s="23">
         <f>G31-前提!$B$4</f>
-        <v>37.2</v>
+        <v>-82.9</v>
       </c>
       <c r="H32" s="23">
         <f>H31-前提!$B$4</f>
-        <v>32.2</v>
+        <v>-87.9</v>
       </c>
       <c r="I32" s="23">
         <f>I31-前提!$B$4</f>
-        <v>15.2</v>
+        <v>-104.9</v>
       </c>
       <c r="J32" s="23">
         <f>J31-前提!$B$4</f>
-        <v>10.2</v>
+        <v>-109.9</v>
       </c>
       <c r="K32" s="23">
         <f>K31-前提!$B$4</f>
-        <v>5.2</v>
+        <v>-114.9</v>
       </c>
       <c r="L32" s="23">
         <f>L31-前提!$B$4</f>
-        <v>0.2</v>
+        <v>-119.9</v>
       </c>
       <c r="M32" s="23">
         <f>M31-前提!$B$4</f>
-        <v>-4.8</v>
+        <v>-124.9</v>
       </c>
       <c r="N32" s="23">
         <f>N31-前提!$B$4</f>
-        <v>-9.8</v>
+        <v>-129.9</v>
       </c>
       <c r="O32" s="23">
         <f>O31-前提!$B$4</f>
-        <v>-14.8</v>
+        <v>-134.9</v>
       </c>
       <c r="P32" s="23">
         <f>P31-前提!$B$4</f>
-        <v>-19.8</v>
+        <v>-139.9</v>
       </c>
       <c r="Q32" s="23">
         <f>Q31-前提!$B$4</f>
-        <v>-24.8</v>
+        <v>-144.9</v>
       </c>
       <c r="R32" s="23">
         <f>R31-前提!$B$4</f>
-        <v>-29.8</v>
+        <v>-149.9</v>
       </c>
       <c r="S32" s="23" t="n"/>
     </row>
@@ -14774,55 +12826,55 @@
       </c>
       <c r="F33" s="24">
         <f>MAX(0,前提!$B$4-F31)</f>
-        <v>0</v>
+        <v>77.9</v>
       </c>
       <c r="G33" s="24">
         <f>MAX(0,前提!$B$4-G31)</f>
-        <v>0</v>
+        <v>82.9</v>
       </c>
       <c r="H33" s="24">
         <f>MAX(0,前提!$B$4-H31)</f>
-        <v>0</v>
+        <v>87.9</v>
       </c>
       <c r="I33" s="24">
         <f>MAX(0,前提!$B$4-I31)</f>
-        <v>0</v>
+        <v>104.9</v>
       </c>
       <c r="J33" s="24">
         <f>MAX(0,前提!$B$4-J31)</f>
-        <v>0</v>
+        <v>109.9</v>
       </c>
       <c r="K33" s="24">
         <f>MAX(0,前提!$B$4-K31)</f>
-        <v>0</v>
+        <v>114.9</v>
       </c>
       <c r="L33" s="24">
         <f>MAX(0,前提!$B$4-L31)</f>
-        <v>0</v>
+        <v>119.9</v>
       </c>
       <c r="M33" s="24">
         <f>MAX(0,前提!$B$4-M31)</f>
-        <v>4.8</v>
+        <v>124.9</v>
       </c>
       <c r="N33" s="24">
         <f>MAX(0,前提!$B$4-N31)</f>
-        <v>9.8</v>
+        <v>129.9</v>
       </c>
       <c r="O33" s="24">
         <f>MAX(0,前提!$B$4-O31)</f>
-        <v>14.8</v>
+        <v>134.9</v>
       </c>
       <c r="P33" s="24">
         <f>MAX(0,前提!$B$4-P31)</f>
-        <v>19.8</v>
+        <v>139.9</v>
       </c>
       <c r="Q33" s="24">
         <f>MAX(0,前提!$B$4-Q31)</f>
-        <v>24.8</v>
+        <v>144.9</v>
       </c>
       <c r="R33" s="24">
         <f>MAX(0,前提!$B$4-R31)</f>
-        <v>29.8</v>
+        <v>149.9</v>
       </c>
       <c r="S33" s="24" t="n"/>
     </row>
@@ -14838,63 +12890,63 @@
       </c>
       <c r="D34" s="23">
         <f>-SUM($C30:D30)</f>
-        <v>49.85</v>
+        <v>50.95</v>
       </c>
       <c r="E34" s="23">
         <f>-SUM($C30:E30)</f>
-        <v>114.35</v>
+        <v>120.45</v>
       </c>
       <c r="F34" s="23">
         <f>-SUM($C30:F30)</f>
-        <v>196.1</v>
+        <v>316.2</v>
       </c>
       <c r="G34" s="23">
         <f>-SUM($C30:G30)</f>
-        <v>196.1</v>
+        <v>316.2</v>
       </c>
       <c r="H34" s="23">
         <f>-SUM($C30:H30)</f>
-        <v>196.1</v>
+        <v>316.2</v>
       </c>
       <c r="I34" s="23">
         <f>-SUM($C30:I30)</f>
-        <v>208.1</v>
+        <v>328.2</v>
       </c>
       <c r="J34" s="23">
         <f>-SUM($C30:J30)</f>
-        <v>208.1</v>
+        <v>328.2</v>
       </c>
       <c r="K34" s="23">
         <f>-SUM($C30:K30)</f>
-        <v>208.1</v>
+        <v>328.2</v>
       </c>
       <c r="L34" s="23">
         <f>-SUM($C30:L30)</f>
-        <v>208.1</v>
+        <v>328.2</v>
       </c>
       <c r="M34" s="23">
         <f>-SUM($C30:M30)</f>
-        <v>208.1</v>
+        <v>328.2</v>
       </c>
       <c r="N34" s="23">
         <f>-SUM($C30:N30)</f>
-        <v>208.1</v>
+        <v>328.2</v>
       </c>
       <c r="O34" s="23">
         <f>-SUM($C30:O30)</f>
-        <v>208.1</v>
+        <v>328.2</v>
       </c>
       <c r="P34" s="23">
         <f>-SUM($C30:P30)</f>
-        <v>208.1</v>
+        <v>328.2</v>
       </c>
       <c r="Q34" s="23">
         <f>-SUM($C30:Q30)</f>
-        <v>208.1</v>
+        <v>328.2</v>
       </c>
       <c r="R34" s="23">
         <f>-SUM($C30:R30)</f>
-        <v>208.1</v>
+        <v>328.2</v>
       </c>
       <c r="S34" s="23" t="n"/>
     </row>
@@ -14918,31 +12970,31 @@
       </c>
       <c r="F35" s="23">
         <f>IF(F31&lt;前提!$B$4,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" s="23">
         <f>IF(G31&lt;前提!$B$4,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" s="23">
         <f>IF(H31&lt;前提!$B$4,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" s="23">
         <f>IF(I31&lt;前提!$B$4,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="23">
         <f>IF(J31&lt;前提!$B$4,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" s="23">
         <f>IF(K31&lt;前提!$B$4,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="23">
         <f>IF(L31&lt;前提!$B$4,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="23">
         <f>IF(M31&lt;前提!$B$4,1,0)</f>
@@ -14985,7 +13037,7 @@
       </c>
       <c r="B39" s="20">
         <f>-S30</f>
-        <v>208.1</v>
+        <v>328.2</v>
       </c>
     </row>
     <row r="40">
@@ -14996,7 +13048,7 @@
       </c>
       <c r="B40" s="20">
         <f>MIN(C31:R31)</f>
-        <v>70.2</v>
+        <v>-49.9</v>
       </c>
     </row>
     <row r="41">
@@ -15018,7 +13070,7 @@
       </c>
       <c r="B42" s="4" t="str">
         <f>IFERROR(INDEX($C$17:$R$17,MATCH(1,C35:R35,0)),"—")</f>
-        <v>2027/7</v>
+        <v>2026/12</v>
       </c>
     </row>
     <row r="43">
@@ -15029,7 +13081,7 @@
       </c>
       <c r="B43" s="20">
         <f>MAX(C33:R33)</f>
-        <v>29.8</v>
+        <v>149.9</v>
       </c>
     </row>
     <row r="44">
@@ -15051,7 +13103,7 @@
       </c>
       <c r="B45" s="20">
         <f>G33</f>
-        <v>0</v>
+        <v>82.9</v>
       </c>
     </row>
     <row r="46">
@@ -15062,7 +13114,7 @@
       </c>
       <c r="B46" s="20">
         <f>I33</f>
-        <v>0</v>
+        <v>104.9</v>
       </c>
     </row>
     <row r="47">
@@ -15073,7 +13125,7 @@
       </c>
       <c r="B47" s="20">
         <f>R31</f>
-        <v>70.2</v>
+        <v>-49.9</v>
       </c>
     </row>
     <row r="48">
@@ -15084,7 +13136,7 @@
       </c>
       <c r="B48" s="25">
         <f>前提!$B$5+SUMPRODUCT($B$6:$B$14,案件一覧!$D$4:$D$12)</f>
-        <v>2108</v>
+        <v>2885</v>
       </c>
     </row>
     <row r="49">
@@ -15095,7 +13147,7 @@
       </c>
       <c r="B49" s="25">
         <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12)</f>
-        <v>124</v>
+        <v>103</v>
       </c>
     </row>
     <row r="50">
@@ -15106,7 +13158,7 @@
       </c>
       <c r="B50" s="25">
         <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$F$4:$F$12)</f>
-        <v>149</v>
+        <v>165</v>
       </c>
     </row>
     <row r="51">
@@ -15117,7 +13169,7 @@
       </c>
       <c r="B51" s="20">
         <f>SUMPRODUCT($B$6:$B$14,案件一覧!$G$4:$G$12)</f>
-        <v>105.25</v>
+        <v>188.25</v>
       </c>
     </row>
   </sheetData>
@@ -15285,7 +13337,7 @@
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -15397,59 +13449,59 @@
       </c>
       <c r="E18" s="20">
         <f>D31</f>
-        <v>293.75</v>
+        <v>292.65</v>
       </c>
       <c r="F18" s="20">
         <f>E31</f>
-        <v>94.95</v>
+        <v>88.85</v>
       </c>
       <c r="G18" s="20">
         <f>F31</f>
-        <v>6.2</v>
+        <v>-113.9</v>
       </c>
       <c r="H18" s="20">
         <f>G31</f>
-        <v>1.2</v>
+        <v>-118.9</v>
       </c>
       <c r="I18" s="20">
         <f>H31</f>
-        <v>-3.8</v>
+        <v>-123.9</v>
       </c>
       <c r="J18" s="20">
         <f>I31</f>
-        <v>-20.8</v>
+        <v>-140.9</v>
       </c>
       <c r="K18" s="20">
         <f>J31</f>
-        <v>-25.8</v>
+        <v>-145.9</v>
       </c>
       <c r="L18" s="20">
         <f>K31</f>
-        <v>-30.8</v>
+        <v>-150.9</v>
       </c>
       <c r="M18" s="20">
         <f>L31</f>
-        <v>-35.8</v>
+        <v>-155.9</v>
       </c>
       <c r="N18" s="20">
         <f>M31</f>
-        <v>-40.8</v>
+        <v>-160.9</v>
       </c>
       <c r="O18" s="20">
         <f>N31</f>
-        <v>-45.8</v>
+        <v>-165.9</v>
       </c>
       <c r="P18" s="20">
         <f>O31</f>
-        <v>-50.8</v>
+        <v>-170.9</v>
       </c>
       <c r="Q18" s="20">
         <f>P31</f>
-        <v>-55.8</v>
+        <v>-175.9</v>
       </c>
       <c r="R18" s="20">
         <f>Q31</f>
-        <v>-60.8</v>
+        <v>-180.9</v>
       </c>
       <c r="S18" s="20" t="n"/>
     </row>
@@ -16147,15 +14199,15 @@
       </c>
       <c r="D29" s="23">
         <f>-$B$14*(SUMIFS(前提!$E$12:$E$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$E$12:$E$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>0.0</v>
+        <v>-1.1</v>
       </c>
       <c r="E29" s="23">
         <f>-$B$14*(SUMIFS(前提!$F$12:$F$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$F$12:$F$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>0.0</v>
+        <v>-5.0</v>
       </c>
       <c r="F29" s="23">
         <f>-$B$14*(SUMIFS(前提!$G$12:$G$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$G$12:$G$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>0.0</v>
+        <v>-114.0</v>
       </c>
       <c r="G29" s="23">
         <f>-$B$14*(SUMIFS(前提!$H$12:$H$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$H$12:$H$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
@@ -16207,7 +14259,7 @@
       </c>
       <c r="S29" s="23">
         <f>SUM(C29:R29)</f>
-        <v>0.0</v>
+        <v>-120.1</v>
       </c>
     </row>
     <row r="30">
@@ -16222,15 +14274,15 @@
       </c>
       <c r="D30" s="20">
         <f>SUM(D21:D29)</f>
-        <v>-28.55</v>
+        <v>-29.65</v>
       </c>
       <c r="E30" s="20">
         <f>SUM(E21:E29)</f>
-        <v>-191.8</v>
+        <v>-196.8</v>
       </c>
       <c r="F30" s="20">
         <f>SUM(F21:F29)</f>
-        <v>-81.75</v>
+        <v>-195.75</v>
       </c>
       <c r="G30" s="20">
         <f>SUM(G21:G29)</f>
@@ -16282,7 +14334,7 @@
       </c>
       <c r="S30" s="20">
         <f>SUM(C30:R30)</f>
-        <v>-344.1</v>
+        <v>-464.2</v>
       </c>
     </row>
     <row r="31">
@@ -16297,63 +14349,63 @@
       </c>
       <c r="D31" s="21">
         <f>D18+D19+D30</f>
-        <v>293.75</v>
+        <v>292.65</v>
       </c>
       <c r="E31" s="21">
         <f>E18+E19+E30</f>
-        <v>94.95</v>
+        <v>88.85</v>
       </c>
       <c r="F31" s="21">
         <f>F18+F19+F30</f>
-        <v>6.2</v>
+        <v>-113.9</v>
       </c>
       <c r="G31" s="21">
         <f>G18+G19+G30</f>
-        <v>1.2</v>
+        <v>-118.9</v>
       </c>
       <c r="H31" s="21">
         <f>H18+H19+H30</f>
-        <v>-3.8</v>
+        <v>-123.9</v>
       </c>
       <c r="I31" s="21">
         <f>I18+I19+I30</f>
-        <v>-20.8</v>
+        <v>-140.9</v>
       </c>
       <c r="J31" s="21">
         <f>J18+J19+J30</f>
-        <v>-25.8</v>
+        <v>-145.9</v>
       </c>
       <c r="K31" s="21">
         <f>K18+K19+K30</f>
-        <v>-30.8</v>
+        <v>-150.9</v>
       </c>
       <c r="L31" s="21">
         <f>L18+L19+L30</f>
-        <v>-35.8</v>
+        <v>-155.9</v>
       </c>
       <c r="M31" s="21">
         <f>M18+M19+M30</f>
-        <v>-40.8</v>
+        <v>-160.9</v>
       </c>
       <c r="N31" s="21">
         <f>N18+N19+N30</f>
-        <v>-45.8</v>
+        <v>-165.9</v>
       </c>
       <c r="O31" s="21">
         <f>O18+O19+O30</f>
-        <v>-50.8</v>
+        <v>-170.9</v>
       </c>
       <c r="P31" s="21">
         <f>P18+P19+P30</f>
-        <v>-55.8</v>
+        <v>-175.9</v>
       </c>
       <c r="Q31" s="21">
         <f>Q18+Q19+Q30</f>
-        <v>-60.8</v>
+        <v>-180.9</v>
       </c>
       <c r="R31" s="21">
         <f>R18+R19+R30</f>
-        <v>-65.8</v>
+        <v>-185.9</v>
       </c>
       <c r="S31" s="21" t="n"/>
     </row>
@@ -16369,63 +14421,63 @@
       </c>
       <c r="D32" s="23">
         <f>D31-前提!$B$4</f>
-        <v>193.75</v>
+        <v>192.65</v>
       </c>
       <c r="E32" s="23">
         <f>E31-前提!$B$4</f>
-        <v>-5.05</v>
+        <v>-11.15</v>
       </c>
       <c r="F32" s="23">
         <f>F31-前提!$B$4</f>
-        <v>-93.8</v>
+        <v>-213.9</v>
       </c>
       <c r="G32" s="23">
         <f>G31-前提!$B$4</f>
-        <v>-98.8</v>
+        <v>-218.9</v>
       </c>
       <c r="H32" s="23">
         <f>H31-前提!$B$4</f>
-        <v>-103.8</v>
+        <v>-223.9</v>
       </c>
       <c r="I32" s="23">
         <f>I31-前提!$B$4</f>
-        <v>-120.8</v>
+        <v>-240.9</v>
       </c>
       <c r="J32" s="23">
         <f>J31-前提!$B$4</f>
-        <v>-125.8</v>
+        <v>-245.9</v>
       </c>
       <c r="K32" s="23">
         <f>K31-前提!$B$4</f>
-        <v>-130.8</v>
+        <v>-250.9</v>
       </c>
       <c r="L32" s="23">
         <f>L31-前提!$B$4</f>
-        <v>-135.8</v>
+        <v>-255.9</v>
       </c>
       <c r="M32" s="23">
         <f>M31-前提!$B$4</f>
-        <v>-140.8</v>
+        <v>-260.9</v>
       </c>
       <c r="N32" s="23">
         <f>N31-前提!$B$4</f>
-        <v>-145.8</v>
+        <v>-265.9</v>
       </c>
       <c r="O32" s="23">
         <f>O31-前提!$B$4</f>
-        <v>-150.8</v>
+        <v>-270.9</v>
       </c>
       <c r="P32" s="23">
         <f>P31-前提!$B$4</f>
-        <v>-155.8</v>
+        <v>-275.9</v>
       </c>
       <c r="Q32" s="23">
         <f>Q31-前提!$B$4</f>
-        <v>-160.8</v>
+        <v>-280.9</v>
       </c>
       <c r="R32" s="23">
         <f>R31-前提!$B$4</f>
-        <v>-165.8</v>
+        <v>-285.9</v>
       </c>
       <c r="S32" s="23" t="n"/>
     </row>
@@ -16445,59 +14497,59 @@
       </c>
       <c r="E33" s="24">
         <f>MAX(0,前提!$B$4-E31)</f>
-        <v>5.05</v>
+        <v>11.15</v>
       </c>
       <c r="F33" s="24">
         <f>MAX(0,前提!$B$4-F31)</f>
-        <v>93.8</v>
+        <v>213.9</v>
       </c>
       <c r="G33" s="24">
         <f>MAX(0,前提!$B$4-G31)</f>
-        <v>98.8</v>
+        <v>218.9</v>
       </c>
       <c r="H33" s="24">
         <f>MAX(0,前提!$B$4-H31)</f>
-        <v>103.8</v>
+        <v>223.9</v>
       </c>
       <c r="I33" s="24">
         <f>MAX(0,前提!$B$4-I31)</f>
-        <v>120.8</v>
+        <v>240.9</v>
       </c>
       <c r="J33" s="24">
         <f>MAX(0,前提!$B$4-J31)</f>
-        <v>125.8</v>
+        <v>245.9</v>
       </c>
       <c r="K33" s="24">
         <f>MAX(0,前提!$B$4-K31)</f>
-        <v>130.8</v>
+        <v>250.9</v>
       </c>
       <c r="L33" s="24">
         <f>MAX(0,前提!$B$4-L31)</f>
-        <v>135.8</v>
+        <v>255.9</v>
       </c>
       <c r="M33" s="24">
         <f>MAX(0,前提!$B$4-M31)</f>
-        <v>140.8</v>
+        <v>260.9</v>
       </c>
       <c r="N33" s="24">
         <f>MAX(0,前提!$B$4-N31)</f>
-        <v>145.8</v>
+        <v>265.9</v>
       </c>
       <c r="O33" s="24">
         <f>MAX(0,前提!$B$4-O31)</f>
-        <v>150.8</v>
+        <v>270.9</v>
       </c>
       <c r="P33" s="24">
         <f>MAX(0,前提!$B$4-P31)</f>
-        <v>155.8</v>
+        <v>275.9</v>
       </c>
       <c r="Q33" s="24">
         <f>MAX(0,前提!$B$4-Q31)</f>
-        <v>160.8</v>
+        <v>280.9</v>
       </c>
       <c r="R33" s="24">
         <f>MAX(0,前提!$B$4-R31)</f>
-        <v>165.8</v>
+        <v>285.9</v>
       </c>
       <c r="S33" s="24" t="n"/>
     </row>
@@ -16513,63 +14565,63 @@
       </c>
       <c r="D34" s="23">
         <f>-SUM($C30:D30)</f>
-        <v>58.55</v>
+        <v>59.65</v>
       </c>
       <c r="E34" s="23">
         <f>-SUM($C30:E30)</f>
-        <v>250.35</v>
+        <v>256.45</v>
       </c>
       <c r="F34" s="23">
         <f>-SUM($C30:F30)</f>
-        <v>332.1</v>
+        <v>452.2</v>
       </c>
       <c r="G34" s="23">
         <f>-SUM($C30:G30)</f>
-        <v>332.1</v>
+        <v>452.2</v>
       </c>
       <c r="H34" s="23">
         <f>-SUM($C30:H30)</f>
-        <v>332.1</v>
+        <v>452.2</v>
       </c>
       <c r="I34" s="23">
         <f>-SUM($C30:I30)</f>
-        <v>344.1</v>
+        <v>464.2</v>
       </c>
       <c r="J34" s="23">
         <f>-SUM($C30:J30)</f>
-        <v>344.1</v>
+        <v>464.2</v>
       </c>
       <c r="K34" s="23">
         <f>-SUM($C30:K30)</f>
-        <v>344.1</v>
+        <v>464.2</v>
       </c>
       <c r="L34" s="23">
         <f>-SUM($C30:L30)</f>
-        <v>344.1</v>
+        <v>464.2</v>
       </c>
       <c r="M34" s="23">
         <f>-SUM($C30:M30)</f>
-        <v>344.1</v>
+        <v>464.2</v>
       </c>
       <c r="N34" s="23">
         <f>-SUM($C30:N30)</f>
-        <v>344.1</v>
+        <v>464.2</v>
       </c>
       <c r="O34" s="23">
         <f>-SUM($C30:O30)</f>
-        <v>344.1</v>
+        <v>464.2</v>
       </c>
       <c r="P34" s="23">
         <f>-SUM($C30:P30)</f>
-        <v>344.1</v>
+        <v>464.2</v>
       </c>
       <c r="Q34" s="23">
         <f>-SUM($C30:Q30)</f>
-        <v>344.1</v>
+        <v>464.2</v>
       </c>
       <c r="R34" s="23">
         <f>-SUM($C30:R30)</f>
-        <v>344.1</v>
+        <v>464.2</v>
       </c>
       <c r="S34" s="23" t="n"/>
     </row>
@@ -16660,7 +14712,7 @@
       </c>
       <c r="B39" s="20">
         <f>-S30</f>
-        <v>344.1</v>
+        <v>464.2</v>
       </c>
     </row>
     <row r="40">
@@ -16671,7 +14723,7 @@
       </c>
       <c r="B40" s="20">
         <f>MIN(C31:R31)</f>
-        <v>-65.8</v>
+        <v>-185.9</v>
       </c>
     </row>
     <row r="41">
@@ -16704,7 +14756,7 @@
       </c>
       <c r="B43" s="20">
         <f>MAX(C33:R33)</f>
-        <v>165.8</v>
+        <v>285.9</v>
       </c>
     </row>
     <row r="44">
@@ -16715,7 +14767,7 @@
       </c>
       <c r="B44" s="20">
         <f>E33</f>
-        <v>5.05</v>
+        <v>11.15</v>
       </c>
     </row>
     <row r="45">
@@ -16726,7 +14778,7 @@
       </c>
       <c r="B45" s="20">
         <f>G33</f>
-        <v>98.8</v>
+        <v>218.9</v>
       </c>
     </row>
     <row r="46">
@@ -16737,7 +14789,7 @@
       </c>
       <c r="B46" s="20">
         <f>I33</f>
-        <v>120.8</v>
+        <v>240.9</v>
       </c>
     </row>
     <row r="47">
@@ -16748,7 +14800,7 @@
       </c>
       <c r="B47" s="20">
         <f>R31</f>
-        <v>-65.8</v>
+        <v>-185.9</v>
       </c>
     </row>
     <row r="48">
@@ -16759,7 +14811,7 @@
       </c>
       <c r="B48" s="25">
         <f>前提!$B$5+SUMPRODUCT($B$6:$B$14,案件一覧!$D$4:$D$12)</f>
-        <v>2593</v>
+        <v>3370</v>
       </c>
     </row>
     <row r="49">
@@ -16770,7 +14822,7 @@
       </c>
       <c r="B49" s="25">
         <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12)</f>
-        <v>162</v>
+        <v>141</v>
       </c>
     </row>
     <row r="50">
@@ -16781,7 +14833,7 @@
       </c>
       <c r="B50" s="25">
         <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$F$4:$F$12)</f>
-        <v>215</v>
+        <v>231</v>
       </c>
     </row>
     <row r="51">
@@ -16792,7 +14844,7 @@
       </c>
       <c r="B51" s="20">
         <f>SUMPRODUCT($B$6:$B$14,案件一覧!$G$4:$G$12)</f>
-        <v>105.25</v>
+        <v>188.25</v>
       </c>
     </row>
   </sheetData>
@@ -16960,7 +15012,7 @@
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -17072,59 +15124,59 @@
       </c>
       <c r="E18" s="20">
         <f>D31</f>
-        <v>293.75</v>
+        <v>292.65</v>
       </c>
       <c r="F18" s="20">
         <f>E31</f>
-        <v>94.95</v>
+        <v>88.85</v>
       </c>
       <c r="G18" s="20">
         <f>F31</f>
-        <v>1.45</v>
+        <v>-118.65</v>
       </c>
       <c r="H18" s="20">
         <f>G31</f>
-        <v>-91.3</v>
+        <v>-211.4</v>
       </c>
       <c r="I18" s="20">
         <f>H31</f>
-        <v>-98.4</v>
+        <v>-218.5</v>
       </c>
       <c r="J18" s="20">
         <f>I31</f>
-        <v>-170.9</v>
+        <v>-291.0</v>
       </c>
       <c r="K18" s="20">
         <f>J31</f>
-        <v>-175.9</v>
+        <v>-296.0</v>
       </c>
       <c r="L18" s="20">
         <f>K31</f>
-        <v>-180.9</v>
+        <v>-301.0</v>
       </c>
       <c r="M18" s="20">
         <f>L31</f>
-        <v>-185.9</v>
+        <v>-306.0</v>
       </c>
       <c r="N18" s="20">
         <f>M31</f>
-        <v>-190.9</v>
+        <v>-311.0</v>
       </c>
       <c r="O18" s="20">
         <f>N31</f>
-        <v>-195.9</v>
+        <v>-316.0</v>
       </c>
       <c r="P18" s="20">
         <f>O31</f>
-        <v>-200.9</v>
+        <v>-321.0</v>
       </c>
       <c r="Q18" s="20">
         <f>P31</f>
-        <v>-205.9</v>
+        <v>-326.0</v>
       </c>
       <c r="R18" s="20">
         <f>Q31</f>
-        <v>-210.9</v>
+        <v>-331.0</v>
       </c>
       <c r="S18" s="20" t="n"/>
     </row>
@@ -17822,15 +15874,15 @@
       </c>
       <c r="D29" s="23">
         <f>-$B$14*(SUMIFS(前提!$E$12:$E$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$E$12:$E$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>0.0</v>
+        <v>-1.1</v>
       </c>
       <c r="E29" s="23">
         <f>-$B$14*(SUMIFS(前提!$F$12:$F$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$F$12:$F$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>0.0</v>
+        <v>-5.0</v>
       </c>
       <c r="F29" s="23">
         <f>-$B$14*(SUMIFS(前提!$G$12:$G$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$G$12:$G$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
-        <v>0.0</v>
+        <v>-114.0</v>
       </c>
       <c r="G29" s="23">
         <f>-$B$14*(SUMIFS(前提!$H$12:$H$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,"共通")+SUMIFS(前提!$H$12:$H$51,前提!$A$12:$A$51,TRIM($A29),前提!$C$12:$C$51,$B$3))</f>
@@ -17882,7 +15934,7 @@
       </c>
       <c r="S29" s="23">
         <f>SUM(C29:R29)</f>
-        <v>0.0</v>
+        <v>-120.1</v>
       </c>
     </row>
     <row r="30">
@@ -17897,15 +15949,15 @@
       </c>
       <c r="D30" s="20">
         <f>SUM(D21:D29)</f>
-        <v>-28.55</v>
+        <v>-29.65</v>
       </c>
       <c r="E30" s="20">
         <f>SUM(E21:E29)</f>
-        <v>-191.8</v>
+        <v>-196.8</v>
       </c>
       <c r="F30" s="20">
         <f>SUM(F21:F29)</f>
-        <v>-86.5</v>
+        <v>-200.5</v>
       </c>
       <c r="G30" s="20">
         <f>SUM(G21:G29)</f>
@@ -17957,7 +16009,7 @@
       </c>
       <c r="S30" s="20">
         <f>SUM(C30:R30)</f>
-        <v>-494.2</v>
+        <v>-614.3</v>
       </c>
     </row>
     <row r="31">
@@ -17972,63 +16024,63 @@
       </c>
       <c r="D31" s="21">
         <f>D18+D19+D30</f>
-        <v>293.75</v>
+        <v>292.65</v>
       </c>
       <c r="E31" s="21">
         <f>E18+E19+E30</f>
-        <v>94.95</v>
+        <v>88.85</v>
       </c>
       <c r="F31" s="21">
         <f>F18+F19+F30</f>
-        <v>1.45</v>
+        <v>-118.65</v>
       </c>
       <c r="G31" s="21">
         <f>G18+G19+G30</f>
-        <v>-91.3</v>
+        <v>-211.4</v>
       </c>
       <c r="H31" s="21">
         <f>H18+H19+H30</f>
-        <v>-98.4</v>
+        <v>-218.5</v>
       </c>
       <c r="I31" s="21">
         <f>I18+I19+I30</f>
-        <v>-170.9</v>
+        <v>-291.0</v>
       </c>
       <c r="J31" s="21">
         <f>J18+J19+J30</f>
-        <v>-175.9</v>
+        <v>-296.0</v>
       </c>
       <c r="K31" s="21">
         <f>K18+K19+K30</f>
-        <v>-180.9</v>
+        <v>-301.0</v>
       </c>
       <c r="L31" s="21">
         <f>L18+L19+L30</f>
-        <v>-185.9</v>
+        <v>-306.0</v>
       </c>
       <c r="M31" s="21">
         <f>M18+M19+M30</f>
-        <v>-190.9</v>
+        <v>-311.0</v>
       </c>
       <c r="N31" s="21">
         <f>N18+N19+N30</f>
-        <v>-195.9</v>
+        <v>-316.0</v>
       </c>
       <c r="O31" s="21">
         <f>O18+O19+O30</f>
-        <v>-200.9</v>
+        <v>-321.0</v>
       </c>
       <c r="P31" s="21">
         <f>P18+P19+P30</f>
-        <v>-205.9</v>
+        <v>-326.0</v>
       </c>
       <c r="Q31" s="21">
         <f>Q18+Q19+Q30</f>
-        <v>-210.9</v>
+        <v>-331.0</v>
       </c>
       <c r="R31" s="21">
         <f>R18+R19+R30</f>
-        <v>-215.9</v>
+        <v>-336.0</v>
       </c>
       <c r="S31" s="21" t="n"/>
     </row>
@@ -18044,63 +16096,63 @@
       </c>
       <c r="D32" s="23">
         <f>D31-前提!$B$4</f>
-        <v>193.75</v>
+        <v>192.65</v>
       </c>
       <c r="E32" s="23">
         <f>E31-前提!$B$4</f>
-        <v>-5.05</v>
+        <v>-11.15</v>
       </c>
       <c r="F32" s="23">
         <f>F31-前提!$B$4</f>
-        <v>-98.55</v>
+        <v>-218.65</v>
       </c>
       <c r="G32" s="23">
         <f>G31-前提!$B$4</f>
-        <v>-191.3</v>
+        <v>-311.4</v>
       </c>
       <c r="H32" s="23">
         <f>H31-前提!$B$4</f>
-        <v>-198.4</v>
+        <v>-318.5</v>
       </c>
       <c r="I32" s="23">
         <f>I31-前提!$B$4</f>
-        <v>-270.9</v>
+        <v>-391.0</v>
       </c>
       <c r="J32" s="23">
         <f>J31-前提!$B$4</f>
-        <v>-275.9</v>
+        <v>-396.0</v>
       </c>
       <c r="K32" s="23">
         <f>K31-前提!$B$4</f>
-        <v>-280.9</v>
+        <v>-401.0</v>
       </c>
       <c r="L32" s="23">
         <f>L31-前提!$B$4</f>
-        <v>-285.9</v>
+        <v>-406.0</v>
       </c>
       <c r="M32" s="23">
         <f>M31-前提!$B$4</f>
-        <v>-290.9</v>
+        <v>-411.0</v>
       </c>
       <c r="N32" s="23">
         <f>N31-前提!$B$4</f>
-        <v>-295.9</v>
+        <v>-416.0</v>
       </c>
       <c r="O32" s="23">
         <f>O31-前提!$B$4</f>
-        <v>-300.9</v>
+        <v>-421.0</v>
       </c>
       <c r="P32" s="23">
         <f>P31-前提!$B$4</f>
-        <v>-305.9</v>
+        <v>-426.0</v>
       </c>
       <c r="Q32" s="23">
         <f>Q31-前提!$B$4</f>
-        <v>-310.9</v>
+        <v>-431.0</v>
       </c>
       <c r="R32" s="23">
         <f>R31-前提!$B$4</f>
-        <v>-315.9</v>
+        <v>-436.0</v>
       </c>
       <c r="S32" s="23" t="n"/>
     </row>
@@ -18120,59 +16172,59 @@
       </c>
       <c r="E33" s="24">
         <f>MAX(0,前提!$B$4-E31)</f>
-        <v>5.05</v>
+        <v>11.15</v>
       </c>
       <c r="F33" s="24">
         <f>MAX(0,前提!$B$4-F31)</f>
-        <v>98.55</v>
+        <v>218.65</v>
       </c>
       <c r="G33" s="24">
         <f>MAX(0,前提!$B$4-G31)</f>
-        <v>191.3</v>
+        <v>311.4</v>
       </c>
       <c r="H33" s="24">
         <f>MAX(0,前提!$B$4-H31)</f>
-        <v>198.4</v>
+        <v>318.5</v>
       </c>
       <c r="I33" s="24">
         <f>MAX(0,前提!$B$4-I31)</f>
-        <v>270.9</v>
+        <v>391.0</v>
       </c>
       <c r="J33" s="24">
         <f>MAX(0,前提!$B$4-J31)</f>
-        <v>275.9</v>
+        <v>396.0</v>
       </c>
       <c r="K33" s="24">
         <f>MAX(0,前提!$B$4-K31)</f>
-        <v>280.9</v>
+        <v>401.0</v>
       </c>
       <c r="L33" s="24">
         <f>MAX(0,前提!$B$4-L31)</f>
-        <v>285.9</v>
+        <v>406.0</v>
       </c>
       <c r="M33" s="24">
         <f>MAX(0,前提!$B$4-M31)</f>
-        <v>290.9</v>
+        <v>411.0</v>
       </c>
       <c r="N33" s="24">
         <f>MAX(0,前提!$B$4-N31)</f>
-        <v>295.9</v>
+        <v>416.0</v>
       </c>
       <c r="O33" s="24">
         <f>MAX(0,前提!$B$4-O31)</f>
-        <v>300.9</v>
+        <v>421.0</v>
       </c>
       <c r="P33" s="24">
         <f>MAX(0,前提!$B$4-P31)</f>
-        <v>305.9</v>
+        <v>426.0</v>
       </c>
       <c r="Q33" s="24">
         <f>MAX(0,前提!$B$4-Q31)</f>
-        <v>310.9</v>
+        <v>431.0</v>
       </c>
       <c r="R33" s="24">
         <f>MAX(0,前提!$B$4-R31)</f>
-        <v>315.9</v>
+        <v>436.0</v>
       </c>
       <c r="S33" s="24" t="n"/>
     </row>
@@ -18188,63 +16240,63 @@
       </c>
       <c r="D34" s="23">
         <f>-SUM($C30:D30)</f>
-        <v>58.55</v>
+        <v>59.65</v>
       </c>
       <c r="E34" s="23">
         <f>-SUM($C30:E30)</f>
-        <v>250.35</v>
+        <v>256.45</v>
       </c>
       <c r="F34" s="23">
         <f>-SUM($C30:F30)</f>
-        <v>336.85</v>
+        <v>456.95</v>
       </c>
       <c r="G34" s="23">
         <f>-SUM($C30:G30)</f>
-        <v>424.6</v>
+        <v>544.7</v>
       </c>
       <c r="H34" s="23">
         <f>-SUM($C30:H30)</f>
-        <v>426.7</v>
+        <v>546.8</v>
       </c>
       <c r="I34" s="23">
         <f>-SUM($C30:I30)</f>
-        <v>494.2</v>
+        <v>614.3</v>
       </c>
       <c r="J34" s="23">
         <f>-SUM($C30:J30)</f>
-        <v>494.2</v>
+        <v>614.3</v>
       </c>
       <c r="K34" s="23">
         <f>-SUM($C30:K30)</f>
-        <v>494.2</v>
+        <v>614.3</v>
       </c>
       <c r="L34" s="23">
         <f>-SUM($C30:L30)</f>
-        <v>494.2</v>
+        <v>614.3</v>
       </c>
       <c r="M34" s="23">
         <f>-SUM($C30:M30)</f>
-        <v>494.2</v>
+        <v>614.3</v>
       </c>
       <c r="N34" s="23">
         <f>-SUM($C30:N30)</f>
-        <v>494.2</v>
+        <v>614.3</v>
       </c>
       <c r="O34" s="23">
         <f>-SUM($C30:O30)</f>
-        <v>494.2</v>
+        <v>614.3</v>
       </c>
       <c r="P34" s="23">
         <f>-SUM($C30:P30)</f>
-        <v>494.2</v>
+        <v>614.3</v>
       </c>
       <c r="Q34" s="23">
         <f>-SUM($C30:Q30)</f>
-        <v>494.2</v>
+        <v>614.3</v>
       </c>
       <c r="R34" s="23">
         <f>-SUM($C30:R30)</f>
-        <v>494.2</v>
+        <v>614.3</v>
       </c>
       <c r="S34" s="23" t="n"/>
     </row>
@@ -18335,7 +16387,7 @@
       </c>
       <c r="B39" s="20">
         <f>-S30</f>
-        <v>494.2</v>
+        <v>614.3</v>
       </c>
     </row>
     <row r="40">
@@ -18346,7 +16398,7 @@
       </c>
       <c r="B40" s="20">
         <f>MIN(C31:R31)</f>
-        <v>-215.9</v>
+        <v>-336.0</v>
       </c>
     </row>
     <row r="41">
@@ -18379,7 +16431,7 @@
       </c>
       <c r="B43" s="20">
         <f>MAX(C33:R33)</f>
-        <v>315.9</v>
+        <v>436.0</v>
       </c>
     </row>
     <row r="44">
@@ -18390,7 +16442,7 @@
       </c>
       <c r="B44" s="20">
         <f>E33</f>
-        <v>5.05</v>
+        <v>11.15</v>
       </c>
     </row>
     <row r="45">
@@ -18401,7 +16453,7 @@
       </c>
       <c r="B45" s="20">
         <f>G33</f>
-        <v>191.3</v>
+        <v>311.4</v>
       </c>
     </row>
     <row r="46">
@@ -18412,7 +16464,7 @@
       </c>
       <c r="B46" s="20">
         <f>I33</f>
-        <v>270.9</v>
+        <v>391.0</v>
       </c>
     </row>
     <row r="47">
@@ -18423,7 +16475,7 @@
       </c>
       <c r="B47" s="20">
         <f>R31</f>
-        <v>-215.9</v>
+        <v>-336.0</v>
       </c>
     </row>
     <row r="48">
@@ -18434,7 +16486,7 @@
       </c>
       <c r="B48" s="25">
         <f>前提!$B$5+SUMPRODUCT($B$6:$B$14,案件一覧!$D$4:$D$12)</f>
-        <v>3111</v>
+        <v>3888</v>
       </c>
     </row>
     <row r="49">
@@ -18445,7 +16497,7 @@
       </c>
       <c r="B49" s="25">
         <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12)</f>
-        <v>182</v>
+        <v>161</v>
       </c>
     </row>
     <row r="50">
@@ -18456,7 +16508,7 @@
       </c>
       <c r="B50" s="25">
         <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$F$4:$F$12)</f>
-        <v>255</v>
+        <v>271</v>
       </c>
     </row>
     <row r="51">
@@ -18467,7 +16519,7 @@
       </c>
       <c r="B51" s="20">
         <f>SUMPRODUCT($B$6:$B$14,案件一覧!$G$4:$G$12)</f>
-        <v>138.15</v>
+        <v>221.15</v>
       </c>
     </row>
   </sheetData>

--- a/EEFUL_資金計画_シナリオ別月次.xlsx
+++ b/EEFUL_資金計画_シナリオ別月次.xlsx
@@ -255,7 +255,7 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <v>S1 基本（確定5件）</v>
+            <v>S1 基本（確定4件＋HT実行済）</v>
           </tx>
           <spPr>
             <a:ln>
@@ -972,7 +972,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>S1 基本（確定5件）</t>
+          <t>S1 基本（確定4件＋HT実行済）</t>
         </is>
       </c>
       <c r="B5" s="5" t="str">
@@ -1361,7 +1361,7 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>S1 基本（確定5件）</t>
+          <t>S1 基本（確定4件＋HT実行済）</t>
         </is>
       </c>
       <c r="B15" s="10" t="n">
@@ -1617,7 +1617,7 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>S1 基本（確定5件）</t>
+          <t>S1 基本（確定4件＋HT実行済）</t>
         </is>
       </c>
       <c r="D23" s="12">
@@ -2139,7 +2139,7 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>S1 基本（確定5件）</t>
+          <t>S1 基本（確定4件＋HT実行済）</t>
         </is>
       </c>
       <c r="D32" s="12">
@@ -2553,7 +2553,7 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>A 確定5件＋中型積み上げ（大型なし）</t>
+          <t>A 確定4件＋中型積み上げ（大型なし）</t>
         </is>
       </c>
       <c r="B61" s="11" t="n">
@@ -8185,7 +8185,7 @@
     <row r="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>S1 基本（確定5件） — HD単体 月次キャッシュ推移（百万円）</t>
+          <t>S1 基本（確定4件＋HT実行済） — HD単体 月次キャッシュ推移（百万円）</t>
         </is>
       </c>
     </row>

--- a/EEFUL_資金計画_シナリオ別月次.xlsx
+++ b/EEFUL_資金計画_シナリオ別月次.xlsx
@@ -1158,15 +1158,15 @@
       </c>
       <c r="M7" s="9">
         <f>S3!$B$48</f>
-        <v>2885</v>
+        <v>3111</v>
       </c>
       <c r="N7" s="9">
         <f>S3!$B$49</f>
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O7" s="9">
         <f>S3!$B$50</f>
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="P7" s="7">
         <f>S3!$B$51</f>
@@ -1226,15 +1226,15 @@
       </c>
       <c r="M8" s="9">
         <f>S4!$B$48</f>
-        <v>3370</v>
+        <v>3596</v>
       </c>
       <c r="N8" s="9">
         <f>S4!$B$49</f>
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="O8" s="9">
         <f>S4!$B$50</f>
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="P8" s="7">
         <f>S4!$B$51</f>
@@ -1294,15 +1294,15 @@
       </c>
       <c r="M9" s="9">
         <f>S5!$B$48</f>
-        <v>3888</v>
+        <v>4114</v>
       </c>
       <c r="N9" s="9">
         <f>S5!$B$49</f>
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="O9" s="9">
         <f>S5!$B$50</f>
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="P9" s="7">
         <f>S5!$B$51</f>
@@ -1446,11 +1446,11 @@
         </is>
       </c>
       <c r="G17" s="10" t="n">
-        <v>2885</v>
+        <v>3111</v>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>103 / 165</t>
+          <t>101 / 183</t>
         </is>
       </c>
     </row>
@@ -1478,11 +1478,11 @@
         </is>
       </c>
       <c r="G18" s="10" t="n">
-        <v>3370</v>
+        <v>3596</v>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>141 / 231</t>
+          <t>139 / 249</t>
         </is>
       </c>
     </row>
@@ -1510,11 +1510,11 @@
         </is>
       </c>
       <c r="G19" s="10" t="n">
-        <v>3888</v>
+        <v>4114</v>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>161 / 271</t>
+          <t>159 / 289</t>
         </is>
       </c>
     </row>
@@ -2560,16 +2560,16 @@
         <v>12</v>
       </c>
       <c r="C61" s="13" t="n">
-        <v>0.294</v>
+        <v>0.38</v>
       </c>
       <c r="D61" s="10" t="n">
-        <v>3370</v>
+        <v>3460</v>
       </c>
       <c r="E61" s="10" t="n">
-        <v>3372</v>
+        <v>3449</v>
       </c>
       <c r="F61" s="10" t="n">
-        <v>3768</v>
+        <v>3908</v>
       </c>
       <c r="G61" s="10" t="n">
         <v>475</v>
@@ -2578,10 +2578,10 @@
         <v>587</v>
       </c>
       <c r="I61" s="10" t="n">
-        <v>612</v>
+        <v>595</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>4600</v>
+        <v>4826</v>
       </c>
     </row>
     <row r="62">
@@ -2594,16 +2594,16 @@
         <v>12</v>
       </c>
       <c r="C62" s="13" t="n">
-        <v>0.422</v>
+        <v>0.489</v>
       </c>
       <c r="D62" s="10" t="n">
-        <v>3521</v>
+        <v>3611</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>3510</v>
+        <v>3593</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>3929</v>
+        <v>4092</v>
       </c>
       <c r="G62" s="10" t="n">
         <v>526</v>
@@ -2612,10 +2612,10 @@
         <v>648</v>
       </c>
       <c r="I62" s="10" t="n">
-        <v>640</v>
+        <v>621</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v>4999</v>
+        <v>5225</v>
       </c>
     </row>
     <row r="63">
@@ -2662,16 +2662,16 @@
         <v>11</v>
       </c>
       <c r="C64" s="13" t="n">
-        <v>0.498</v>
+        <v>0.542</v>
       </c>
       <c r="D64" s="10" t="n">
-        <v>3693</v>
+        <v>3784</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>3599</v>
+        <v>3698</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>4253</v>
+        <v>4411</v>
       </c>
       <c r="G64" s="10" t="n">
         <v>544</v>
@@ -2680,10 +2680,10 @@
         <v>687</v>
       </c>
       <c r="I64" s="10" t="n">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>6057</v>
+        <v>6283</v>
       </c>
     </row>
     <row r="65">
@@ -2696,16 +2696,16 @@
         <v>14</v>
       </c>
       <c r="C65" s="13" t="n">
-        <v>0.677</v>
+        <v>0.711</v>
       </c>
       <c r="D65" s="10" t="n">
+        <v>4284</v>
+      </c>
+      <c r="E65" s="10" t="n">
         <v>4194</v>
       </c>
-      <c r="E65" s="10" t="n">
-        <v>4056</v>
-      </c>
       <c r="F65" s="10" t="n">
-        <v>5043</v>
+        <v>5132</v>
       </c>
       <c r="G65" s="10" t="n">
         <v>653</v>
@@ -2714,10 +2714,10 @@
         <v>890</v>
       </c>
       <c r="I65" s="10" t="n">
-        <v>763</v>
+        <v>753</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>7686</v>
+        <v>7912</v>
       </c>
     </row>
     <row r="66">
@@ -2730,16 +2730,16 @@
         <v>22</v>
       </c>
       <c r="C66" s="13" t="n">
-        <v>0.78</v>
+        <v>0.804</v>
       </c>
       <c r="D66" s="10" t="n">
-        <v>4434</v>
+        <v>4524</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>4340</v>
+        <v>4438</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>5291</v>
+        <v>5403</v>
       </c>
       <c r="G66" s="10" t="n">
         <v>837</v>
@@ -2748,16 +2748,16 @@
         <v>1099</v>
       </c>
       <c r="I66" s="10" t="n">
-        <v>920</v>
+        <v>911</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>9210</v>
+        <v>9436</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>期限を2028/6に延ばした場合（戦略F）：到達確率 91%、必要資金P50 814</t>
+          <t>期限を2028/6に延ばした場合（戦略F）：到達確率 92%、必要資金P50 814</t>
         </is>
       </c>
     </row>
@@ -6436,13 +6436,13 @@
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>450</v>
+        <v>676</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="G9" s="15" t="n">
         <v>60.4</v>
@@ -13136,7 +13136,7 @@
       </c>
       <c r="B48" s="25">
         <f>前提!$B$5+SUMPRODUCT($B$6:$B$14,案件一覧!$D$4:$D$12)</f>
-        <v>2885</v>
+        <v>3111</v>
       </c>
     </row>
     <row r="49">
@@ -13147,7 +13147,7 @@
       </c>
       <c r="B49" s="25">
         <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12)</f>
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="50">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="B50" s="25">
         <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$F$4:$F$12)</f>
-        <v>165</v>
+        <v>183</v>
       </c>
     </row>
     <row r="51">
@@ -14811,7 +14811,7 @@
       </c>
       <c r="B48" s="25">
         <f>前提!$B$5+SUMPRODUCT($B$6:$B$14,案件一覧!$D$4:$D$12)</f>
-        <v>3370</v>
+        <v>3596</v>
       </c>
     </row>
     <row r="49">
@@ -14822,7 +14822,7 @@
       </c>
       <c r="B49" s="25">
         <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12)</f>
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="50">
@@ -14833,7 +14833,7 @@
       </c>
       <c r="B50" s="25">
         <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$F$4:$F$12)</f>
-        <v>231</v>
+        <v>249</v>
       </c>
     </row>
     <row r="51">
@@ -16486,7 +16486,7 @@
       </c>
       <c r="B48" s="25">
         <f>前提!$B$5+SUMPRODUCT($B$6:$B$14,案件一覧!$D$4:$D$12)</f>
-        <v>3888</v>
+        <v>4114</v>
       </c>
     </row>
     <row r="49">
@@ -16497,7 +16497,7 @@
       </c>
       <c r="B49" s="25">
         <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12)</f>
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="50">
@@ -16508,7 +16508,7 @@
       </c>
       <c r="B50" s="25">
         <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$F$4:$F$12)</f>
-        <v>271</v>
+        <v>289</v>
       </c>
     </row>
     <row r="51">

--- a/EEFUL_資金計画_シナリオ別月次.xlsx
+++ b/EEFUL_資金計画_シナリオ別月次.xlsx
@@ -48,6 +48,9 @@
     </font>
     <font>
       <name val="Arial"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <i val="1"/>
       <sz val="9"/>
     </font>
@@ -59,9 +62,6 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-    </font>
-    <font>
-      <name val="Arial"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -116,13 +116,13 @@
   <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -143,19 +143,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -705,6 +705,16 @@
         <t>半年分のHD運営費＋HT一時支援余力として1億円を仮置き（当社判断値）</t>
       </text>
     </comment>
+    <comment ref="B6" authorId="0" shapeId="0">
+      <text>
+        <t>連結月次DCの調整後EBITDA年換算（1〜7月累計18.8÷7×12＝32.3）。5〜7月の直近3ヶ月も年換算32で同水準</t>
+      </text>
+    </comment>
+    <comment ref="D6" authorId="0" shapeId="0">
+      <text>
+        <t>HT実態EBITDA年換算69（上期34.7×2）−HD運営コスト9。改善後EBITDAの計算にのみ使用</t>
+      </text>
+    </comment>
     <comment ref="D11" authorId="0" shapeId="0">
       <text>
         <t>1〜8月実績：HD調整後営業損失 月▲1〜2、現金減少 月▲9（DD費用・HT支援含む）。当社仮置き</t>
@@ -712,7 +722,7 @@
     </comment>
     <comment ref="B56" authorId="0" shapeId="0">
       <text>
-        <t>2026年は7月YTD年換算32から計画達成で39へ、2027年はHT年換算69・HD▲9で60を仮置き</t>
+        <t>実質収益力（連結DCの調整後EBITDA年換算32）で据え置き。計画達成を織り込まない</t>
       </text>
     </comment>
   </commentList>
@@ -725,9 +735,9 @@
     <author>EEFUL</author>
   </authors>
   <commentList>
-    <comment ref="D4" authorId="0" shapeId="0">
+    <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>売上・EBITDAは各案件の直近実績（現状）と改善後（確信度8割・8/24議事録ほか）。日本経営センターは親族継続12／退任後32（Slack 9/17）</t>
+        <t>調整後EBITDA＝実質収益力（オーナー費用・非経常を調整した直近の年換算）。メディプロ実態18／ヒューマンアイ9.9（FA修正：食費増額+4.2・家賃+0.6、管理者補充あり）／クレッシェンド20／シルバー3期平均▲21（27/3期Q1営業損失▲5.6の年換算▲22と整合）／ワイズケア正常化38.2（藤井寺立上げ赤字を含む）／エーステイスト正常化24.9（9/2修正計画17.5＋役員報酬調整6.8＋非経常0.6）／日本経営センター調整後20.6（25/12期・IM）／セレサ営業利益8</t>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
@@ -1198,7 +1208,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>年換算 調整後EBITDA（現状）</t>
+          <t>年換算 調整後EBITDA（実質収益力）</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -1284,7 +1294,7 @@
       </c>
       <c r="N5" s="9">
         <f>S1!$B$56</f>
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="O5" s="9">
         <f>S1!$B$57</f>
@@ -1296,11 +1306,11 @@
       </c>
       <c r="Q5" s="7">
         <f>S1!$B$59</f>
-        <v>348.2</v>
+        <v>336.2</v>
       </c>
       <c r="R5" s="7">
         <f>S1!$B$60</f>
-        <v>372.5</v>
+        <v>276.5</v>
       </c>
       <c r="S5" s="7">
         <f>S1!$B$61</f>
@@ -1364,7 +1374,7 @@
       </c>
       <c r="N6" s="9">
         <f>S2!$B$56</f>
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="O6" s="9">
         <f>S2!$B$57</f>
@@ -1376,11 +1386,11 @@
       </c>
       <c r="Q6" s="7">
         <f>S2!$B$59</f>
-        <v>375.2</v>
+        <v>363.2</v>
       </c>
       <c r="R6" s="7">
         <f>S2!$B$60</f>
-        <v>399.5</v>
+        <v>303.5</v>
       </c>
       <c r="S6" s="7">
         <f>S2!$B$61</f>
@@ -1444,7 +1454,7 @@
       </c>
       <c r="N7" s="9">
         <f>S3!$B$56</f>
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="O7" s="9">
         <f>S3!$B$57</f>
@@ -1456,11 +1466,11 @@
       </c>
       <c r="Q7" s="7">
         <f>S3!$B$59</f>
-        <v>380.4</v>
+        <v>396.4</v>
       </c>
       <c r="R7" s="7">
         <f>S3!$B$60</f>
-        <v>404.6</v>
+        <v>336.6</v>
       </c>
       <c r="S7" s="7">
         <f>S3!$B$61</f>
@@ -1524,7 +1534,7 @@
       </c>
       <c r="N8" s="9">
         <f>S4!$B$56</f>
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="O8" s="9">
         <f>S4!$B$57</f>
@@ -1536,11 +1546,11 @@
       </c>
       <c r="Q8" s="7">
         <f>S4!$B$59</f>
-        <v>407.3</v>
+        <v>423.3</v>
       </c>
       <c r="R8" s="7">
         <f>S4!$B$60</f>
-        <v>431.5</v>
+        <v>363.6</v>
       </c>
       <c r="S8" s="7">
         <f>S4!$B$61</f>
@@ -1604,7 +1614,7 @@
       </c>
       <c r="N9" s="9">
         <f>S5!$B$56</f>
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="O9" s="9">
         <f>S5!$B$57</f>
@@ -1616,11 +1626,11 @@
       </c>
       <c r="Q9" s="7">
         <f>S5!$B$59</f>
-        <v>402.7</v>
+        <v>418.7</v>
       </c>
       <c r="R9" s="7">
         <f>S5!$B$60</f>
-        <v>439.6</v>
+        <v>407.6</v>
       </c>
       <c r="S9" s="7">
         <f>S5!$B$61</f>
@@ -1672,7 +1682,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>EBITDA現状／改善後</t>
+          <t>EBITDA 実質／改善後</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1714,7 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>83 / 140</t>
+          <t>59 / 140</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1746,7 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>121 / 206</t>
+          <t>97 / 206</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1778,7 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>101 / 183</t>
+          <t>84 / 183</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1810,7 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>139 / 249</t>
+          <t>122 / 249</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1842,7 @@
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>159 / 289</t>
+          <t>151 / 289</t>
         </is>
       </c>
     </row>
@@ -2917,63 +2927,63 @@
       </c>
       <c r="E40" s="12">
         <f>S1!D42</f>
-        <v>302.9</v>
+        <v>294.9</v>
       </c>
       <c r="F40" s="12">
         <f>S1!E42</f>
-        <v>421.4</v>
+        <v>401.4</v>
       </c>
       <c r="G40" s="12">
         <f>S1!F42</f>
-        <v>348.2</v>
+        <v>336.2</v>
       </c>
       <c r="H40" s="12">
         <f>S1!G42</f>
-        <v>436.1</v>
+        <v>340.1</v>
       </c>
       <c r="I40" s="12">
         <f>S1!H42</f>
-        <v>436.0</v>
+        <v>340.0</v>
       </c>
       <c r="J40" s="12">
         <f>S1!I42</f>
-        <v>423.8</v>
+        <v>327.8</v>
       </c>
       <c r="K40" s="12">
         <f>S1!J42</f>
-        <v>423.7</v>
+        <v>327.7</v>
       </c>
       <c r="L40" s="12">
         <f>S1!K42</f>
-        <v>373.5</v>
+        <v>277.5</v>
       </c>
       <c r="M40" s="12">
         <f>S1!L42</f>
-        <v>373.4</v>
+        <v>277.4</v>
       </c>
       <c r="N40" s="12">
         <f>S1!M42</f>
-        <v>373.2</v>
+        <v>277.2</v>
       </c>
       <c r="O40" s="12">
         <f>S1!N42</f>
-        <v>373.1</v>
+        <v>277.1</v>
       </c>
       <c r="P40" s="12">
         <f>S1!O42</f>
-        <v>372.9</v>
+        <v>276.9</v>
       </c>
       <c r="Q40" s="12">
         <f>S1!P42</f>
-        <v>372.8</v>
+        <v>276.8</v>
       </c>
       <c r="R40" s="12">
         <f>S1!Q42</f>
-        <v>372.6</v>
+        <v>276.6</v>
       </c>
       <c r="S40" s="12">
         <f>S1!R42</f>
-        <v>372.5</v>
+        <v>276.5</v>
       </c>
     </row>
     <row r="41">
@@ -2988,63 +2998,63 @@
       </c>
       <c r="E41" s="12">
         <f>S2!D42</f>
-        <v>294.2</v>
+        <v>286.2</v>
       </c>
       <c r="F41" s="12">
         <f>S2!E42</f>
-        <v>448.4</v>
+        <v>428.4</v>
       </c>
       <c r="G41" s="12">
         <f>S2!F42</f>
-        <v>375.2</v>
+        <v>363.2</v>
       </c>
       <c r="H41" s="12">
         <f>S2!G42</f>
-        <v>463.1</v>
+        <v>367.1</v>
       </c>
       <c r="I41" s="12">
         <f>S2!H42</f>
-        <v>462.9</v>
+        <v>367.0</v>
       </c>
       <c r="J41" s="12">
         <f>S2!I42</f>
-        <v>450.8</v>
+        <v>354.8</v>
       </c>
       <c r="K41" s="12">
         <f>S2!J42</f>
-        <v>450.6</v>
+        <v>354.6</v>
       </c>
       <c r="L41" s="12">
         <f>S2!K42</f>
-        <v>400.5</v>
+        <v>304.5</v>
       </c>
       <c r="M41" s="12">
         <f>S2!L42</f>
-        <v>400.3</v>
+        <v>304.4</v>
       </c>
       <c r="N41" s="12">
         <f>S2!M42</f>
-        <v>400.2</v>
+        <v>304.2</v>
       </c>
       <c r="O41" s="12">
         <f>S2!N42</f>
-        <v>400.1</v>
+        <v>304.1</v>
       </c>
       <c r="P41" s="12">
         <f>S2!O42</f>
-        <v>399.9</v>
+        <v>303.9</v>
       </c>
       <c r="Q41" s="12">
         <f>S2!P42</f>
-        <v>399.8</v>
+        <v>303.8</v>
       </c>
       <c r="R41" s="12">
         <f>S2!Q42</f>
-        <v>399.6</v>
+        <v>303.6</v>
       </c>
       <c r="S41" s="12">
         <f>S2!R42</f>
-        <v>399.5</v>
+        <v>303.5</v>
       </c>
     </row>
     <row r="42">
@@ -3059,63 +3069,63 @@
       </c>
       <c r="E42" s="12">
         <f>S3!D42</f>
-        <v>300.2</v>
+        <v>292.2</v>
       </c>
       <c r="F42" s="12">
         <f>S3!E42</f>
-        <v>416.7</v>
+        <v>396.7</v>
       </c>
       <c r="G42" s="12">
         <f>S3!F42</f>
-        <v>380.4</v>
+        <v>396.4</v>
       </c>
       <c r="H42" s="12">
         <f>S3!G42</f>
-        <v>468.2</v>
+        <v>400.2</v>
       </c>
       <c r="I42" s="12">
         <f>S3!H42</f>
-        <v>468.0</v>
+        <v>400.1</v>
       </c>
       <c r="J42" s="12">
         <f>S3!I42</f>
-        <v>455.9</v>
+        <v>387.9</v>
       </c>
       <c r="K42" s="12">
         <f>S3!J42</f>
-        <v>455.8</v>
+        <v>387.8</v>
       </c>
       <c r="L42" s="12">
         <f>S3!K42</f>
-        <v>405.6</v>
+        <v>337.6</v>
       </c>
       <c r="M42" s="12">
         <f>S3!L42</f>
-        <v>405.5</v>
+        <v>337.5</v>
       </c>
       <c r="N42" s="12">
         <f>S3!M42</f>
-        <v>405.3</v>
+        <v>337.3</v>
       </c>
       <c r="O42" s="12">
         <f>S3!N42</f>
-        <v>405.2</v>
+        <v>337.2</v>
       </c>
       <c r="P42" s="12">
         <f>S3!O42</f>
-        <v>405.0</v>
+        <v>337.0</v>
       </c>
       <c r="Q42" s="12">
         <f>S3!P42</f>
-        <v>404.9</v>
+        <v>336.9</v>
       </c>
       <c r="R42" s="12">
         <f>S3!Q42</f>
-        <v>404.7</v>
+        <v>336.7</v>
       </c>
       <c r="S42" s="12">
         <f>S3!R42</f>
-        <v>404.6</v>
+        <v>336.6</v>
       </c>
     </row>
     <row r="43">
@@ -3130,63 +3140,63 @@
       </c>
       <c r="E43" s="12">
         <f>S4!D42</f>
-        <v>291.5</v>
+        <v>283.5</v>
       </c>
       <c r="F43" s="12">
         <f>S4!E42</f>
-        <v>443.7</v>
+        <v>423.7</v>
       </c>
       <c r="G43" s="12">
         <f>S4!F42</f>
-        <v>407.3</v>
+        <v>423.3</v>
       </c>
       <c r="H43" s="12">
         <f>S4!G42</f>
-        <v>495.2</v>
+        <v>427.2</v>
       </c>
       <c r="I43" s="12">
         <f>S4!H42</f>
-        <v>495.0</v>
+        <v>427.0</v>
       </c>
       <c r="J43" s="12">
         <f>S4!I42</f>
-        <v>482.9</v>
+        <v>414.9</v>
       </c>
       <c r="K43" s="12">
         <f>S4!J42</f>
-        <v>482.7</v>
+        <v>414.7</v>
       </c>
       <c r="L43" s="12">
         <f>S4!K42</f>
-        <v>432.6</v>
+        <v>364.6</v>
       </c>
       <c r="M43" s="12">
         <f>S4!L42</f>
-        <v>432.4</v>
+        <v>364.4</v>
       </c>
       <c r="N43" s="12">
         <f>S4!M42</f>
-        <v>432.3</v>
+        <v>364.3</v>
       </c>
       <c r="O43" s="12">
         <f>S4!N42</f>
-        <v>432.1</v>
+        <v>364.1</v>
       </c>
       <c r="P43" s="12">
         <f>S4!O42</f>
-        <v>432.0</v>
+        <v>364.0</v>
       </c>
       <c r="Q43" s="12">
         <f>S4!P42</f>
-        <v>431.8</v>
+        <v>363.8</v>
       </c>
       <c r="R43" s="12">
         <f>S4!Q42</f>
-        <v>431.7</v>
+        <v>363.7</v>
       </c>
       <c r="S43" s="12">
         <f>S4!R42</f>
-        <v>431.5</v>
+        <v>363.6</v>
       </c>
     </row>
     <row r="44">
@@ -3201,63 +3211,63 @@
       </c>
       <c r="E44" s="12">
         <f>S5!D42</f>
-        <v>291.5</v>
+        <v>283.5</v>
       </c>
       <c r="F44" s="12">
         <f>S5!E42</f>
-        <v>443.7</v>
+        <v>423.7</v>
       </c>
       <c r="G44" s="12">
         <f>S5!F42</f>
-        <v>402.7</v>
+        <v>418.7</v>
       </c>
       <c r="H44" s="12">
         <f>S5!G42</f>
-        <v>485.8</v>
+        <v>453.8</v>
       </c>
       <c r="I44" s="12">
         <f>S5!H42</f>
-        <v>483.6</v>
+        <v>451.6</v>
       </c>
       <c r="J44" s="12">
         <f>S5!I42</f>
-        <v>490.9</v>
+        <v>458.9</v>
       </c>
       <c r="K44" s="12">
         <f>S5!J42</f>
-        <v>490.8</v>
+        <v>458.8</v>
       </c>
       <c r="L44" s="12">
         <f>S5!K42</f>
-        <v>440.6</v>
+        <v>408.6</v>
       </c>
       <c r="M44" s="12">
         <f>S5!L42</f>
-        <v>440.5</v>
+        <v>408.5</v>
       </c>
       <c r="N44" s="12">
         <f>S5!M42</f>
-        <v>440.3</v>
+        <v>408.3</v>
       </c>
       <c r="O44" s="12">
         <f>S5!N42</f>
-        <v>440.2</v>
+        <v>408.2</v>
       </c>
       <c r="P44" s="12">
         <f>S5!O42</f>
-        <v>440.0</v>
+        <v>408.0</v>
       </c>
       <c r="Q44" s="12">
         <f>S5!P42</f>
-        <v>439.9</v>
+        <v>407.9</v>
       </c>
       <c r="R44" s="12">
         <f>S5!Q42</f>
-        <v>439.7</v>
+        <v>407.7</v>
       </c>
       <c r="S44" s="12">
         <f>S5!R42</f>
-        <v>439.6</v>
+        <v>407.6</v>
       </c>
     </row>
     <row r="87">
@@ -3863,10 +3873,18 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>年換算オーガニック調整後EBITDA</t>
+          <t>年換算オーガニック調整後EBITDA（実質収益力）</t>
         </is>
       </c>
       <c r="B6" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>改善後（2027計画）</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="n">
         <v>60</v>
       </c>
     </row>
@@ -6833,7 +6851,7 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>オーガニック 調整後EBITDA年換算</t>
+          <t>オーガニック 調整後EBITDA年換算（実質収益力）</t>
         </is>
       </c>
       <c r="B56" t="n"/>
@@ -6846,49 +6864,49 @@
         <v>32</v>
       </c>
       <c r="E56" s="15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F56" s="15" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="J56" s="15" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="K56" s="15" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="L56" s="15" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="M56" s="15" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="N56" s="15" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="O56" s="15" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="P56" s="15" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="Q56" s="15" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="R56" s="15" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="S56" s="15" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="57">
@@ -7118,7 +7136,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>調整後EBITDA（現状）</t>
+          <t>調整後EBITDA（実質収益力）</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -7336,7 +7354,7 @@
         <v>182</v>
       </c>
       <c r="E6" s="15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F6" s="15" t="n">
         <v>15</v>
@@ -7537,7 +7555,7 @@
         <v>676</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F9" s="15" t="n">
         <v>43</v>
@@ -7604,7 +7622,7 @@
         <v>378</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F10" s="15" t="n">
         <v>32</v>
@@ -10993,63 +11011,63 @@
       </c>
       <c r="D40" s="24">
         <f>前提!E$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=2))</f>
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E40" s="24">
         <f>前提!F$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=3))</f>
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F40" s="24">
         <f>前提!G$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=4))</f>
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G40" s="24">
         <f>前提!H$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=5))</f>
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="H40" s="24">
         <f>前提!I$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=6))</f>
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="I40" s="24">
         <f>前提!J$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=7))</f>
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="J40" s="24">
         <f>前提!K$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=8))</f>
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="K40" s="24">
         <f>前提!L$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=9))</f>
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="L40" s="24">
         <f>前提!M$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=10))</f>
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="M40" s="24">
         <f>前提!N$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=11))</f>
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="N40" s="24">
         <f>前提!O$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=12))</f>
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="O40" s="24">
         <f>前提!P$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=13))</f>
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="P40" s="24">
         <f>前提!Q$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=14))</f>
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="Q40" s="24">
         <f>前提!R$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=15))</f>
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="R40" s="24">
         <f>前提!S$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=16))</f>
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="S40" s="24" t="n"/>
     </row>
@@ -11137,63 +11155,63 @@
       </c>
       <c r="D42" s="26">
         <f>D40*4+D38+D39-D41</f>
-        <v>302.9</v>
+        <v>294.9</v>
       </c>
       <c r="E42" s="26">
         <f>E40*4+E38+E39-E41</f>
-        <v>421.4</v>
+        <v>401.4</v>
       </c>
       <c r="F42" s="26">
         <f>F40*4+F38+F39-F41</f>
-        <v>348.2</v>
+        <v>336.2</v>
       </c>
       <c r="G42" s="26">
         <f>G40*4+G38+G39-G41</f>
-        <v>436.1</v>
+        <v>340.1</v>
       </c>
       <c r="H42" s="26">
         <f>H40*4+H38+H39-H41</f>
-        <v>436.0</v>
+        <v>340.0</v>
       </c>
       <c r="I42" s="26">
         <f>I40*4+I38+I39-I41</f>
-        <v>423.8</v>
+        <v>327.8</v>
       </c>
       <c r="J42" s="26">
         <f>J40*4+J38+J39-J41</f>
-        <v>423.7</v>
+        <v>327.7</v>
       </c>
       <c r="K42" s="26">
         <f>K40*4+K38+K39-K41</f>
-        <v>373.5</v>
+        <v>277.5</v>
       </c>
       <c r="L42" s="26">
         <f>L40*4+L38+L39-L41</f>
-        <v>373.4</v>
+        <v>277.4</v>
       </c>
       <c r="M42" s="26">
         <f>M40*4+M38+M39-M41</f>
-        <v>373.2</v>
+        <v>277.2</v>
       </c>
       <c r="N42" s="26">
         <f>N40*4+N38+N39-N41</f>
-        <v>373.1</v>
+        <v>277.1</v>
       </c>
       <c r="O42" s="26">
         <f>O40*4+O38+O39-O41</f>
-        <v>372.9</v>
+        <v>276.9</v>
       </c>
       <c r="P42" s="26">
         <f>P40*4+P38+P39-P41</f>
-        <v>372.8</v>
+        <v>276.8</v>
       </c>
       <c r="Q42" s="26">
         <f>Q40*4+Q38+Q39-Q41</f>
-        <v>372.6</v>
+        <v>276.6</v>
       </c>
       <c r="R42" s="26">
         <f>R40*4+R38+R39-R41</f>
-        <v>372.5</v>
+        <v>276.5</v>
       </c>
       <c r="S42" s="26" t="n"/>
     </row>
@@ -11317,12 +11335,12 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>年換算 調整後EBITDA（現状）</t>
+          <t>年換算 調整後EBITDA（実質収益力）</t>
         </is>
       </c>
       <c r="B56" s="27">
         <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12)</f>
-        <v>83</v>
+        <v>59</v>
       </c>
     </row>
     <row r="57">
@@ -11332,7 +11350,7 @@
         </is>
       </c>
       <c r="B57" s="27">
-        <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$F$4:$F$12)</f>
+        <f>前提!$D$6+SUMPRODUCT($B$6:$B$14,案件一覧!$F$4:$F$12)</f>
         <v>140</v>
       </c>
     </row>
@@ -11355,7 +11373,7 @@
       </c>
       <c r="B59" s="21">
         <f>F42</f>
-        <v>348.2</v>
+        <v>336.2</v>
       </c>
     </row>
     <row r="60">
@@ -11366,7 +11384,7 @@
       </c>
       <c r="B60" s="21">
         <f>R42</f>
-        <v>372.5</v>
+        <v>276.5</v>
       </c>
     </row>
     <row r="61">
@@ -13068,63 +13086,63 @@
       </c>
       <c r="D40" s="24">
         <f>前提!E$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=2))</f>
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E40" s="24">
         <f>前提!F$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=3))</f>
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F40" s="24">
         <f>前提!G$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=4))</f>
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G40" s="24">
         <f>前提!H$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=5))</f>
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="H40" s="24">
         <f>前提!I$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=6))</f>
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="I40" s="24">
         <f>前提!J$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=7))</f>
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="J40" s="24">
         <f>前提!K$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=8))</f>
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="K40" s="24">
         <f>前提!L$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=9))</f>
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="L40" s="24">
         <f>前提!M$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=10))</f>
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="M40" s="24">
         <f>前提!N$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=11))</f>
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="N40" s="24">
         <f>前提!O$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=12))</f>
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="O40" s="24">
         <f>前提!P$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=13))</f>
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="P40" s="24">
         <f>前提!Q$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=14))</f>
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="Q40" s="24">
         <f>前提!R$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=15))</f>
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="R40" s="24">
         <f>前提!S$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=16))</f>
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="S40" s="24" t="n"/>
     </row>
@@ -13212,63 +13230,63 @@
       </c>
       <c r="D42" s="26">
         <f>D40*4+D38+D39-D41</f>
-        <v>294.2</v>
+        <v>286.2</v>
       </c>
       <c r="E42" s="26">
         <f>E40*4+E38+E39-E41</f>
-        <v>448.4</v>
+        <v>428.4</v>
       </c>
       <c r="F42" s="26">
         <f>F40*4+F38+F39-F41</f>
-        <v>375.2</v>
+        <v>363.2</v>
       </c>
       <c r="G42" s="26">
         <f>G40*4+G38+G39-G41</f>
-        <v>463.1</v>
+        <v>367.1</v>
       </c>
       <c r="H42" s="26">
         <f>H40*4+H38+H39-H41</f>
-        <v>462.9</v>
+        <v>367.0</v>
       </c>
       <c r="I42" s="26">
         <f>I40*4+I38+I39-I41</f>
-        <v>450.8</v>
+        <v>354.8</v>
       </c>
       <c r="J42" s="26">
         <f>J40*4+J38+J39-J41</f>
-        <v>450.6</v>
+        <v>354.6</v>
       </c>
       <c r="K42" s="26">
         <f>K40*4+K38+K39-K41</f>
-        <v>400.5</v>
+        <v>304.5</v>
       </c>
       <c r="L42" s="26">
         <f>L40*4+L38+L39-L41</f>
-        <v>400.3</v>
+        <v>304.4</v>
       </c>
       <c r="M42" s="26">
         <f>M40*4+M38+M39-M41</f>
-        <v>400.2</v>
+        <v>304.2</v>
       </c>
       <c r="N42" s="26">
         <f>N40*4+N38+N39-N41</f>
-        <v>400.1</v>
+        <v>304.1</v>
       </c>
       <c r="O42" s="26">
         <f>O40*4+O38+O39-O41</f>
-        <v>399.9</v>
+        <v>303.9</v>
       </c>
       <c r="P42" s="26">
         <f>P40*4+P38+P39-P41</f>
-        <v>399.8</v>
+        <v>303.8</v>
       </c>
       <c r="Q42" s="26">
         <f>Q40*4+Q38+Q39-Q41</f>
-        <v>399.6</v>
+        <v>303.6</v>
       </c>
       <c r="R42" s="26">
         <f>R40*4+R38+R39-R41</f>
-        <v>399.5</v>
+        <v>303.5</v>
       </c>
       <c r="S42" s="26" t="n"/>
     </row>
@@ -13392,12 +13410,12 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>年換算 調整後EBITDA（現状）</t>
+          <t>年換算 調整後EBITDA（実質収益力）</t>
         </is>
       </c>
       <c r="B56" s="27">
         <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12)</f>
-        <v>121</v>
+        <v>97</v>
       </c>
     </row>
     <row r="57">
@@ -13407,7 +13425,7 @@
         </is>
       </c>
       <c r="B57" s="27">
-        <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$F$4:$F$12)</f>
+        <f>前提!$D$6+SUMPRODUCT($B$6:$B$14,案件一覧!$F$4:$F$12)</f>
         <v>206</v>
       </c>
     </row>
@@ -13430,7 +13448,7 @@
       </c>
       <c r="B59" s="21">
         <f>F42</f>
-        <v>375.2</v>
+        <v>363.2</v>
       </c>
     </row>
     <row r="60">
@@ -13441,7 +13459,7 @@
       </c>
       <c r="B60" s="21">
         <f>R42</f>
-        <v>399.5</v>
+        <v>303.5</v>
       </c>
     </row>
     <row r="61">
@@ -15143,63 +15161,63 @@
       </c>
       <c r="D40" s="24">
         <f>前提!E$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=2))</f>
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E40" s="24">
         <f>前提!F$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=3))</f>
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F40" s="24">
         <f>前提!G$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=4))</f>
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G40" s="24">
         <f>前提!H$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=5))</f>
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="H40" s="24">
         <f>前提!I$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=6))</f>
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I40" s="24">
         <f>前提!J$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=7))</f>
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="J40" s="24">
         <f>前提!K$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=8))</f>
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="K40" s="24">
         <f>前提!L$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=9))</f>
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="L40" s="24">
         <f>前提!M$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=10))</f>
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="M40" s="24">
         <f>前提!N$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=11))</f>
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="N40" s="24">
         <f>前提!O$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=12))</f>
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="O40" s="24">
         <f>前提!P$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=13))</f>
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="P40" s="24">
         <f>前提!Q$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=14))</f>
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="Q40" s="24">
         <f>前提!R$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=15))</f>
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="R40" s="24">
         <f>前提!S$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=16))</f>
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="S40" s="24" t="n"/>
     </row>
@@ -15287,63 +15305,63 @@
       </c>
       <c r="D42" s="26">
         <f>D40*4+D38+D39-D41</f>
-        <v>300.2</v>
+        <v>292.2</v>
       </c>
       <c r="E42" s="26">
         <f>E40*4+E38+E39-E41</f>
-        <v>416.7</v>
+        <v>396.7</v>
       </c>
       <c r="F42" s="26">
         <f>F40*4+F38+F39-F41</f>
-        <v>380.4</v>
+        <v>396.4</v>
       </c>
       <c r="G42" s="26">
         <f>G40*4+G38+G39-G41</f>
-        <v>468.2</v>
+        <v>400.2</v>
       </c>
       <c r="H42" s="26">
         <f>H40*4+H38+H39-H41</f>
-        <v>468.0</v>
+        <v>400.1</v>
       </c>
       <c r="I42" s="26">
         <f>I40*4+I38+I39-I41</f>
-        <v>455.9</v>
+        <v>387.9</v>
       </c>
       <c r="J42" s="26">
         <f>J40*4+J38+J39-J41</f>
-        <v>455.8</v>
+        <v>387.8</v>
       </c>
       <c r="K42" s="26">
         <f>K40*4+K38+K39-K41</f>
-        <v>405.6</v>
+        <v>337.6</v>
       </c>
       <c r="L42" s="26">
         <f>L40*4+L38+L39-L41</f>
-        <v>405.5</v>
+        <v>337.5</v>
       </c>
       <c r="M42" s="26">
         <f>M40*4+M38+M39-M41</f>
-        <v>405.3</v>
+        <v>337.3</v>
       </c>
       <c r="N42" s="26">
         <f>N40*4+N38+N39-N41</f>
-        <v>405.2</v>
+        <v>337.2</v>
       </c>
       <c r="O42" s="26">
         <f>O40*4+O38+O39-O41</f>
-        <v>405.0</v>
+        <v>337.0</v>
       </c>
       <c r="P42" s="26">
         <f>P40*4+P38+P39-P41</f>
-        <v>404.9</v>
+        <v>336.9</v>
       </c>
       <c r="Q42" s="26">
         <f>Q40*4+Q38+Q39-Q41</f>
-        <v>404.7</v>
+        <v>336.7</v>
       </c>
       <c r="R42" s="26">
         <f>R40*4+R38+R39-R41</f>
-        <v>404.6</v>
+        <v>336.6</v>
       </c>
       <c r="S42" s="26" t="n"/>
     </row>
@@ -15467,12 +15485,12 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>年換算 調整後EBITDA（現状）</t>
+          <t>年換算 調整後EBITDA（実質収益力）</t>
         </is>
       </c>
       <c r="B56" s="27">
         <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12)</f>
-        <v>101</v>
+        <v>84</v>
       </c>
     </row>
     <row r="57">
@@ -15482,7 +15500,7 @@
         </is>
       </c>
       <c r="B57" s="27">
-        <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$F$4:$F$12)</f>
+        <f>前提!$D$6+SUMPRODUCT($B$6:$B$14,案件一覧!$F$4:$F$12)</f>
         <v>183</v>
       </c>
     </row>
@@ -15505,7 +15523,7 @@
       </c>
       <c r="B59" s="21">
         <f>F42</f>
-        <v>380.4</v>
+        <v>396.4</v>
       </c>
     </row>
     <row r="60">
@@ -15516,7 +15534,7 @@
       </c>
       <c r="B60" s="21">
         <f>R42</f>
-        <v>404.6</v>
+        <v>336.6</v>
       </c>
     </row>
     <row r="61">
@@ -17218,63 +17236,63 @@
       </c>
       <c r="D40" s="24">
         <f>前提!E$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=2))</f>
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E40" s="24">
         <f>前提!F$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=3))</f>
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F40" s="24">
         <f>前提!G$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=4))</f>
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G40" s="24">
         <f>前提!H$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=5))</f>
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="H40" s="24">
         <f>前提!I$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=6))</f>
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="I40" s="24">
         <f>前提!J$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=7))</f>
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="J40" s="24">
         <f>前提!K$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=8))</f>
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="K40" s="24">
         <f>前提!L$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=9))</f>
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="L40" s="24">
         <f>前提!M$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=10))</f>
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="M40" s="24">
         <f>前提!N$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=11))</f>
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="N40" s="24">
         <f>前提!O$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=12))</f>
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="O40" s="24">
         <f>前提!P$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=13))</f>
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="P40" s="24">
         <f>前提!Q$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=14))</f>
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="Q40" s="24">
         <f>前提!R$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=15))</f>
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="R40" s="24">
         <f>前提!S$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=16))</f>
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="S40" s="24" t="n"/>
     </row>
@@ -17362,63 +17380,63 @@
       </c>
       <c r="D42" s="26">
         <f>D40*4+D38+D39-D41</f>
-        <v>291.5</v>
+        <v>283.5</v>
       </c>
       <c r="E42" s="26">
         <f>E40*4+E38+E39-E41</f>
-        <v>443.7</v>
+        <v>423.7</v>
       </c>
       <c r="F42" s="26">
         <f>F40*4+F38+F39-F41</f>
-        <v>407.3</v>
+        <v>423.3</v>
       </c>
       <c r="G42" s="26">
         <f>G40*4+G38+G39-G41</f>
-        <v>495.2</v>
+        <v>427.2</v>
       </c>
       <c r="H42" s="26">
         <f>H40*4+H38+H39-H41</f>
-        <v>495.0</v>
+        <v>427.0</v>
       </c>
       <c r="I42" s="26">
         <f>I40*4+I38+I39-I41</f>
-        <v>482.9</v>
+        <v>414.9</v>
       </c>
       <c r="J42" s="26">
         <f>J40*4+J38+J39-J41</f>
-        <v>482.7</v>
+        <v>414.7</v>
       </c>
       <c r="K42" s="26">
         <f>K40*4+K38+K39-K41</f>
-        <v>432.6</v>
+        <v>364.6</v>
       </c>
       <c r="L42" s="26">
         <f>L40*4+L38+L39-L41</f>
-        <v>432.4</v>
+        <v>364.4</v>
       </c>
       <c r="M42" s="26">
         <f>M40*4+M38+M39-M41</f>
-        <v>432.3</v>
+        <v>364.3</v>
       </c>
       <c r="N42" s="26">
         <f>N40*4+N38+N39-N41</f>
-        <v>432.1</v>
+        <v>364.1</v>
       </c>
       <c r="O42" s="26">
         <f>O40*4+O38+O39-O41</f>
-        <v>432.0</v>
+        <v>364.0</v>
       </c>
       <c r="P42" s="26">
         <f>P40*4+P38+P39-P41</f>
-        <v>431.8</v>
+        <v>363.8</v>
       </c>
       <c r="Q42" s="26">
         <f>Q40*4+Q38+Q39-Q41</f>
-        <v>431.7</v>
+        <v>363.7</v>
       </c>
       <c r="R42" s="26">
         <f>R40*4+R38+R39-R41</f>
-        <v>431.5</v>
+        <v>363.6</v>
       </c>
       <c r="S42" s="26" t="n"/>
     </row>
@@ -17542,12 +17560,12 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>年換算 調整後EBITDA（現状）</t>
+          <t>年換算 調整後EBITDA（実質収益力）</t>
         </is>
       </c>
       <c r="B56" s="27">
         <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12)</f>
-        <v>139</v>
+        <v>122</v>
       </c>
     </row>
     <row r="57">
@@ -17557,7 +17575,7 @@
         </is>
       </c>
       <c r="B57" s="27">
-        <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$F$4:$F$12)</f>
+        <f>前提!$D$6+SUMPRODUCT($B$6:$B$14,案件一覧!$F$4:$F$12)</f>
         <v>249</v>
       </c>
     </row>
@@ -17580,7 +17598,7 @@
       </c>
       <c r="B59" s="21">
         <f>F42</f>
-        <v>407.3</v>
+        <v>423.3</v>
       </c>
     </row>
     <row r="60">
@@ -17591,7 +17609,7 @@
       </c>
       <c r="B60" s="21">
         <f>R42</f>
-        <v>431.5</v>
+        <v>363.6</v>
       </c>
     </row>
     <row r="61">
@@ -19293,63 +19311,63 @@
       </c>
       <c r="D40" s="24">
         <f>前提!E$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=2))</f>
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E40" s="24">
         <f>前提!F$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=3))</f>
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F40" s="24">
         <f>前提!G$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=4))</f>
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G40" s="24">
         <f>前提!H$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=5))</f>
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="H40" s="24">
         <f>前提!I$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=6))</f>
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="I40" s="24">
         <f>前提!J$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=7))</f>
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="J40" s="24">
         <f>前提!K$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=8))</f>
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="K40" s="24">
         <f>前提!L$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=9))</f>
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="L40" s="24">
         <f>前提!M$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=10))</f>
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="M40" s="24">
         <f>前提!N$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=11))</f>
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="N40" s="24">
         <f>前提!O$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=12))</f>
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="O40" s="24">
         <f>前提!P$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=13))</f>
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="P40" s="24">
         <f>前提!Q$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=14))</f>
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="24">
         <f>前提!R$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=15))</f>
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="R40" s="24">
         <f>前提!S$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=16))</f>
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="S40" s="24" t="n"/>
     </row>
@@ -19437,63 +19455,63 @@
       </c>
       <c r="D42" s="26">
         <f>D40*4+D38+D39-D41</f>
-        <v>291.5</v>
+        <v>283.5</v>
       </c>
       <c r="E42" s="26">
         <f>E40*4+E38+E39-E41</f>
-        <v>443.7</v>
+        <v>423.7</v>
       </c>
       <c r="F42" s="26">
         <f>F40*4+F38+F39-F41</f>
-        <v>402.7</v>
+        <v>418.7</v>
       </c>
       <c r="G42" s="26">
         <f>G40*4+G38+G39-G41</f>
-        <v>485.8</v>
+        <v>453.8</v>
       </c>
       <c r="H42" s="26">
         <f>H40*4+H38+H39-H41</f>
-        <v>483.6</v>
+        <v>451.6</v>
       </c>
       <c r="I42" s="26">
         <f>I40*4+I38+I39-I41</f>
-        <v>490.9</v>
+        <v>458.9</v>
       </c>
       <c r="J42" s="26">
         <f>J40*4+J38+J39-J41</f>
-        <v>490.8</v>
+        <v>458.8</v>
       </c>
       <c r="K42" s="26">
         <f>K40*4+K38+K39-K41</f>
-        <v>440.6</v>
+        <v>408.6</v>
       </c>
       <c r="L42" s="26">
         <f>L40*4+L38+L39-L41</f>
-        <v>440.5</v>
+        <v>408.5</v>
       </c>
       <c r="M42" s="26">
         <f>M40*4+M38+M39-M41</f>
-        <v>440.3</v>
+        <v>408.3</v>
       </c>
       <c r="N42" s="26">
         <f>N40*4+N38+N39-N41</f>
-        <v>440.2</v>
+        <v>408.2</v>
       </c>
       <c r="O42" s="26">
         <f>O40*4+O38+O39-O41</f>
-        <v>440.0</v>
+        <v>408.0</v>
       </c>
       <c r="P42" s="26">
         <f>P40*4+P38+P39-P41</f>
-        <v>439.9</v>
+        <v>407.9</v>
       </c>
       <c r="Q42" s="26">
         <f>Q40*4+Q38+Q39-Q41</f>
-        <v>439.7</v>
+        <v>407.7</v>
       </c>
       <c r="R42" s="26">
         <f>R40*4+R38+R39-R41</f>
-        <v>439.6</v>
+        <v>407.6</v>
       </c>
       <c r="S42" s="26" t="n"/>
     </row>
@@ -19617,12 +19635,12 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>年換算 調整後EBITDA（現状）</t>
+          <t>年換算 調整後EBITDA（実質収益力）</t>
         </is>
       </c>
       <c r="B56" s="27">
         <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12)</f>
-        <v>159</v>
+        <v>151</v>
       </c>
     </row>
     <row r="57">
@@ -19632,7 +19650,7 @@
         </is>
       </c>
       <c r="B57" s="27">
-        <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$F$4:$F$12)</f>
+        <f>前提!$D$6+SUMPRODUCT($B$6:$B$14,案件一覧!$F$4:$F$12)</f>
         <v>289</v>
       </c>
     </row>
@@ -19655,7 +19673,7 @@
       </c>
       <c r="B59" s="21">
         <f>F42</f>
-        <v>402.7</v>
+        <v>418.7</v>
       </c>
     </row>
     <row r="60">
@@ -19666,7 +19684,7 @@
       </c>
       <c r="B60" s="21">
         <f>R42</f>
-        <v>439.6</v>
+        <v>407.6</v>
       </c>
     </row>
     <row r="61">

--- a/EEFUL_資金計画_シナリオ別月次.xlsx
+++ b/EEFUL_資金計画_シナリオ別月次.xlsx
@@ -737,7 +737,7 @@
   <commentList>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>調整後EBITDA＝実質収益力（オーナー費用・非経常を調整した直近の年換算）。メディプロ実態18／ヒューマンアイ9.9（FA修正：食費増額+4.2・家賃+0.6、管理者補充あり）／クレッシェンド20／シルバー3期平均▲21（27/3期Q1営業損失▲5.6の年換算▲22と整合）／ワイズケア正常化38.2（藤井寺立上げ赤字を含む）／エーステイスト正常化24.9（9/2修正計画17.5＋役員報酬調整6.8＋非経常0.6）／日本経営センター調整後20.6（25/12期・IM）／セレサ営業利益8</t>
+        <t>調整後EBITDA＝実質収益力（オーナー費用・非経常を調整した直近の年換算）。メディプロ実態18／ヒューマンアイ9.9（FA修正：食費増額+4.2・家賃+0.6、管理者補充あり）／クレッシェンド20／シルバー0（森山氏指示：27/3期Q1で赤字縮小・6月単月黒字。参考：3期平均▲21）／ワイズケア正常化38.2（藤井寺立上げ赤字を含む）／エーステイスト正常化24.9（9/2修正計画17.5＋役員報酬調整6.8＋非経常0.6）／日本経営センター調整後20.6（25/12期・IM）／セレサ営業利益8</t>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="N5" s="9">
         <f>S1!$B$56</f>
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="O5" s="9">
         <f>S1!$B$57</f>
@@ -1306,11 +1306,11 @@
       </c>
       <c r="Q5" s="7">
         <f>S1!$B$59</f>
-        <v>336.2</v>
+        <v>420.2</v>
       </c>
       <c r="R5" s="7">
         <f>S1!$B$60</f>
-        <v>276.5</v>
+        <v>360.5</v>
       </c>
       <c r="S5" s="7">
         <f>S1!$B$61</f>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="N6" s="9">
         <f>S2!$B$56</f>
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="O6" s="9">
         <f>S2!$B$57</f>
@@ -1386,11 +1386,11 @@
       </c>
       <c r="Q6" s="7">
         <f>S2!$B$59</f>
-        <v>363.2</v>
+        <v>447.2</v>
       </c>
       <c r="R6" s="7">
         <f>S2!$B$60</f>
-        <v>303.5</v>
+        <v>387.5</v>
       </c>
       <c r="S6" s="7">
         <f>S2!$B$61</f>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="N7" s="9">
         <f>S3!$B$56</f>
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="O7" s="9">
         <f>S3!$B$57</f>
@@ -1466,11 +1466,11 @@
       </c>
       <c r="Q7" s="7">
         <f>S3!$B$59</f>
-        <v>396.4</v>
+        <v>480.3</v>
       </c>
       <c r="R7" s="7">
         <f>S3!$B$60</f>
-        <v>336.6</v>
+        <v>420.6</v>
       </c>
       <c r="S7" s="7">
         <f>S3!$B$61</f>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="N8" s="9">
         <f>S4!$B$56</f>
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="O8" s="9">
         <f>S4!$B$57</f>
@@ -1546,11 +1546,11 @@
       </c>
       <c r="Q8" s="7">
         <f>S4!$B$59</f>
-        <v>423.3</v>
+        <v>507.3</v>
       </c>
       <c r="R8" s="7">
         <f>S4!$B$60</f>
-        <v>363.6</v>
+        <v>447.5</v>
       </c>
       <c r="S8" s="7">
         <f>S4!$B$61</f>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="N9" s="9">
         <f>S5!$B$56</f>
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="O9" s="9">
         <f>S5!$B$57</f>
@@ -1626,11 +1626,11 @@
       </c>
       <c r="Q9" s="7">
         <f>S5!$B$59</f>
-        <v>418.7</v>
+        <v>502.7</v>
       </c>
       <c r="R9" s="7">
         <f>S5!$B$60</f>
-        <v>407.6</v>
+        <v>491.6</v>
       </c>
       <c r="S9" s="7">
         <f>S5!$B$61</f>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>59 / 140</t>
+          <t>80 / 140</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>97 / 206</t>
+          <t>118 / 206</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>84 / 183</t>
+          <t>105 / 183</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>122 / 249</t>
+          <t>143 / 249</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>151 / 289</t>
+          <t>172 / 289</t>
         </is>
       </c>
     </row>
@@ -2935,55 +2935,55 @@
       </c>
       <c r="G40" s="12">
         <f>S1!F42</f>
-        <v>336.2</v>
+        <v>420.2</v>
       </c>
       <c r="H40" s="12">
         <f>S1!G42</f>
-        <v>340.1</v>
+        <v>424.1</v>
       </c>
       <c r="I40" s="12">
         <f>S1!H42</f>
-        <v>340.0</v>
+        <v>424.0</v>
       </c>
       <c r="J40" s="12">
         <f>S1!I42</f>
-        <v>327.8</v>
+        <v>411.8</v>
       </c>
       <c r="K40" s="12">
         <f>S1!J42</f>
-        <v>327.7</v>
+        <v>411.7</v>
       </c>
       <c r="L40" s="12">
         <f>S1!K42</f>
-        <v>277.5</v>
+        <v>361.5</v>
       </c>
       <c r="M40" s="12">
         <f>S1!L42</f>
-        <v>277.4</v>
+        <v>361.4</v>
       </c>
       <c r="N40" s="12">
         <f>S1!M42</f>
-        <v>277.2</v>
+        <v>361.2</v>
       </c>
       <c r="O40" s="12">
         <f>S1!N42</f>
-        <v>277.1</v>
+        <v>361.1</v>
       </c>
       <c r="P40" s="12">
         <f>S1!O42</f>
-        <v>276.9</v>
+        <v>360.9</v>
       </c>
       <c r="Q40" s="12">
         <f>S1!P42</f>
-        <v>276.8</v>
+        <v>360.8</v>
       </c>
       <c r="R40" s="12">
         <f>S1!Q42</f>
-        <v>276.6</v>
+        <v>360.6</v>
       </c>
       <c r="S40" s="12">
         <f>S1!R42</f>
-        <v>276.5</v>
+        <v>360.5</v>
       </c>
     </row>
     <row r="41">
@@ -3006,55 +3006,55 @@
       </c>
       <c r="G41" s="12">
         <f>S2!F42</f>
-        <v>363.2</v>
+        <v>447.2</v>
       </c>
       <c r="H41" s="12">
         <f>S2!G42</f>
-        <v>367.1</v>
+        <v>451.1</v>
       </c>
       <c r="I41" s="12">
         <f>S2!H42</f>
-        <v>367.0</v>
+        <v>450.9</v>
       </c>
       <c r="J41" s="12">
         <f>S2!I42</f>
-        <v>354.8</v>
+        <v>438.8</v>
       </c>
       <c r="K41" s="12">
         <f>S2!J42</f>
-        <v>354.6</v>
+        <v>438.6</v>
       </c>
       <c r="L41" s="12">
         <f>S2!K42</f>
-        <v>304.5</v>
+        <v>388.5</v>
       </c>
       <c r="M41" s="12">
         <f>S2!L42</f>
-        <v>304.4</v>
+        <v>388.4</v>
       </c>
       <c r="N41" s="12">
         <f>S2!M42</f>
-        <v>304.2</v>
+        <v>388.2</v>
       </c>
       <c r="O41" s="12">
         <f>S2!N42</f>
-        <v>304.1</v>
+        <v>388.1</v>
       </c>
       <c r="P41" s="12">
         <f>S2!O42</f>
-        <v>303.9</v>
+        <v>387.9</v>
       </c>
       <c r="Q41" s="12">
         <f>S2!P42</f>
-        <v>303.8</v>
+        <v>387.8</v>
       </c>
       <c r="R41" s="12">
         <f>S2!Q42</f>
-        <v>303.6</v>
+        <v>387.6</v>
       </c>
       <c r="S41" s="12">
         <f>S2!R42</f>
-        <v>303.5</v>
+        <v>387.5</v>
       </c>
     </row>
     <row r="42">
@@ -3077,55 +3077,55 @@
       </c>
       <c r="G42" s="12">
         <f>S3!F42</f>
-        <v>396.4</v>
+        <v>480.3</v>
       </c>
       <c r="H42" s="12">
         <f>S3!G42</f>
-        <v>400.2</v>
+        <v>484.2</v>
       </c>
       <c r="I42" s="12">
         <f>S3!H42</f>
-        <v>400.1</v>
+        <v>484.0</v>
       </c>
       <c r="J42" s="12">
         <f>S3!I42</f>
-        <v>387.9</v>
+        <v>471.9</v>
       </c>
       <c r="K42" s="12">
         <f>S3!J42</f>
-        <v>387.8</v>
+        <v>471.7</v>
       </c>
       <c r="L42" s="12">
         <f>S3!K42</f>
-        <v>337.6</v>
+        <v>421.6</v>
       </c>
       <c r="M42" s="12">
         <f>S3!L42</f>
-        <v>337.5</v>
+        <v>421.4</v>
       </c>
       <c r="N42" s="12">
         <f>S3!M42</f>
-        <v>337.3</v>
+        <v>421.3</v>
       </c>
       <c r="O42" s="12">
         <f>S3!N42</f>
-        <v>337.2</v>
+        <v>421.2</v>
       </c>
       <c r="P42" s="12">
         <f>S3!O42</f>
-        <v>337.0</v>
+        <v>421.0</v>
       </c>
       <c r="Q42" s="12">
         <f>S3!P42</f>
-        <v>336.9</v>
+        <v>420.9</v>
       </c>
       <c r="R42" s="12">
         <f>S3!Q42</f>
-        <v>336.7</v>
+        <v>420.7</v>
       </c>
       <c r="S42" s="12">
         <f>S3!R42</f>
-        <v>336.6</v>
+        <v>420.6</v>
       </c>
     </row>
     <row r="43">
@@ -3148,55 +3148,55 @@
       </c>
       <c r="G43" s="12">
         <f>S4!F42</f>
-        <v>423.3</v>
+        <v>507.3</v>
       </c>
       <c r="H43" s="12">
         <f>S4!G42</f>
-        <v>427.2</v>
+        <v>511.2</v>
       </c>
       <c r="I43" s="12">
         <f>S4!H42</f>
-        <v>427.0</v>
+        <v>511.0</v>
       </c>
       <c r="J43" s="12">
         <f>S4!I42</f>
-        <v>414.9</v>
+        <v>498.9</v>
       </c>
       <c r="K43" s="12">
         <f>S4!J42</f>
-        <v>414.7</v>
+        <v>498.7</v>
       </c>
       <c r="L43" s="12">
         <f>S4!K42</f>
-        <v>364.6</v>
+        <v>448.6</v>
       </c>
       <c r="M43" s="12">
         <f>S4!L42</f>
-        <v>364.4</v>
+        <v>448.4</v>
       </c>
       <c r="N43" s="12">
         <f>S4!M42</f>
-        <v>364.3</v>
+        <v>448.3</v>
       </c>
       <c r="O43" s="12">
         <f>S4!N42</f>
-        <v>364.1</v>
+        <v>448.1</v>
       </c>
       <c r="P43" s="12">
         <f>S4!O42</f>
-        <v>364.0</v>
+        <v>448.0</v>
       </c>
       <c r="Q43" s="12">
         <f>S4!P42</f>
-        <v>363.8</v>
+        <v>447.8</v>
       </c>
       <c r="R43" s="12">
         <f>S4!Q42</f>
-        <v>363.7</v>
+        <v>447.7</v>
       </c>
       <c r="S43" s="12">
         <f>S4!R42</f>
-        <v>363.6</v>
+        <v>447.5</v>
       </c>
     </row>
     <row r="44">
@@ -3219,55 +3219,55 @@
       </c>
       <c r="G44" s="12">
         <f>S5!F42</f>
-        <v>418.7</v>
+        <v>502.7</v>
       </c>
       <c r="H44" s="12">
         <f>S5!G42</f>
-        <v>453.8</v>
+        <v>537.8</v>
       </c>
       <c r="I44" s="12">
         <f>S5!H42</f>
-        <v>451.6</v>
+        <v>535.6</v>
       </c>
       <c r="J44" s="12">
         <f>S5!I42</f>
-        <v>458.9</v>
+        <v>542.9</v>
       </c>
       <c r="K44" s="12">
         <f>S5!J42</f>
-        <v>458.8</v>
+        <v>542.8</v>
       </c>
       <c r="L44" s="12">
         <f>S5!K42</f>
-        <v>408.6</v>
+        <v>492.6</v>
       </c>
       <c r="M44" s="12">
         <f>S5!L42</f>
-        <v>408.5</v>
+        <v>492.5</v>
       </c>
       <c r="N44" s="12">
         <f>S5!M42</f>
-        <v>408.3</v>
+        <v>492.3</v>
       </c>
       <c r="O44" s="12">
         <f>S5!N42</f>
-        <v>408.2</v>
+        <v>492.2</v>
       </c>
       <c r="P44" s="12">
         <f>S5!O42</f>
-        <v>408.0</v>
+        <v>492.0</v>
       </c>
       <c r="Q44" s="12">
         <f>S5!P42</f>
-        <v>407.9</v>
+        <v>491.9</v>
       </c>
       <c r="R44" s="12">
         <f>S5!Q42</f>
-        <v>407.7</v>
+        <v>491.7</v>
       </c>
       <c r="S44" s="12">
         <f>S5!R42</f>
-        <v>407.6</v>
+        <v>491.6</v>
       </c>
     </row>
     <row r="87">
@@ -7756,7 +7756,7 @@
         <v>777</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>-21</v>
+        <v>0</v>
       </c>
       <c r="F12" s="15" t="n">
         <v>16</v>
@@ -11019,55 +11019,55 @@
       </c>
       <c r="F40" s="24">
         <f>前提!G$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=4))</f>
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="G40" s="24">
         <f>前提!H$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=5))</f>
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="H40" s="24">
         <f>前提!I$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=6))</f>
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="I40" s="24">
         <f>前提!J$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=7))</f>
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="J40" s="24">
         <f>前提!K$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=8))</f>
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="K40" s="24">
         <f>前提!L$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=9))</f>
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="L40" s="24">
         <f>前提!M$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=10))</f>
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="M40" s="24">
         <f>前提!N$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=11))</f>
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="N40" s="24">
         <f>前提!O$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=12))</f>
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="O40" s="24">
         <f>前提!P$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=13))</f>
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="P40" s="24">
         <f>前提!Q$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=14))</f>
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="Q40" s="24">
         <f>前提!R$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=15))</f>
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="R40" s="24">
         <f>前提!S$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=16))</f>
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="S40" s="24" t="n"/>
     </row>
@@ -11163,55 +11163,55 @@
       </c>
       <c r="F42" s="26">
         <f>F40*4+F38+F39-F41</f>
-        <v>336.2</v>
+        <v>420.2</v>
       </c>
       <c r="G42" s="26">
         <f>G40*4+G38+G39-G41</f>
-        <v>340.1</v>
+        <v>424.1</v>
       </c>
       <c r="H42" s="26">
         <f>H40*4+H38+H39-H41</f>
-        <v>340.0</v>
+        <v>424.0</v>
       </c>
       <c r="I42" s="26">
         <f>I40*4+I38+I39-I41</f>
-        <v>327.8</v>
+        <v>411.8</v>
       </c>
       <c r="J42" s="26">
         <f>J40*4+J38+J39-J41</f>
-        <v>327.7</v>
+        <v>411.7</v>
       </c>
       <c r="K42" s="26">
         <f>K40*4+K38+K39-K41</f>
-        <v>277.5</v>
+        <v>361.5</v>
       </c>
       <c r="L42" s="26">
         <f>L40*4+L38+L39-L41</f>
-        <v>277.4</v>
+        <v>361.4</v>
       </c>
       <c r="M42" s="26">
         <f>M40*4+M38+M39-M41</f>
-        <v>277.2</v>
+        <v>361.2</v>
       </c>
       <c r="N42" s="26">
         <f>N40*4+N38+N39-N41</f>
-        <v>277.1</v>
+        <v>361.1</v>
       </c>
       <c r="O42" s="26">
         <f>O40*4+O38+O39-O41</f>
-        <v>276.9</v>
+        <v>360.9</v>
       </c>
       <c r="P42" s="26">
         <f>P40*4+P38+P39-P41</f>
-        <v>276.8</v>
+        <v>360.8</v>
       </c>
       <c r="Q42" s="26">
         <f>Q40*4+Q38+Q39-Q41</f>
-        <v>276.6</v>
+        <v>360.6</v>
       </c>
       <c r="R42" s="26">
         <f>R40*4+R38+R39-R41</f>
-        <v>276.5</v>
+        <v>360.5</v>
       </c>
       <c r="S42" s="26" t="n"/>
     </row>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="B56" s="27">
         <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12)</f>
-        <v>59</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57">
@@ -11373,7 +11373,7 @@
       </c>
       <c r="B59" s="21">
         <f>F42</f>
-        <v>336.2</v>
+        <v>420.2</v>
       </c>
     </row>
     <row r="60">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="B60" s="21">
         <f>R42</f>
-        <v>276.5</v>
+        <v>360.5</v>
       </c>
     </row>
     <row r="61">
@@ -13094,55 +13094,55 @@
       </c>
       <c r="F40" s="24">
         <f>前提!G$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=4))</f>
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="G40" s="24">
         <f>前提!H$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=5))</f>
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="H40" s="24">
         <f>前提!I$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=6))</f>
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="I40" s="24">
         <f>前提!J$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=7))</f>
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="J40" s="24">
         <f>前提!K$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=8))</f>
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="K40" s="24">
         <f>前提!L$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=9))</f>
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="L40" s="24">
         <f>前提!M$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=10))</f>
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="M40" s="24">
         <f>前提!N$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=11))</f>
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="N40" s="24">
         <f>前提!O$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=12))</f>
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="O40" s="24">
         <f>前提!P$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=13))</f>
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="P40" s="24">
         <f>前提!Q$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=14))</f>
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="Q40" s="24">
         <f>前提!R$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=15))</f>
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="R40" s="24">
         <f>前提!S$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=16))</f>
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="S40" s="24" t="n"/>
     </row>
@@ -13238,55 +13238,55 @@
       </c>
       <c r="F42" s="26">
         <f>F40*4+F38+F39-F41</f>
-        <v>363.2</v>
+        <v>447.2</v>
       </c>
       <c r="G42" s="26">
         <f>G40*4+G38+G39-G41</f>
-        <v>367.1</v>
+        <v>451.1</v>
       </c>
       <c r="H42" s="26">
         <f>H40*4+H38+H39-H41</f>
-        <v>367.0</v>
+        <v>450.9</v>
       </c>
       <c r="I42" s="26">
         <f>I40*4+I38+I39-I41</f>
-        <v>354.8</v>
+        <v>438.8</v>
       </c>
       <c r="J42" s="26">
         <f>J40*4+J38+J39-J41</f>
-        <v>354.6</v>
+        <v>438.6</v>
       </c>
       <c r="K42" s="26">
         <f>K40*4+K38+K39-K41</f>
-        <v>304.5</v>
+        <v>388.5</v>
       </c>
       <c r="L42" s="26">
         <f>L40*4+L38+L39-L41</f>
-        <v>304.4</v>
+        <v>388.4</v>
       </c>
       <c r="M42" s="26">
         <f>M40*4+M38+M39-M41</f>
-        <v>304.2</v>
+        <v>388.2</v>
       </c>
       <c r="N42" s="26">
         <f>N40*4+N38+N39-N41</f>
-        <v>304.1</v>
+        <v>388.1</v>
       </c>
       <c r="O42" s="26">
         <f>O40*4+O38+O39-O41</f>
-        <v>303.9</v>
+        <v>387.9</v>
       </c>
       <c r="P42" s="26">
         <f>P40*4+P38+P39-P41</f>
-        <v>303.8</v>
+        <v>387.8</v>
       </c>
       <c r="Q42" s="26">
         <f>Q40*4+Q38+Q39-Q41</f>
-        <v>303.6</v>
+        <v>387.6</v>
       </c>
       <c r="R42" s="26">
         <f>R40*4+R38+R39-R41</f>
-        <v>303.5</v>
+        <v>387.5</v>
       </c>
       <c r="S42" s="26" t="n"/>
     </row>
@@ -13415,7 +13415,7 @@
       </c>
       <c r="B56" s="27">
         <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12)</f>
-        <v>97</v>
+        <v>118</v>
       </c>
     </row>
     <row r="57">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="B59" s="21">
         <f>F42</f>
-        <v>363.2</v>
+        <v>447.2</v>
       </c>
     </row>
     <row r="60">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="B60" s="21">
         <f>R42</f>
-        <v>303.5</v>
+        <v>387.5</v>
       </c>
     </row>
     <row r="61">
@@ -15169,55 +15169,55 @@
       </c>
       <c r="F40" s="24">
         <f>前提!G$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=4))</f>
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="G40" s="24">
         <f>前提!H$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=5))</f>
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="H40" s="24">
         <f>前提!I$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=6))</f>
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="I40" s="24">
         <f>前提!J$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=7))</f>
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="J40" s="24">
         <f>前提!K$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=8))</f>
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="K40" s="24">
         <f>前提!L$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=9))</f>
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="L40" s="24">
         <f>前提!M$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=10))</f>
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="M40" s="24">
         <f>前提!N$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=11))</f>
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="N40" s="24">
         <f>前提!O$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=12))</f>
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="O40" s="24">
         <f>前提!P$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=13))</f>
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="P40" s="24">
         <f>前提!Q$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=14))</f>
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="Q40" s="24">
         <f>前提!R$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=15))</f>
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="R40" s="24">
         <f>前提!S$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=16))</f>
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="S40" s="24" t="n"/>
     </row>
@@ -15313,55 +15313,55 @@
       </c>
       <c r="F42" s="26">
         <f>F40*4+F38+F39-F41</f>
-        <v>396.4</v>
+        <v>480.3</v>
       </c>
       <c r="G42" s="26">
         <f>G40*4+G38+G39-G41</f>
-        <v>400.2</v>
+        <v>484.2</v>
       </c>
       <c r="H42" s="26">
         <f>H40*4+H38+H39-H41</f>
-        <v>400.1</v>
+        <v>484.0</v>
       </c>
       <c r="I42" s="26">
         <f>I40*4+I38+I39-I41</f>
-        <v>387.9</v>
+        <v>471.9</v>
       </c>
       <c r="J42" s="26">
         <f>J40*4+J38+J39-J41</f>
-        <v>387.8</v>
+        <v>471.7</v>
       </c>
       <c r="K42" s="26">
         <f>K40*4+K38+K39-K41</f>
-        <v>337.6</v>
+        <v>421.6</v>
       </c>
       <c r="L42" s="26">
         <f>L40*4+L38+L39-L41</f>
-        <v>337.5</v>
+        <v>421.4</v>
       </c>
       <c r="M42" s="26">
         <f>M40*4+M38+M39-M41</f>
-        <v>337.3</v>
+        <v>421.3</v>
       </c>
       <c r="N42" s="26">
         <f>N40*4+N38+N39-N41</f>
-        <v>337.2</v>
+        <v>421.2</v>
       </c>
       <c r="O42" s="26">
         <f>O40*4+O38+O39-O41</f>
-        <v>337.0</v>
+        <v>421.0</v>
       </c>
       <c r="P42" s="26">
         <f>P40*4+P38+P39-P41</f>
-        <v>336.9</v>
+        <v>420.9</v>
       </c>
       <c r="Q42" s="26">
         <f>Q40*4+Q38+Q39-Q41</f>
-        <v>336.7</v>
+        <v>420.7</v>
       </c>
       <c r="R42" s="26">
         <f>R40*4+R38+R39-R41</f>
-        <v>336.6</v>
+        <v>420.6</v>
       </c>
       <c r="S42" s="26" t="n"/>
     </row>
@@ -15490,7 +15490,7 @@
       </c>
       <c r="B56" s="27">
         <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12)</f>
-        <v>84</v>
+        <v>105</v>
       </c>
     </row>
     <row r="57">
@@ -15523,7 +15523,7 @@
       </c>
       <c r="B59" s="21">
         <f>F42</f>
-        <v>396.4</v>
+        <v>480.3</v>
       </c>
     </row>
     <row r="60">
@@ -15534,7 +15534,7 @@
       </c>
       <c r="B60" s="21">
         <f>R42</f>
-        <v>336.6</v>
+        <v>420.6</v>
       </c>
     </row>
     <row r="61">
@@ -17244,55 +17244,55 @@
       </c>
       <c r="F40" s="24">
         <f>前提!G$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=4))</f>
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="G40" s="24">
         <f>前提!H$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=5))</f>
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="H40" s="24">
         <f>前提!I$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=6))</f>
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="I40" s="24">
         <f>前提!J$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=7))</f>
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="J40" s="24">
         <f>前提!K$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=8))</f>
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="K40" s="24">
         <f>前提!L$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=9))</f>
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="L40" s="24">
         <f>前提!M$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=10))</f>
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="M40" s="24">
         <f>前提!N$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=11))</f>
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="N40" s="24">
         <f>前提!O$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=12))</f>
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="O40" s="24">
         <f>前提!P$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=13))</f>
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="P40" s="24">
         <f>前提!Q$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=14))</f>
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="Q40" s="24">
         <f>前提!R$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=15))</f>
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="R40" s="24">
         <f>前提!S$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=16))</f>
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="S40" s="24" t="n"/>
     </row>
@@ -17388,55 +17388,55 @@
       </c>
       <c r="F42" s="26">
         <f>F40*4+F38+F39-F41</f>
-        <v>423.3</v>
+        <v>507.3</v>
       </c>
       <c r="G42" s="26">
         <f>G40*4+G38+G39-G41</f>
-        <v>427.2</v>
+        <v>511.2</v>
       </c>
       <c r="H42" s="26">
         <f>H40*4+H38+H39-H41</f>
-        <v>427.0</v>
+        <v>511.0</v>
       </c>
       <c r="I42" s="26">
         <f>I40*4+I38+I39-I41</f>
-        <v>414.9</v>
+        <v>498.9</v>
       </c>
       <c r="J42" s="26">
         <f>J40*4+J38+J39-J41</f>
-        <v>414.7</v>
+        <v>498.7</v>
       </c>
       <c r="K42" s="26">
         <f>K40*4+K38+K39-K41</f>
-        <v>364.6</v>
+        <v>448.6</v>
       </c>
       <c r="L42" s="26">
         <f>L40*4+L38+L39-L41</f>
-        <v>364.4</v>
+        <v>448.4</v>
       </c>
       <c r="M42" s="26">
         <f>M40*4+M38+M39-M41</f>
-        <v>364.3</v>
+        <v>448.3</v>
       </c>
       <c r="N42" s="26">
         <f>N40*4+N38+N39-N41</f>
-        <v>364.1</v>
+        <v>448.1</v>
       </c>
       <c r="O42" s="26">
         <f>O40*4+O38+O39-O41</f>
-        <v>364.0</v>
+        <v>448.0</v>
       </c>
       <c r="P42" s="26">
         <f>P40*4+P38+P39-P41</f>
-        <v>363.8</v>
+        <v>447.8</v>
       </c>
       <c r="Q42" s="26">
         <f>Q40*4+Q38+Q39-Q41</f>
-        <v>363.7</v>
+        <v>447.7</v>
       </c>
       <c r="R42" s="26">
         <f>R40*4+R38+R39-R41</f>
-        <v>363.6</v>
+        <v>447.5</v>
       </c>
       <c r="S42" s="26" t="n"/>
     </row>
@@ -17565,7 +17565,7 @@
       </c>
       <c r="B56" s="27">
         <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12)</f>
-        <v>122</v>
+        <v>143</v>
       </c>
     </row>
     <row r="57">
@@ -17598,7 +17598,7 @@
       </c>
       <c r="B59" s="21">
         <f>F42</f>
-        <v>423.3</v>
+        <v>507.3</v>
       </c>
     </row>
     <row r="60">
@@ -17609,7 +17609,7 @@
       </c>
       <c r="B60" s="21">
         <f>R42</f>
-        <v>363.6</v>
+        <v>447.5</v>
       </c>
     </row>
     <row r="61">
@@ -19319,55 +19319,55 @@
       </c>
       <c r="F40" s="24">
         <f>前提!G$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=4))</f>
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="G40" s="24">
         <f>前提!H$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=5))</f>
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="H40" s="24">
         <f>前提!I$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=6))</f>
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="I40" s="24">
         <f>前提!J$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=7))</f>
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="J40" s="24">
         <f>前提!K$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=8))</f>
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="K40" s="24">
         <f>前提!L$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=9))</f>
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="L40" s="24">
         <f>前提!M$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=10))</f>
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="M40" s="24">
         <f>前提!N$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=11))</f>
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="N40" s="24">
         <f>前提!O$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=12))</f>
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="O40" s="24">
         <f>前提!P$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=13))</f>
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="P40" s="24">
         <f>前提!Q$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=14))</f>
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="Q40" s="24">
         <f>前提!R$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=15))</f>
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="R40" s="24">
         <f>前提!S$56+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12,--(案件一覧!$M$4:$M$12&lt;=16))</f>
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="S40" s="24" t="n"/>
     </row>
@@ -19463,55 +19463,55 @@
       </c>
       <c r="F42" s="26">
         <f>F40*4+F38+F39-F41</f>
-        <v>418.7</v>
+        <v>502.7</v>
       </c>
       <c r="G42" s="26">
         <f>G40*4+G38+G39-G41</f>
-        <v>453.8</v>
+        <v>537.8</v>
       </c>
       <c r="H42" s="26">
         <f>H40*4+H38+H39-H41</f>
-        <v>451.6</v>
+        <v>535.6</v>
       </c>
       <c r="I42" s="26">
         <f>I40*4+I38+I39-I41</f>
-        <v>458.9</v>
+        <v>542.9</v>
       </c>
       <c r="J42" s="26">
         <f>J40*4+J38+J39-J41</f>
-        <v>458.8</v>
+        <v>542.8</v>
       </c>
       <c r="K42" s="26">
         <f>K40*4+K38+K39-K41</f>
-        <v>408.6</v>
+        <v>492.6</v>
       </c>
       <c r="L42" s="26">
         <f>L40*4+L38+L39-L41</f>
-        <v>408.5</v>
+        <v>492.5</v>
       </c>
       <c r="M42" s="26">
         <f>M40*4+M38+M39-M41</f>
-        <v>408.3</v>
+        <v>492.3</v>
       </c>
       <c r="N42" s="26">
         <f>N40*4+N38+N39-N41</f>
-        <v>408.2</v>
+        <v>492.2</v>
       </c>
       <c r="O42" s="26">
         <f>O40*4+O38+O39-O41</f>
-        <v>408.0</v>
+        <v>492.0</v>
       </c>
       <c r="P42" s="26">
         <f>P40*4+P38+P39-P41</f>
-        <v>407.9</v>
+        <v>491.9</v>
       </c>
       <c r="Q42" s="26">
         <f>Q40*4+Q38+Q39-Q41</f>
-        <v>407.7</v>
+        <v>491.7</v>
       </c>
       <c r="R42" s="26">
         <f>R40*4+R38+R39-R41</f>
-        <v>407.6</v>
+        <v>491.6</v>
       </c>
       <c r="S42" s="26" t="n"/>
     </row>
@@ -19640,7 +19640,7 @@
       </c>
       <c r="B56" s="27">
         <f>前提!$B$6+SUMPRODUCT($B$6:$B$14,案件一覧!$E$4:$E$12)</f>
-        <v>151</v>
+        <v>172</v>
       </c>
     </row>
     <row r="57">
@@ -19673,7 +19673,7 @@
       </c>
       <c r="B59" s="21">
         <f>F42</f>
-        <v>418.7</v>
+        <v>502.7</v>
       </c>
     </row>
     <row r="60">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="B60" s="21">
         <f>R42</f>
-        <v>407.6</v>
+        <v>491.6</v>
       </c>
     </row>
     <row r="61">

--- a/EEFUL_資金計画_シナリオ別月次.xlsx
+++ b/EEFUL_資金計画_シナリオ別月次.xlsx
@@ -16,7 +16,8 @@
     <sheet name="S3" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="S4" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="S5" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="月次実績2026" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="2026年末36億" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="月次実績2026" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -113,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -156,6 +157,8 @@
     <xf numFmtId="164" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3552,6 +3555,670 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>2026年12月末に年換算36億円に近づける道筋（百万円・手出し最小化・値貼付）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>確定4件＋HT100%化の年換算売上 2,435。36億円まで残り 1,165。年内決済の確率は当社の判断値。日本経営センター・セレサは12月決済に前倒しした場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>候補</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>年間売上</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>年内決済の確率</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>年内決済に必要な段取り</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>主なリスク</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>ワイズケア</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>485</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>LOI受入（9月中旬）→DD 9月下旬〜10月→最終条件11月上旬→SPA・決済11月下旬（LOIどおり）</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>八尾拠点の減収の構造性、退職慰労金50の損金限度、対象会社ローン80の銀行承認（11月中旬まで）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>エーステイスト</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>676</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>独占交渉権を10月上旬までに獲得→DD 10〜11月→事業譲渡契約・実行12月末</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>競合3社との条件競争、約40施設の委託契約・177名の転籍同意、借入60.4の免責的引受に銀行同意</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>日本経営センター</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>378</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>LOI提出9月末→基本合意10月中旬→DD 10月下旬〜11月→SPA・決済12月中旬（当初2027/1から前倒し）</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>売主・MACPの前倒し合意、奥様・息子の退任時期と引継ぎ、手数料25の負担</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>セレサ</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>140</v>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>LOI 10月上旬→DD 11月→SPA・決済12月（当初2027/3から前倒し）</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>統括貴島氏の処遇・インセンティブ制度の差、SMS手数料の再見積</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>プラスディー</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>1387</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>LOI 8/19・独占交渉期限10月末。年内決済には借換3.9億と手出し約3.7億の同時調達が必要</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>8法人（医療法人含む）の同時承継、ファクタリング解消、資金調達</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>カイゴス</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>96</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>対価3＋借入69引継。株式譲渡で手続きは軽い</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>債務超過▲44、役員借入放棄の確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>組み合わせ（確定4件＋HTに加えて）</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>12月末の年換算売上</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>36億円との差</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>実質EBITDA</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>改善後EBITDA</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>2026年の案件支出</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>12月末までの必要調達</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>27/12までの必要調達</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>同時成立確率</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>確定4件＋HT（基準）</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>2435</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>1165</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>140</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>241.7</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>＋ワイズケア</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>2920</v>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>680</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>118</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>206</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>377.7</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>139</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>211</v>
+      </c>
+      <c r="I14" s="13" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>＋エーステイスト</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>3111</v>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>489</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>105</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>183</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>316.2</v>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>78</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="I15" s="13" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>＋ワイズケア＋エーステイスト</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>3596</v>
+      </c>
+      <c r="C16" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>143</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>249</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>452.2</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>214</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>286</v>
+      </c>
+      <c r="I16" s="13" t="n">
+        <v>0.193</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>＋エーステイスト＋日本経営C＋セレサ</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n">
+        <v>3629</v>
+      </c>
+      <c r="C17" s="10" t="n">
+        <v>-29</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>134</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>223</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>466.2</v>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>228</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="I17" s="13" t="n">
+        <v>0.037</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>＋ワイズケア＋日本経営C＋セレサ</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>3438</v>
+      </c>
+      <c r="C18" s="10" t="n">
+        <v>162</v>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>147</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>246</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>527.8</v>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>290</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>362</v>
+      </c>
+      <c r="I18" s="13" t="n">
+        <v>0.058</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>＋ワイズ＋エース＋日本経営C</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>3974</v>
+      </c>
+      <c r="C19" s="10" t="n">
+        <v>-374</v>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>164</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>281</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <v>544.7</v>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>306</v>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>378</v>
+      </c>
+      <c r="I19" s="13" t="n">
+        <v>0.067</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>＋ワイズ＋エース＋日本経営C＋セレサ</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>4114</v>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>-514</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>172</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>289</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <v>602.3</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>364</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>436</v>
+      </c>
+      <c r="I20" s="13" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>追い方</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>36億以上</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>35億以上</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>32億以上</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>期待値（年換算売上）</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>35億以上（4件に集中）</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>36億以上（4件に集中）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>① ワイズケア＋エーステイストのみ</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>2937</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="29" t="inlineStr">
+        <is>
+          <t>② ①＋日本経営センター前倒し</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>3073</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>0.206</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="inlineStr">
+        <is>
+          <t>③ ②＋セレサ前倒し</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>3111</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>0.333</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>④ ③＋カイゴス</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="C26" s="13" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>3132</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>0.457</v>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>0.344</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="29" t="inlineStr">
+        <is>
+          <t>⑤ ④＋プラスディー（資金調達が付く場合）</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>3268</v>
+      </c>
+      <c r="F27" s="13" t="n"/>
+      <c r="G27" s="13" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>「4件に集中」＝ワイズケア75%・エーステイスト55%・日本経営センター50%・セレサ45%まで年内決済の確度を引き上げた場合（価格の上積み、外部DDの増員、売主への前倒し打診が前提）。モンテカルロ4万回</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
